--- a/DCF_Model_Sample.xlsx
+++ b/DCF_Model_Sample.xlsx
@@ -1,19 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Stock Search" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Assumptions" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Income Statement" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="WACC" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="DCF Valuation" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Sensitivity" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock Search" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income Statement" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WACC" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF Valuation" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reverse DCF" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Price" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,7 +31,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -137,12 +140,18 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00606060"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -182,6 +191,26 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00375623"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -229,9 +258,7 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color rgb="008EA9C1"/>
-      </right>
+      <right/>
       <top style="thin">
         <color rgb="008EA9C1"/>
       </top>
@@ -242,7 +269,9 @@
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin">
+        <color rgb="008EA9C1"/>
+      </right>
       <top style="thin">
         <color rgb="008EA9C1"/>
       </top>
@@ -255,7 +284,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -383,10 +412,13 @@
     <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -416,7 +448,7 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -431,8 +463,47 @@
     <xf numFmtId="165" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="13" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="13" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -510,18 +581,18 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Projected FCFF  (USD $M)</a:t>
+              <a:t>FCF Projection  (USD $M)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -531,17 +602,24 @@
       <barChart>
         <barDir val="col"/>
         <grouping val="clustered"/>
+        <varyColors val="1"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill>
-              <a:srgbClr val="2E4170"/>
-            </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <dLbls>
+            <numFmt formatCode="#,##0"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+            <showBubbleSize val="0"/>
+          </dLbls>
           <cat>
             <numRef>
               <f>'Income Statement'!$F$4:$O$4</f>
@@ -549,182 +627,11 @@
           </cat>
           <val>
             <numRef>
-              <f>'Income Statement'!$F$29</f>
+              <f>'Income Statement'!$F$29:$O$29</f>
             </numRef>
           </val>
         </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Income Statement'!$F$4:$O$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Income Statement'!$G$29</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Income Statement'!$F$4:$O$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Income Statement'!$H$29</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="3"/>
-          <order val="3"/>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Income Statement'!$F$4:$O$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Income Statement'!$I$29</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="4"/>
-          <order val="4"/>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Income Statement'!$F$4:$O$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Income Statement'!$J$29</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="5"/>
-          <order val="5"/>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Income Statement'!$F$4:$O$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Income Statement'!$K$29</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="6"/>
-          <order val="6"/>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Income Statement'!$F$4:$O$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Income Statement'!$L$29</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="7"/>
-          <order val="7"/>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Income Statement'!$F$4:$O$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Income Statement'!$M$29</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="8"/>
-          <order val="8"/>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Income Statement'!$F$4:$O$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Income Statement'!$N$29</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="9"/>
-          <order val="9"/>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Income Statement'!$F$4:$O$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Income Statement'!$O$29</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
+        <gapWidth val="30"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -733,9 +640,11 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -745,12 +654,11 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -766,9 +674,6 @@
         <crossAx val="10"/>
       </valAx>
     </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -776,7 +681,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>1</col>
@@ -784,16 +689,16 @@
       <row>32</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="3600000"/>
+    <ext cx="8640000" cy="4680000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1092,7 +997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:C10"/>
+  <dimension ref="B1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1110,77 +1015,430 @@
     <row r="2" ht="16" customHeight="1">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Built 2026-05-25  |  Gold cells = inputs  |  White cells = formulas</t>
+          <t xml:space="preserve">  Built 2026-06-02  |  Gold cells = inputs  |  White cells = formulas</t>
         </is>
       </c>
     </row>
     <row r="4" ht="14" customHeight="1">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  [Stock Search]  Enter ticker in B5. Microsoft 365: Data &gt; Stocks to link live data.</t>
-        </is>
-      </c>
-      <c r="C4" s="61" t="n"/>
+          <t xml:space="preserve">  [Stock Search]  One command to build and populate — pick your stock and date:</t>
+        </is>
+      </c>
+      <c r="C4" s="73" t="n"/>
     </row>
     <row r="5" ht="13" customHeight="1">
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">       Or run:  python build_dcf.py AAPL  to build and auto-fill in one step.</t>
-        </is>
-      </c>
-      <c r="C5" s="61" t="n"/>
-    </row>
-    <row r="6" ht="14" customHeight="1">
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  [Assumptions]  Edit all gold cells. Revenue growth, margins, WACC inputs, terminal value.</t>
-        </is>
-      </c>
-      <c r="C6" s="61" t="n"/>
-    </row>
-    <row r="7" ht="14" customHeight="1">
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  [Income Statement]  Historical (grey) + 10-year projection. FCF computed automatically.</t>
-        </is>
-      </c>
-      <c r="C7" s="61" t="n"/>
-    </row>
-    <row r="8" ht="14" customHeight="1">
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  [WACC]  Cost of equity (CAPM), cost of debt, capital structure -&gt; WACC.</t>
-        </is>
-      </c>
-      <c r="C8" s="61" t="n"/>
+          <t xml:space="preserve">         python build_dcf.py AAPL                     (live data)</t>
+        </is>
+      </c>
+      <c r="C5" s="73" t="n"/>
+    </row>
+    <row r="6" ht="13" customHeight="1">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         python build_dcf.py AAPL --date 2020-03-23   (COVID crash low)</t>
+        </is>
+      </c>
+      <c r="C6" s="73" t="n"/>
+    </row>
+    <row r="7" ht="13" customHeight="1">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         python build_dcf.py AAPL --date 2008         (financial crisis)</t>
+        </is>
+      </c>
+      <c r="C7" s="73" t="n"/>
+    </row>
+    <row r="8" ht="13" customHeight="1">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       Microsoft 365: select B5 then Data &gt; Stocks to link live data.</t>
+        </is>
+      </c>
+      <c r="C8" s="73" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="B9" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">  [Assumptions]  Edit all gold cells. Revenue growth, margins, WACC inputs, terminal value.</t>
+        </is>
+      </c>
+      <c r="C9" s="73" t="n"/>
+    </row>
+    <row r="10" ht="13" customHeight="1">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       To refresh data only:  python update_dcf.py AAPL  (keeps your thesis intact)</t>
+        </is>
+      </c>
+      <c r="C10" s="73" t="n"/>
+    </row>
+    <row r="11" ht="14" customHeight="1">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  [Income Statement]  Historical (grey) + 10-year projection. FCF computed automatically.</t>
+        </is>
+      </c>
+      <c r="C11" s="73" t="n"/>
+    </row>
+    <row r="12" ht="14" customHeight="1">
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  [WACC]  Cost of equity (CAPM), cost of debt, capital structure -&gt; WACC.</t>
+        </is>
+      </c>
+      <c r="C12" s="73" t="n"/>
+    </row>
+    <row r="13" ht="14" customHeight="1">
+      <c r="B13" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">  [DCF Valuation]  Discounted FCFs + terminal value -&gt; Enterprise Value -&gt; Implied Price.</t>
         </is>
       </c>
-      <c r="C9" s="61" t="n"/>
-    </row>
-    <row r="10" ht="14" customHeight="1">
-      <c r="B10" s="5" t="inlineStr">
+      <c r="C13" s="73" t="n"/>
+    </row>
+    <row r="14" ht="14" customHeight="1">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  [Sensitivity]  Implied price vs WACC x terminal growth rate. Green = upside.</t>
         </is>
       </c>
-      <c r="C10" s="61" t="n"/>
+      <c r="C14" s="73" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="13">
+    <mergeCell ref="B13:C13"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B11:C11"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B12:C12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="004472C4"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="B1" s="20" t="inlineStr">
+        <is>
+          <t>PRICE TRACKER  -  Intraday Monitor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="13" customHeight="1">
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Run  python update_dcf.py TICKER  to refresh. Gold cells = live data from Yahoo Finance. White = formulas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  COMPANY</t>
+        </is>
+      </c>
+      <c r="C4" s="72" t="n"/>
+      <c r="D4" s="72" t="n"/>
+      <c r="E4" s="73" t="n"/>
+    </row>
+    <row r="5" ht="17" customHeight="1">
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ticker</t>
+        </is>
+      </c>
+      <c r="C5" s="41">
+        <f>'Stock Search'!B5</f>
+        <v/>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Company</t>
+        </is>
+      </c>
+      <c r="E5" s="41">
+        <f>'Stock Search'!D5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Beta (1-yr vs S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="C6" s="38">
+        <f>Assumptions!C22</f>
+        <v/>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Last Updated</t>
+        </is>
+      </c>
+      <c r="E6" s="41">
+        <f>TEXT('Stock Search'!E5,"YYYY-MM-DD")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SESSION PRICES  (refreshed by update_dcf.py)</t>
+        </is>
+      </c>
+      <c r="C7" s="72" t="n"/>
+      <c r="D7" s="72" t="n"/>
+      <c r="E7" s="73" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Open ($)</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>309.63</v>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Market Status</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>HISTORICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Current ($)</t>
+        </is>
+      </c>
+      <c r="C9" s="71">
+        <f>'Stock Search'!C5</f>
+        <v/>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Change from Open ($)</t>
+        </is>
+      </c>
+      <c r="E9" s="71">
+        <f>'Stock Search'!C5-C8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Session High ($)</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>310.94</v>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Session Low ($)</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>305.02</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Change from Open (%)</t>
+        </is>
+      </c>
+      <c r="C11" s="24">
+        <f>IF(C8=0,0,('Stock Search'!C5-C8)/C8)</f>
+        <v/>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  High-Low Range ($)</t>
+        </is>
+      </c>
+      <c r="E11" s="71">
+        <f>C10-E10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  52-WEEK RANGE</t>
+        </is>
+      </c>
+      <c r="C12" s="72" t="n"/>
+      <c r="D12" s="72" t="n"/>
+      <c r="E12" s="73" t="n"/>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  52-Week High ($)</t>
+        </is>
+      </c>
+      <c r="C13" s="53">
+        <f>'Stock Search'!D8</f>
+        <v/>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  52-Week Low ($)</t>
+        </is>
+      </c>
+      <c r="E13" s="53">
+        <f>'Stock Search'!E8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  vs 52-Week High</t>
+        </is>
+      </c>
+      <c r="C14" s="34">
+        <f>IF(C13=0,0,('Stock Search'!C5-C13)/C13)</f>
+        <v/>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  vs 52-Week Low</t>
+        </is>
+      </c>
+      <c r="E14" s="34">
+        <f>IF(E13=0,0,('Stock Search'!C5-E13)/E13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  52-Week Percentile  (100% = at 52W high)</t>
+        </is>
+      </c>
+      <c r="C15" s="55">
+        <f>IFERROR(('Stock Search'!C5-E13)/(C13-E13),0)</f>
+        <v/>
+      </c>
+      <c r="D15" s="72" t="n"/>
+      <c r="E15" s="73" t="n"/>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  BETA-ADJUSTED PERFORMANCE  (vs S&amp;P 500 today)</t>
+        </is>
+      </c>
+      <c r="C16" s="72" t="n"/>
+      <c r="D16" s="72" t="n"/>
+      <c r="E16" s="73" t="n"/>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  S&amp;P 500 Move Today (%)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (auto-filled by update_dcf.py)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr"/>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Expected Move  (Beta x S&amp;P move)</t>
+        </is>
+      </c>
+      <c r="C18" s="34">
+        <f>Assumptions!C22*C17</f>
+        <v/>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Actual Move (vs open)</t>
+        </is>
+      </c>
+      <c r="E18" s="34">
+        <f>C11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Alpha Today  (actual - expected)</t>
+        </is>
+      </c>
+      <c r="C19" s="24">
+        <f>C11-Assumptions!C22*C17</f>
+        <v/>
+      </c>
+      <c r="D19" s="72" t="n"/>
+      <c r="E19" s="73" t="n"/>
+    </row>
+    <row r="20" ht="14" customHeight="1">
+      <c r="B20" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Alpha = actual stock move minus CAPM-predicted move (beta x market). Positive alpha = stock outperformed its risk-adjusted expectation today.</t>
+        </is>
+      </c>
+      <c r="C20" s="72" t="n"/>
+      <c r="D20" s="72" t="n"/>
+      <c r="E20" s="73" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="C15:E15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1193,7 +1451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E28"/>
+  <dimension ref="B1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1246,7 +1504,7 @@
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>308.82</v>
+        <v>306.31</v>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
@@ -1255,7 +1513,7 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01 (historical)</t>
         </is>
       </c>
     </row>
@@ -1265,9 +1523,9 @@
           <t xml:space="preserve">  PRICE &amp; RANGE</t>
         </is>
       </c>
-      <c r="C7" s="62" t="n"/>
-      <c r="D7" s="62" t="n"/>
-      <c r="E7" s="61" t="n"/>
+      <c r="C7" s="72" t="n"/>
+      <c r="D7" s="72" t="n"/>
+      <c r="E7" s="73" t="n"/>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="B8" s="12" t="inlineStr">
@@ -1276,13 +1534,13 @@
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>308.82</v>
+        <v>306.31</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>311.4</v>
+        <v>315</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>192.7</v>
+        <v>194.3</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
@@ -1291,9 +1549,9 @@
           <t xml:space="preserve">  SHARES &amp; MARKET CAP</t>
         </is>
       </c>
-      <c r="C9" s="62" t="n"/>
-      <c r="D9" s="62" t="n"/>
-      <c r="E9" s="61" t="n"/>
+      <c r="C9" s="72" t="n"/>
+      <c r="D9" s="72" t="n"/>
+      <c r="E9" s="73" t="n"/>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="B10" s="12" t="inlineStr">
@@ -1302,13 +1560,13 @@
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>4535749.2</v>
+        <v>4498884</v>
       </c>
       <c r="D10" s="13" t="n">
         <v>14687.4</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>0.9983</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
@@ -1317,9 +1575,9 @@
           <t xml:space="preserve">  INCOME (TTM, $M)</t>
         </is>
       </c>
-      <c r="C11" s="62" t="n"/>
-      <c r="D11" s="62" t="n"/>
-      <c r="E11" s="61" t="n"/>
+      <c r="C11" s="72" t="n"/>
+      <c r="D11" s="72" t="n"/>
+      <c r="E11" s="73" t="n"/>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="B12" s="12" t="inlineStr">
@@ -1328,13 +1586,13 @@
         </is>
       </c>
       <c r="C12" s="13" t="n">
-        <v>451442</v>
+        <v>416161</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>159976</v>
+        <v>144748</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>122575</v>
+        <v>112010</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
@@ -1343,9 +1601,9 @@
           <t xml:space="preserve">  BALANCE SHEET ($M)</t>
         </is>
       </c>
-      <c r="C13" s="62" t="n"/>
-      <c r="D13" s="62" t="n"/>
-      <c r="E13" s="61" t="n"/>
+      <c r="C13" s="72" t="n"/>
+      <c r="D13" s="72" t="n"/>
+      <c r="E13" s="73" t="n"/>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="B14" s="12" t="inlineStr">
@@ -1354,10 +1612,10 @@
         </is>
       </c>
       <c r="C14" s="13" t="n">
-        <v>84711</v>
+        <v>98657</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>68507</v>
+        <v>35934</v>
       </c>
       <c r="E14" s="15">
         <f>C16-D16</f>
@@ -1370,9 +1628,9 @@
           <t xml:space="preserve">  VALUATION</t>
         </is>
       </c>
-      <c r="C15" s="62" t="n"/>
-      <c r="D15" s="62" t="n"/>
-      <c r="E15" s="61" t="n"/>
+      <c r="C15" s="72" t="n"/>
+      <c r="D15" s="72" t="n"/>
+      <c r="E15" s="73" t="n"/>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="B16" s="12" t="inlineStr">
@@ -1381,13 +1639,13 @@
         </is>
       </c>
       <c r="C16" s="16" t="n">
-        <v>37.4</v>
+        <v>40.2</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>28.5</v>
+        <v>31.5</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>1.06</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
@@ -1396,9 +1654,9 @@
           <t xml:space="preserve">  MICROSOFT 365 STOCKS DATA TYPE - INSTRUCTIONS</t>
         </is>
       </c>
-      <c r="C18" s="62" t="n"/>
-      <c r="D18" s="62" t="n"/>
-      <c r="E18" s="61" t="n"/>
+      <c r="C18" s="72" t="n"/>
+      <c r="D18" s="72" t="n"/>
+      <c r="E18" s="73" t="n"/>
     </row>
     <row r="19" ht="13" customHeight="1">
       <c r="B19" s="18" t="inlineStr">
@@ -1406,9 +1664,9 @@
           <t xml:space="preserve">  1. Type ticker in B5  (e.g. AAPL, MSFT, GOOGL, NVDA)</t>
         </is>
       </c>
-      <c r="C19" s="62" t="n"/>
-      <c r="D19" s="62" t="n"/>
-      <c r="E19" s="61" t="n"/>
+      <c r="C19" s="72" t="n"/>
+      <c r="D19" s="72" t="n"/>
+      <c r="E19" s="73" t="n"/>
     </row>
     <row r="20" ht="13" customHeight="1">
       <c r="B20" s="18" t="inlineStr">
@@ -1416,9 +1674,9 @@
           <t xml:space="preserve">  2. With B5 selected: click  Data  tab  &gt;  Stocks  button in ribbon</t>
         </is>
       </c>
-      <c r="C20" s="62" t="n"/>
-      <c r="D20" s="62" t="n"/>
-      <c r="E20" s="61" t="n"/>
+      <c r="C20" s="72" t="n"/>
+      <c r="D20" s="72" t="n"/>
+      <c r="E20" s="73" t="n"/>
     </row>
     <row r="21" ht="13" customHeight="1">
       <c r="B21" s="18" t="inlineStr">
@@ -1426,9 +1684,9 @@
           <t xml:space="preserve">  3. Excel converts the text to a linked Stocks data type (shows stock icon)</t>
         </is>
       </c>
-      <c r="C21" s="62" t="n"/>
-      <c r="D21" s="62" t="n"/>
-      <c r="E21" s="61" t="n"/>
+      <c r="C21" s="72" t="n"/>
+      <c r="D21" s="72" t="n"/>
+      <c r="E21" s="73" t="n"/>
     </row>
     <row r="22" ht="13" customHeight="1">
       <c r="B22" s="18" t="inlineStr">
@@ -1436,9 +1694,9 @@
           <t xml:space="preserve">  4. Click the icon to browse available fields, or type  =B5.Price  to extract any field</t>
         </is>
       </c>
-      <c r="C22" s="62" t="n"/>
-      <c r="D22" s="62" t="n"/>
-      <c r="E22" s="61" t="n"/>
+      <c r="C22" s="72" t="n"/>
+      <c r="D22" s="72" t="n"/>
+      <c r="E22" s="73" t="n"/>
     </row>
     <row r="23" ht="13" customHeight="1">
       <c r="B23" s="18" t="inlineStr">
@@ -1446,19 +1704,19 @@
           <t xml:space="preserve">  5. STOCKHISTORY(B5, start_date, end_date)  returns historical price table</t>
         </is>
       </c>
-      <c r="C23" s="62" t="n"/>
-      <c r="D23" s="62" t="n"/>
-      <c r="E23" s="61" t="n"/>
+      <c r="C23" s="72" t="n"/>
+      <c r="D23" s="72" t="n"/>
+      <c r="E23" s="73" t="n"/>
     </row>
     <row r="24" ht="13" customHeight="1">
       <c r="B24" s="18" t="inlineStr">
         <is>
-          <t>  </t>
-        </is>
-      </c>
-      <c r="C24" s="62" t="n"/>
-      <c r="D24" s="62" t="n"/>
-      <c r="E24" s="61" t="n"/>
+          <t xml:space="preserve">  </t>
+        </is>
+      </c>
+      <c r="C24" s="72" t="n"/>
+      <c r="D24" s="72" t="n"/>
+      <c r="E24" s="73" t="n"/>
     </row>
     <row r="25" ht="13" customHeight="1">
       <c r="B25" s="5" t="inlineStr">
@@ -1466,9 +1724,9 @@
           <t xml:space="preserve">  PYTHON AUTO-FILL (works with any Excel version):</t>
         </is>
       </c>
-      <c r="C25" s="62" t="n"/>
-      <c r="D25" s="62" t="n"/>
-      <c r="E25" s="61" t="n"/>
+      <c r="C25" s="72" t="n"/>
+      <c r="D25" s="72" t="n"/>
+      <c r="E25" s="73" t="n"/>
     </row>
     <row r="26" ht="13" customHeight="1">
       <c r="B26" s="19" t="inlineStr">
@@ -1476,32 +1734,22 @@
           <t xml:space="preserve">     pip install yfinance openpyxl</t>
         </is>
       </c>
-      <c r="C26" s="62" t="n"/>
-      <c r="D26" s="62" t="n"/>
-      <c r="E26" s="61" t="n"/>
+      <c r="C26" s="72" t="n"/>
+      <c r="D26" s="72" t="n"/>
+      <c r="E26" s="73" t="n"/>
     </row>
     <row r="27" ht="13" customHeight="1">
       <c r="B27" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">     python build_dcf.py AAPL   (build + fill in one step)</t>
-        </is>
-      </c>
-      <c r="C27" s="62" t="n"/>
-      <c r="D27" s="62" t="n"/>
-      <c r="E27" s="61" t="n"/>
-    </row>
-    <row r="28" ht="13" customHeight="1">
-      <c r="B28" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     python update_dcf.py AAPL  (refresh an existing model)</t>
-        </is>
-      </c>
-      <c r="C28" s="62" t="n"/>
-      <c r="D28" s="62" t="n"/>
-      <c r="E28" s="61" t="n"/>
+          <t xml:space="preserve">     python update_dcf.py AAPL</t>
+        </is>
+      </c>
+      <c r="C27" s="72" t="n"/>
+      <c r="D27" s="72" t="n"/>
+      <c r="E27" s="73" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="22">
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B15:E15"/>
     <mergeCell ref="B24:E24"/>
@@ -1524,7 +1772,6 @@
     <mergeCell ref="B13:E13"/>
     <mergeCell ref="B10"/>
     <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B28:E28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1567,9 +1814,9 @@
           <t xml:space="preserve">  COMPANY</t>
         </is>
       </c>
-      <c r="C4" s="62" t="n"/>
-      <c r="D4" s="62" t="n"/>
-      <c r="E4" s="61" t="n"/>
+      <c r="C4" s="72" t="n"/>
+      <c r="D4" s="72" t="n"/>
+      <c r="E4" s="73" t="n"/>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="B5" s="18" t="inlineStr">
@@ -1622,7 +1869,7 @@
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>308.82</v>
+        <v>306.31</v>
       </c>
       <c r="D7" s="18" t="inlineStr">
         <is>
@@ -1640,7 +1887,7 @@
         </is>
       </c>
       <c r="C8" s="13" t="n">
-        <v>84711</v>
+        <v>98657</v>
       </c>
       <c r="D8" s="18" t="inlineStr">
         <is>
@@ -1648,7 +1895,7 @@
         </is>
       </c>
       <c r="E8" s="13" t="n">
-        <v>68507</v>
+        <v>35934</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
@@ -1657,9 +1904,9 @@
           <t xml:space="preserve">  REVENUE GROWTH  (10-year projection ramp)</t>
         </is>
       </c>
-      <c r="C9" s="62" t="n"/>
-      <c r="D9" s="62" t="n"/>
-      <c r="E9" s="61" t="n"/>
+      <c r="C9" s="72" t="n"/>
+      <c r="D9" s="72" t="n"/>
+      <c r="E9" s="73" t="n"/>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="B10" s="18" t="inlineStr">
@@ -1757,9 +2004,9 @@
           <t xml:space="preserve">  MARGIN ASSUMPTIONS</t>
         </is>
       </c>
-      <c r="C15" s="62" t="n"/>
-      <c r="D15" s="62" t="n"/>
-      <c r="E15" s="61" t="n"/>
+      <c r="C15" s="72" t="n"/>
+      <c r="D15" s="72" t="n"/>
+      <c r="E15" s="73" t="n"/>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="B16" s="18" t="inlineStr">
@@ -1833,9 +2080,9 @@
           <t xml:space="preserve">  WACC INPUTS</t>
         </is>
       </c>
-      <c r="C20" s="62" t="n"/>
-      <c r="D20" s="62" t="n"/>
-      <c r="E20" s="61" t="n"/>
+      <c r="C20" s="72" t="n"/>
+      <c r="D20" s="72" t="n"/>
+      <c r="E20" s="73" t="n"/>
     </row>
     <row r="21" ht="17" customHeight="1">
       <c r="B21" s="18" t="inlineStr">
@@ -1844,7 +2091,7 @@
         </is>
       </c>
       <c r="C21" s="21" t="n">
-        <v>0.043</v>
+        <v>0.04475</v>
       </c>
       <c r="D21" s="18" t="inlineStr">
         <is>
@@ -1862,7 +2109,7 @@
         </is>
       </c>
       <c r="C22" s="17" t="n">
-        <v>1.06</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D22" s="18" t="inlineStr">
         <is>
@@ -1910,9 +2157,9 @@
           <t xml:space="preserve">  TERMINAL VALUE</t>
         </is>
       </c>
-      <c r="C25" s="62" t="n"/>
-      <c r="D25" s="62" t="n"/>
-      <c r="E25" s="61" t="n"/>
+      <c r="C25" s="72" t="n"/>
+      <c r="D25" s="72" t="n"/>
+      <c r="E25" s="73" t="n"/>
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="B26" s="18" t="inlineStr">
@@ -1938,9 +2185,9 @@
           <t xml:space="preserve">  HISTORICAL REVENUE (for Y0 base)</t>
         </is>
       </c>
-      <c r="C27" s="62" t="n"/>
-      <c r="D27" s="62" t="n"/>
-      <c r="E27" s="61" t="n"/>
+      <c r="C27" s="72" t="n"/>
+      <c r="D27" s="72" t="n"/>
+      <c r="E27" s="73" t="n"/>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="B28" s="18" t="inlineStr">
@@ -1949,7 +2196,7 @@
         </is>
       </c>
       <c r="C28" s="13" t="n">
-        <v>451442</v>
+        <v>416161</v>
       </c>
       <c r="D28" s="18" t="inlineStr">
         <is>
@@ -1978,9 +2225,9 @@
           <t xml:space="preserve">  INVESTMENT THESIS (free text)</t>
         </is>
       </c>
-      <c r="C31" s="62" t="n"/>
-      <c r="D31" s="62" t="n"/>
-      <c r="E31" s="61" t="n"/>
+      <c r="C31" s="72" t="n"/>
+      <c r="D31" s="72" t="n"/>
+      <c r="E31" s="73" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="B32" s="9" t="inlineStr">
@@ -1988,9 +2235,9 @@
           <t>Company and thesis notes here.</t>
         </is>
       </c>
-      <c r="C32" s="62" t="n"/>
-      <c r="D32" s="62" t="n"/>
-      <c r="E32" s="61" t="n"/>
+      <c r="C32" s="72" t="n"/>
+      <c r="D32" s="72" t="n"/>
+      <c r="E32" s="73" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="B33" s="9" t="inlineStr">
@@ -1998,9 +2245,9 @@
           <t>Key risks:</t>
         </is>
       </c>
-      <c r="C33" s="62" t="n"/>
-      <c r="D33" s="62" t="n"/>
-      <c r="E33" s="61" t="n"/>
+      <c r="C33" s="72" t="n"/>
+      <c r="D33" s="72" t="n"/>
+      <c r="E33" s="73" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="B34" s="9" t="inlineStr">
@@ -2008,9 +2255,9 @@
           <t>Key catalysts:</t>
         </is>
       </c>
-      <c r="C34" s="62" t="n"/>
-      <c r="D34" s="62" t="n"/>
-      <c r="E34" s="61" t="n"/>
+      <c r="C34" s="72" t="n"/>
+      <c r="D34" s="72" t="n"/>
+      <c r="E34" s="73" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -2019,13 +2266,13 @@
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B32:E32"/>
     <mergeCell ref="B15:E15"/>
     <mergeCell ref="B33:E33"/>
     <mergeCell ref="B25:E25"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="B20:E20"/>
-    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B34:E34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2156,19 +2403,19 @@
           <t xml:space="preserve">  REVENUE</t>
         </is>
       </c>
-      <c r="C5" s="62" t="n"/>
-      <c r="D5" s="62" t="n"/>
-      <c r="E5" s="62" t="n"/>
-      <c r="F5" s="62" t="n"/>
-      <c r="G5" s="62" t="n"/>
-      <c r="H5" s="62" t="n"/>
-      <c r="I5" s="62" t="n"/>
-      <c r="J5" s="62" t="n"/>
-      <c r="K5" s="62" t="n"/>
-      <c r="L5" s="62" t="n"/>
-      <c r="M5" s="62" t="n"/>
-      <c r="N5" s="62" t="n"/>
-      <c r="O5" s="61" t="n"/>
+      <c r="C5" s="72" t="n"/>
+      <c r="D5" s="72" t="n"/>
+      <c r="E5" s="72" t="n"/>
+      <c r="F5" s="72" t="n"/>
+      <c r="G5" s="72" t="n"/>
+      <c r="H5" s="72" t="n"/>
+      <c r="I5" s="72" t="n"/>
+      <c r="J5" s="72" t="n"/>
+      <c r="K5" s="72" t="n"/>
+      <c r="L5" s="72" t="n"/>
+      <c r="M5" s="72" t="n"/>
+      <c r="N5" s="72" t="n"/>
+      <c r="O5" s="73" t="n"/>
     </row>
     <row r="6" ht="14" customHeight="1">
       <c r="B6" s="19" t="inlineStr">
@@ -2295,19 +2542,19 @@
           <t xml:space="preserve">  GROSS PROFIT</t>
         </is>
       </c>
-      <c r="C8" s="62" t="n"/>
-      <c r="D8" s="62" t="n"/>
-      <c r="E8" s="62" t="n"/>
-      <c r="F8" s="62" t="n"/>
-      <c r="G8" s="62" t="n"/>
-      <c r="H8" s="62" t="n"/>
-      <c r="I8" s="62" t="n"/>
-      <c r="J8" s="62" t="n"/>
-      <c r="K8" s="62" t="n"/>
-      <c r="L8" s="62" t="n"/>
-      <c r="M8" s="62" t="n"/>
-      <c r="N8" s="62" t="n"/>
-      <c r="O8" s="61" t="n"/>
+      <c r="C8" s="72" t="n"/>
+      <c r="D8" s="72" t="n"/>
+      <c r="E8" s="72" t="n"/>
+      <c r="F8" s="72" t="n"/>
+      <c r="G8" s="72" t="n"/>
+      <c r="H8" s="72" t="n"/>
+      <c r="I8" s="72" t="n"/>
+      <c r="J8" s="72" t="n"/>
+      <c r="K8" s="72" t="n"/>
+      <c r="L8" s="72" t="n"/>
+      <c r="M8" s="72" t="n"/>
+      <c r="N8" s="72" t="n"/>
+      <c r="O8" s="73" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="B9" s="19" t="inlineStr">
@@ -2430,19 +2677,19 @@
           <t xml:space="preserve">  OPERATING EXPENSES -&gt; EBITDA</t>
         </is>
       </c>
-      <c r="C11" s="62" t="n"/>
-      <c r="D11" s="62" t="n"/>
-      <c r="E11" s="62" t="n"/>
-      <c r="F11" s="62" t="n"/>
-      <c r="G11" s="62" t="n"/>
-      <c r="H11" s="62" t="n"/>
-      <c r="I11" s="62" t="n"/>
-      <c r="J11" s="62" t="n"/>
-      <c r="K11" s="62" t="n"/>
-      <c r="L11" s="62" t="n"/>
-      <c r="M11" s="62" t="n"/>
-      <c r="N11" s="62" t="n"/>
-      <c r="O11" s="61" t="n"/>
+      <c r="C11" s="72" t="n"/>
+      <c r="D11" s="72" t="n"/>
+      <c r="E11" s="72" t="n"/>
+      <c r="F11" s="72" t="n"/>
+      <c r="G11" s="72" t="n"/>
+      <c r="H11" s="72" t="n"/>
+      <c r="I11" s="72" t="n"/>
+      <c r="J11" s="72" t="n"/>
+      <c r="K11" s="72" t="n"/>
+      <c r="L11" s="72" t="n"/>
+      <c r="M11" s="72" t="n"/>
+      <c r="N11" s="72" t="n"/>
+      <c r="O11" s="73" t="n"/>
     </row>
     <row r="12" ht="14" customHeight="1">
       <c r="B12" s="19" t="inlineStr">
@@ -2624,19 +2871,19 @@
           <t xml:space="preserve">  D&amp;A  -&gt;  EBIT</t>
         </is>
       </c>
-      <c r="C15" s="62" t="n"/>
-      <c r="D15" s="62" t="n"/>
-      <c r="E15" s="62" t="n"/>
-      <c r="F15" s="62" t="n"/>
-      <c r="G15" s="62" t="n"/>
-      <c r="H15" s="62" t="n"/>
-      <c r="I15" s="62" t="n"/>
-      <c r="J15" s="62" t="n"/>
-      <c r="K15" s="62" t="n"/>
-      <c r="L15" s="62" t="n"/>
-      <c r="M15" s="62" t="n"/>
-      <c r="N15" s="62" t="n"/>
-      <c r="O15" s="61" t="n"/>
+      <c r="C15" s="72" t="n"/>
+      <c r="D15" s="72" t="n"/>
+      <c r="E15" s="72" t="n"/>
+      <c r="F15" s="72" t="n"/>
+      <c r="G15" s="72" t="n"/>
+      <c r="H15" s="72" t="n"/>
+      <c r="I15" s="72" t="n"/>
+      <c r="J15" s="72" t="n"/>
+      <c r="K15" s="72" t="n"/>
+      <c r="L15" s="72" t="n"/>
+      <c r="M15" s="72" t="n"/>
+      <c r="N15" s="72" t="n"/>
+      <c r="O15" s="73" t="n"/>
     </row>
     <row r="16" ht="14" customHeight="1">
       <c r="B16" s="19" t="inlineStr">
@@ -2877,19 +3124,19 @@
           <t xml:space="preserve">  NOPAT  (Net Operating Profit After Tax)</t>
         </is>
       </c>
-      <c r="C20" s="62" t="n"/>
-      <c r="D20" s="62" t="n"/>
-      <c r="E20" s="62" t="n"/>
-      <c r="F20" s="62" t="n"/>
-      <c r="G20" s="62" t="n"/>
-      <c r="H20" s="62" t="n"/>
-      <c r="I20" s="62" t="n"/>
-      <c r="J20" s="62" t="n"/>
-      <c r="K20" s="62" t="n"/>
-      <c r="L20" s="62" t="n"/>
-      <c r="M20" s="62" t="n"/>
-      <c r="N20" s="62" t="n"/>
-      <c r="O20" s="61" t="n"/>
+      <c r="C20" s="72" t="n"/>
+      <c r="D20" s="72" t="n"/>
+      <c r="E20" s="72" t="n"/>
+      <c r="F20" s="72" t="n"/>
+      <c r="G20" s="72" t="n"/>
+      <c r="H20" s="72" t="n"/>
+      <c r="I20" s="72" t="n"/>
+      <c r="J20" s="72" t="n"/>
+      <c r="K20" s="72" t="n"/>
+      <c r="L20" s="72" t="n"/>
+      <c r="M20" s="72" t="n"/>
+      <c r="N20" s="72" t="n"/>
+      <c r="O20" s="73" t="n"/>
     </row>
     <row r="21" ht="14" customHeight="1">
       <c r="B21" s="19" t="inlineStr">
@@ -3012,19 +3259,19 @@
           <t xml:space="preserve">  FREE CASH FLOW TO FIRM (FCFF)</t>
         </is>
       </c>
-      <c r="C23" s="62" t="n"/>
-      <c r="D23" s="62" t="n"/>
-      <c r="E23" s="62" t="n"/>
-      <c r="F23" s="62" t="n"/>
-      <c r="G23" s="62" t="n"/>
-      <c r="H23" s="62" t="n"/>
-      <c r="I23" s="62" t="n"/>
-      <c r="J23" s="62" t="n"/>
-      <c r="K23" s="62" t="n"/>
-      <c r="L23" s="62" t="n"/>
-      <c r="M23" s="62" t="n"/>
-      <c r="N23" s="62" t="n"/>
-      <c r="O23" s="61" t="n"/>
+      <c r="C23" s="72" t="n"/>
+      <c r="D23" s="72" t="n"/>
+      <c r="E23" s="72" t="n"/>
+      <c r="F23" s="72" t="n"/>
+      <c r="G23" s="72" t="n"/>
+      <c r="H23" s="72" t="n"/>
+      <c r="I23" s="72" t="n"/>
+      <c r="J23" s="72" t="n"/>
+      <c r="K23" s="72" t="n"/>
+      <c r="L23" s="72" t="n"/>
+      <c r="M23" s="72" t="n"/>
+      <c r="N23" s="72" t="n"/>
+      <c r="O23" s="73" t="n"/>
     </row>
     <row r="24" ht="14" customHeight="1">
       <c r="B24" s="19" t="inlineStr">
@@ -3438,19 +3685,19 @@
           <t xml:space="preserve">  10-YEAR FCF PROJECTION (from model above)</t>
         </is>
       </c>
-      <c r="C32" s="62" t="n"/>
-      <c r="D32" s="62" t="n"/>
-      <c r="E32" s="62" t="n"/>
-      <c r="F32" s="62" t="n"/>
-      <c r="G32" s="62" t="n"/>
-      <c r="H32" s="62" t="n"/>
-      <c r="I32" s="62" t="n"/>
-      <c r="J32" s="62" t="n"/>
-      <c r="K32" s="62" t="n"/>
-      <c r="L32" s="62" t="n"/>
-      <c r="M32" s="62" t="n"/>
-      <c r="N32" s="62" t="n"/>
-      <c r="O32" s="61" t="n"/>
+      <c r="C32" s="72" t="n"/>
+      <c r="D32" s="72" t="n"/>
+      <c r="E32" s="72" t="n"/>
+      <c r="F32" s="72" t="n"/>
+      <c r="G32" s="72" t="n"/>
+      <c r="H32" s="72" t="n"/>
+      <c r="I32" s="72" t="n"/>
+      <c r="J32" s="72" t="n"/>
+      <c r="K32" s="72" t="n"/>
+      <c r="L32" s="72" t="n"/>
+      <c r="M32" s="72" t="n"/>
+      <c r="N32" s="72" t="n"/>
+      <c r="O32" s="73" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -3507,9 +3754,9 @@
           <t xml:space="preserve">  COST OF EQUITY  -  CAPM:  Ke = Rf + beta x ERP</t>
         </is>
       </c>
-      <c r="C4" s="62" t="n"/>
-      <c r="D4" s="62" t="n"/>
-      <c r="E4" s="61" t="n"/>
+      <c r="C4" s="72" t="n"/>
+      <c r="D4" s="72" t="n"/>
+      <c r="E4" s="73" t="n"/>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="B5" s="18" t="inlineStr">
@@ -3548,8 +3795,8 @@
           <t xml:space="preserve">  COST OF EQUITY (Ke)</t>
         </is>
       </c>
-      <c r="C7" s="62" t="n"/>
-      <c r="D7" s="61" t="n"/>
+      <c r="C7" s="72" t="n"/>
+      <c r="D7" s="73" t="n"/>
       <c r="E7" s="40">
         <f>Assumptions!C21+Assumptions!C22*Assumptions!E21</f>
         <v/>
@@ -3561,9 +3808,9 @@
           <t xml:space="preserve">  COST OF DEBT  -  After Tax:  Kd_at = Kd x (1 - Tax Rate)</t>
         </is>
       </c>
-      <c r="C8" s="62" t="n"/>
-      <c r="D8" s="62" t="n"/>
-      <c r="E8" s="61" t="n"/>
+      <c r="C8" s="72" t="n"/>
+      <c r="D8" s="72" t="n"/>
+      <c r="E8" s="73" t="n"/>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="B9" s="18" t="inlineStr">
@@ -3591,8 +3838,8 @@
           <t xml:space="preserve">  AFTER-TAX COST OF DEBT (Kd)</t>
         </is>
       </c>
-      <c r="C10" s="62" t="n"/>
-      <c r="D10" s="61" t="n"/>
+      <c r="C10" s="72" t="n"/>
+      <c r="D10" s="73" t="n"/>
       <c r="E10" s="40">
         <f>C9*(1-E9)</f>
         <v/>
@@ -3604,9 +3851,9 @@
           <t xml:space="preserve">  CAPITAL STRUCTURE WEIGHTS</t>
         </is>
       </c>
-      <c r="C11" s="62" t="n"/>
-      <c r="D11" s="62" t="n"/>
-      <c r="E11" s="61" t="n"/>
+      <c r="C11" s="72" t="n"/>
+      <c r="D11" s="72" t="n"/>
+      <c r="E11" s="73" t="n"/>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="B12" s="18" t="inlineStr">
@@ -3654,9 +3901,9 @@
           <t xml:space="preserve">  WACC CALCULATION</t>
         </is>
       </c>
-      <c r="C14" s="62" t="n"/>
-      <c r="D14" s="62" t="n"/>
-      <c r="E14" s="61" t="n"/>
+      <c r="C14" s="72" t="n"/>
+      <c r="D14" s="72" t="n"/>
+      <c r="E14" s="73" t="n"/>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="B15" s="18" t="inlineStr">
@@ -3684,8 +3931,8 @@
           <t xml:space="preserve">  WACC  =  Ke x We  +  Kd(1-t) x Wd</t>
         </is>
       </c>
-      <c r="C16" s="62" t="n"/>
-      <c r="D16" s="61" t="n"/>
+      <c r="C16" s="72" t="n"/>
+      <c r="D16" s="73" t="n"/>
       <c r="E16" s="43">
         <f>C15+E15</f>
         <v/>
@@ -3750,9 +3997,9 @@
           <t xml:space="preserve">  DISCOUNT RATE &amp; KEY INPUTS</t>
         </is>
       </c>
-      <c r="C3" s="62" t="n"/>
-      <c r="D3" s="62" t="n"/>
-      <c r="E3" s="61" t="n"/>
+      <c r="C3" s="72" t="n"/>
+      <c r="D3" s="72" t="n"/>
+      <c r="E3" s="73" t="n"/>
     </row>
     <row r="4" ht="17" customHeight="1">
       <c r="B4" s="18" t="inlineStr">
@@ -3764,8 +4011,12 @@
         <f>WACC!E16</f>
         <v/>
       </c>
-      <c r="D4" s="22" t="inlineStr"/>
-      <c r="E4" s="22" t="inlineStr"/>
+      <c r="D4" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ke×We + Kd(1-t)×Wd  —  from WACC sheet</t>
+        </is>
+      </c>
+      <c r="E4" s="73" t="n"/>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="B5" s="18" t="inlineStr">
@@ -3777,8 +4028,12 @@
         <f>Assumptions!C26</f>
         <v/>
       </c>
-      <c r="D5" s="22" t="inlineStr"/>
-      <c r="E5" s="22" t="inlineStr"/>
+      <c r="D5" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Long-run FCF growth after Year 10  —  Assumptions</t>
+        </is>
+      </c>
+      <c r="E5" s="73" t="n"/>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="B6" s="18" t="inlineStr">
@@ -3786,12 +4041,16 @@
           <t xml:space="preserve">  Exit EBITDA Multiple</t>
         </is>
       </c>
-      <c r="C6" s="45">
+      <c r="C6" s="46">
         <f>Assumptions!E26</f>
         <v/>
       </c>
-      <c r="D6" s="22" t="inlineStr"/>
-      <c r="E6" s="22" t="inlineStr"/>
+      <c r="D6" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Reference only; Gordon Growth is primary TV method</t>
+        </is>
+      </c>
+      <c r="E6" s="73" t="n"/>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="B7" s="18" t="inlineStr">
@@ -3803,8 +4062,12 @@
         <f>Assumptions!C8-Assumptions!E8</f>
         <v/>
       </c>
-      <c r="D7" s="22" t="inlineStr"/>
-      <c r="E7" s="22" t="inlineStr"/>
+      <c r="D7" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Total Debt minus Cash  —  from Assumptions</t>
+        </is>
+      </c>
+      <c r="E7" s="73" t="n"/>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="B8" s="18" t="inlineStr">
@@ -3816,8 +4079,12 @@
         <f>Assumptions!E7</f>
         <v/>
       </c>
-      <c r="D8" s="22" t="inlineStr"/>
-      <c r="E8" s="22" t="inlineStr"/>
+      <c r="D8" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Diluted share count  —  from Assumptions</t>
+        </is>
+      </c>
+      <c r="E8" s="73" t="n"/>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="B9" s="11" t="inlineStr">
@@ -3825,9 +4092,9 @@
           <t xml:space="preserve">  PROJECTED FCF BY YEAR  (from Income Statement)</t>
         </is>
       </c>
-      <c r="C9" s="62" t="n"/>
-      <c r="D9" s="62" t="n"/>
-      <c r="E9" s="61" t="n"/>
+      <c r="C9" s="72" t="n"/>
+      <c r="D9" s="72" t="n"/>
+      <c r="E9" s="73" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
       <c r="B10" s="18" t="inlineStr">
@@ -3835,52 +4102,52 @@
           <t xml:space="preserve">  Year</t>
         </is>
       </c>
-      <c r="C10" s="46" t="inlineStr">
+      <c r="C10" s="47" t="inlineStr">
         <is>
           <t>FY2027</t>
         </is>
       </c>
-      <c r="D10" s="46" t="inlineStr">
+      <c r="D10" s="47" t="inlineStr">
         <is>
           <t>FY2028</t>
         </is>
       </c>
-      <c r="E10" s="46" t="inlineStr">
+      <c r="E10" s="47" t="inlineStr">
         <is>
           <t>FY2029</t>
         </is>
       </c>
-      <c r="F10" s="46" t="inlineStr">
+      <c r="F10" s="47" t="inlineStr">
         <is>
           <t>FY2030</t>
         </is>
       </c>
-      <c r="G10" s="46" t="inlineStr">
+      <c r="G10" s="47" t="inlineStr">
         <is>
           <t>FY2031</t>
         </is>
       </c>
-      <c r="H10" s="46" t="inlineStr">
+      <c r="H10" s="47" t="inlineStr">
         <is>
           <t>FY2032</t>
         </is>
       </c>
-      <c r="I10" s="46" t="inlineStr">
+      <c r="I10" s="47" t="inlineStr">
         <is>
           <t>FY2033</t>
         </is>
       </c>
-      <c r="J10" s="46" t="inlineStr">
+      <c r="J10" s="47" t="inlineStr">
         <is>
           <t>FY2034</t>
         </is>
       </c>
-      <c r="K10" s="46" t="inlineStr">
+      <c r="K10" s="47" t="inlineStr">
         <is>
           <t>FY2035</t>
         </is>
       </c>
-      <c r="L10" s="46" t="inlineStr">
+      <c r="L10" s="47" t="inlineStr">
         <is>
           <t>FY2036</t>
         </is>
@@ -3939,34 +4206,34 @@
           <t xml:space="preserve">  Discount Period (t)</t>
         </is>
       </c>
-      <c r="C12" s="45" t="n">
+      <c r="C12" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="45" t="n">
+      <c r="D12" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="45" t="n">
+      <c r="E12" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="F12" s="45" t="n">
+      <c r="F12" s="46" t="n">
         <v>4</v>
       </c>
-      <c r="G12" s="45" t="n">
+      <c r="G12" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="H12" s="45" t="n">
+      <c r="H12" s="46" t="n">
         <v>6</v>
       </c>
-      <c r="I12" s="45" t="n">
+      <c r="I12" s="46" t="n">
         <v>7</v>
       </c>
-      <c r="J12" s="45" t="n">
+      <c r="J12" s="46" t="n">
         <v>8</v>
       </c>
-      <c r="K12" s="45" t="n">
+      <c r="K12" s="46" t="n">
         <v>9</v>
       </c>
-      <c r="L12" s="45" t="n">
+      <c r="L12" s="46" t="n">
         <v>10</v>
       </c>
     </row>
@@ -3976,43 +4243,43 @@
           <t xml:space="preserve">  Discount Factor  [1/(1+WACC)^t]</t>
         </is>
       </c>
-      <c r="C13" s="47">
+      <c r="C13" s="48">
         <f>1/(1+C4)^C12</f>
         <v/>
       </c>
-      <c r="D13" s="47">
+      <c r="D13" s="48">
         <f>1/(1+C4)^D12</f>
         <v/>
       </c>
-      <c r="E13" s="47">
+      <c r="E13" s="48">
         <f>1/(1+C4)^E12</f>
         <v/>
       </c>
-      <c r="F13" s="47">
+      <c r="F13" s="48">
         <f>1/(1+C4)^F12</f>
         <v/>
       </c>
-      <c r="G13" s="47">
+      <c r="G13" s="48">
         <f>1/(1+C4)^G12</f>
         <v/>
       </c>
-      <c r="H13" s="47">
+      <c r="H13" s="48">
         <f>1/(1+C4)^H12</f>
         <v/>
       </c>
-      <c r="I13" s="47">
+      <c r="I13" s="48">
         <f>1/(1+C4)^I12</f>
         <v/>
       </c>
-      <c r="J13" s="47">
+      <c r="J13" s="48">
         <f>1/(1+C4)^J12</f>
         <v/>
       </c>
-      <c r="K13" s="47">
+      <c r="K13" s="48">
         <f>1/(1+C4)^K12</f>
         <v/>
       </c>
-      <c r="L13" s="47">
+      <c r="L13" s="48">
         <f>1/(1+C4)^L12</f>
         <v/>
       </c>
@@ -4081,9 +4348,9 @@
           <t xml:space="preserve">  TERMINAL VALUE</t>
         </is>
       </c>
-      <c r="C16" s="62" t="n"/>
-      <c r="D16" s="62" t="n"/>
-      <c r="E16" s="61" t="n"/>
+      <c r="C16" s="72" t="n"/>
+      <c r="D16" s="72" t="n"/>
+      <c r="E16" s="73" t="n"/>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="B17" s="18" t="inlineStr">
@@ -4131,9 +4398,9 @@
           <t xml:space="preserve">  VALUATION BRIDGE</t>
         </is>
       </c>
-      <c r="C19" s="62" t="n"/>
-      <c r="D19" s="62" t="n"/>
-      <c r="E19" s="61" t="n"/>
+      <c r="C19" s="72" t="n"/>
+      <c r="D19" s="72" t="n"/>
+      <c r="E19" s="73" t="n"/>
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="B20" s="18" t="inlineStr">
@@ -4158,12 +4425,12 @@
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="B22" s="48" t="inlineStr">
+      <c r="B22" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">  ENTERPRISE VALUE</t>
         </is>
       </c>
-      <c r="C22" s="49">
+      <c r="C22" s="50">
         <f>C20+C21</f>
         <v/>
       </c>
@@ -4180,12 +4447,12 @@
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="B24" s="48" t="inlineStr">
+      <c r="B24" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">  EQUITY VALUE</t>
         </is>
       </c>
-      <c r="C24" s="49">
+      <c r="C24" s="50">
         <f>C22-C23</f>
         <v/>
       </c>
@@ -4202,12 +4469,12 @@
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
-      <c r="B26" s="50" t="inlineStr">
+      <c r="B26" s="51" t="inlineStr">
         <is>
           <t xml:space="preserve">  IMPLIED SHARE PRICE (DCF)</t>
         </is>
       </c>
-      <c r="C26" s="51">
+      <c r="C26" s="52">
         <f>C24/C25</f>
         <v/>
       </c>
@@ -4218,7 +4485,7 @@
           <t xml:space="preserve">  Current Stock Price ($)</t>
         </is>
       </c>
-      <c r="C27" s="52">
+      <c r="C27" s="53">
         <f>Assumptions!C7</f>
         <v/>
       </c>
@@ -4229,7 +4496,7 @@
           <t xml:space="preserve">  Upside / (Downside) %</t>
         </is>
       </c>
-      <c r="C28" s="53">
+      <c r="C28" s="54">
         <f>(C26-C27)/C27</f>
         <v/>
       </c>
@@ -4240,9 +4507,9 @@
           <t xml:space="preserve">  VALUATION COMPOSITION</t>
         </is>
       </c>
-      <c r="C29" s="62" t="n"/>
-      <c r="D29" s="62" t="n"/>
-      <c r="E29" s="61" t="n"/>
+      <c r="C29" s="72" t="n"/>
+      <c r="D29" s="72" t="n"/>
+      <c r="E29" s="73" t="n"/>
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="B30" s="18" t="inlineStr">
@@ -4250,7 +4517,7 @@
           <t xml:space="preserve">  PV of FCFs as % of Enterprise Value</t>
         </is>
       </c>
-      <c r="C30" s="54">
+      <c r="C30" s="55">
         <f>IF(C22=0,0,C20/C22)</f>
         <v/>
       </c>
@@ -4261,7 +4528,7 @@
           <t xml:space="preserve">  PV of Terminal Value as % of Enterprise Value</t>
         </is>
       </c>
-      <c r="C31" s="54">
+      <c r="C31" s="55">
         <f>IF(C22=0,0,C21/C22)</f>
         <v/>
       </c>
@@ -4272,17 +4539,22 @@
           <t xml:space="preserve">  Implied EV / EBITDA Multiple (LTM)</t>
         </is>
       </c>
-      <c r="C32" s="45">
+      <c r="C32" s="46">
         <f>IF('Income Statement'!E13=0,0,C22/'Income Statement'!E13)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="11">
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D6:E6"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B1:E1"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D5:E5"/>
     <mergeCell ref="B16:E16"/>
     <mergeCell ref="B29:E29"/>
+    <mergeCell ref="D4:E4"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B19:E19"/>
   </mergeCells>
@@ -4326,494 +4598,494 @@
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="B4" s="55" t="inlineStr">
+      <c r="B4" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">  TABLE 1 - Implied Share Price  vs  WACC  x  Terminal Growth Rate</t>
         </is>
       </c>
-      <c r="C4" s="62" t="n"/>
-      <c r="D4" s="62" t="n"/>
-      <c r="E4" s="62" t="n"/>
-      <c r="F4" s="62" t="n"/>
-      <c r="G4" s="62" t="n"/>
-      <c r="H4" s="62" t="n"/>
-      <c r="I4" s="61" t="n"/>
+      <c r="C4" s="72" t="n"/>
+      <c r="D4" s="72" t="n"/>
+      <c r="E4" s="72" t="n"/>
+      <c r="F4" s="72" t="n"/>
+      <c r="G4" s="72" t="n"/>
+      <c r="H4" s="72" t="n"/>
+      <c r="I4" s="73" t="n"/>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="B5" s="56" t="inlineStr">
+      <c r="B5" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">  WACC \ TGR</t>
         </is>
       </c>
-      <c r="C5" s="57">
+      <c r="C5" s="58">
         <f>'DCF Valuation'!C5+(-0.01)</f>
         <v/>
       </c>
-      <c r="D5" s="57">
+      <c r="D5" s="58">
         <f>'DCF Valuation'!C5+(-0.005)</f>
         <v/>
       </c>
-      <c r="E5" s="57">
+      <c r="E5" s="58">
         <f>'DCF Valuation'!C5+(0.0)</f>
         <v/>
       </c>
-      <c r="F5" s="57">
+      <c r="F5" s="58">
         <f>'DCF Valuation'!C5+(0.005)</f>
         <v/>
       </c>
-      <c r="G5" s="57">
+      <c r="G5" s="58">
         <f>'DCF Valuation'!C5+(0.01)</f>
         <v/>
       </c>
-      <c r="H5" s="57">
+      <c r="H5" s="58">
         <f>'DCF Valuation'!C5+(0.015)</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="B6" s="58">
+      <c r="B6" s="59">
         <f>'DCF Valuation'!C4+(-0.015)</f>
         <v/>
       </c>
-      <c r="C6" s="52">
+      <c r="C6" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B6)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+C5)/MAX(B6-C5,0.0001)/(1+B6)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
-      <c r="D6" s="52">
+      <c r="D6" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B6)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+D5)/MAX(B6-D5,0.0001)/(1+B6)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
-      <c r="E6" s="52">
+      <c r="E6" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B6)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+E5)/MAX(B6-E5,0.0001)/(1+B6)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
-      <c r="F6" s="52">
+      <c r="F6" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B6)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+F5)/MAX(B6-F5,0.0001)/(1+B6)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
-      <c r="G6" s="52">
+      <c r="G6" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B6)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+G5)/MAX(B6-G5,0.0001)/(1+B6)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
-      <c r="H6" s="52">
+      <c r="H6" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B6)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+H5)/MAX(B6-H5,0.0001)/(1+B6)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="B7" s="58">
+      <c r="B7" s="59">
         <f>'DCF Valuation'!C4+(-0.01)</f>
         <v/>
       </c>
-      <c r="C7" s="52">
+      <c r="C7" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B7)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+C5)/MAX(B7-C5,0.0001)/(1+B7)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
-      <c r="D7" s="52">
+      <c r="D7" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B7)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+D5)/MAX(B7-D5,0.0001)/(1+B7)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
-      <c r="E7" s="52">
+      <c r="E7" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B7)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+E5)/MAX(B7-E5,0.0001)/(1+B7)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
-      <c r="F7" s="52">
+      <c r="F7" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B7)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+F5)/MAX(B7-F5,0.0001)/(1+B7)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
-      <c r="G7" s="52">
+      <c r="G7" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B7)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+G5)/MAX(B7-G5,0.0001)/(1+B7)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
-      <c r="H7" s="52">
+      <c r="H7" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B7)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+H5)/MAX(B7-H5,0.0001)/(1+B7)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="B8" s="58">
+      <c r="B8" s="59">
         <f>'DCF Valuation'!C4+(-0.005)</f>
         <v/>
       </c>
-      <c r="C8" s="52">
+      <c r="C8" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B8)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+C5)/MAX(B8-C5,0.0001)/(1+B8)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
-      <c r="D8" s="52">
+      <c r="D8" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B8)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+D5)/MAX(B8-D5,0.0001)/(1+B8)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
-      <c r="E8" s="52">
+      <c r="E8" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B8)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+E5)/MAX(B8-E5,0.0001)/(1+B8)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
-      <c r="F8" s="52">
+      <c r="F8" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B8)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+F5)/MAX(B8-F5,0.0001)/(1+B8)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
-      <c r="G8" s="52">
+      <c r="G8" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B8)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+G5)/MAX(B8-G5,0.0001)/(1+B8)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
-      <c r="H8" s="52">
+      <c r="H8" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B8)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+H5)/MAX(B8-H5,0.0001)/(1+B8)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="B9" s="58">
+      <c r="B9" s="59">
         <f>'DCF Valuation'!C4+(0.0)</f>
         <v/>
       </c>
-      <c r="C9" s="52">
+      <c r="C9" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B9)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+C5)/MAX(B9-C5,0.0001)/(1+B9)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
-      <c r="D9" s="52">
+      <c r="D9" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B9)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+D5)/MAX(B9-D5,0.0001)/(1+B9)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
-      <c r="E9" s="52">
+      <c r="E9" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B9)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+E5)/MAX(B9-E5,0.0001)/(1+B9)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
-      <c r="F9" s="52">
+      <c r="F9" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B9)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+F5)/MAX(B9-F5,0.0001)/(1+B9)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
-      <c r="G9" s="52">
+      <c r="G9" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B9)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+G5)/MAX(B9-G5,0.0001)/(1+B9)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
-      <c r="H9" s="52">
+      <c r="H9" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B9)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+H5)/MAX(B9-H5,0.0001)/(1+B9)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="B10" s="58">
+      <c r="B10" s="59">
         <f>'DCF Valuation'!C4+(0.005)</f>
         <v/>
       </c>
-      <c r="C10" s="52">
+      <c r="C10" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B10)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+C5)/MAX(B10-C5,0.0001)/(1+B10)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
-      <c r="D10" s="52">
+      <c r="D10" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B10)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+D5)/MAX(B10-D5,0.0001)/(1+B10)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
-      <c r="E10" s="52">
+      <c r="E10" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B10)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+E5)/MAX(B10-E5,0.0001)/(1+B10)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
-      <c r="F10" s="52">
+      <c r="F10" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B10)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+F5)/MAX(B10-F5,0.0001)/(1+B10)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
-      <c r="G10" s="52">
+      <c r="G10" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B10)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+G5)/MAX(B10-G5,0.0001)/(1+B10)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
-      <c r="H10" s="52">
+      <c r="H10" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B10)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+H5)/MAX(B10-H5,0.0001)/(1+B10)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="B11" s="58">
+      <c r="B11" s="59">
         <f>'DCF Valuation'!C4+(0.01)</f>
         <v/>
       </c>
-      <c r="C11" s="52">
+      <c r="C11" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B11)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+C5)/MAX(B11-C5,0.0001)/(1+B11)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
-      <c r="D11" s="52">
+      <c r="D11" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B11)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+D5)/MAX(B11-D5,0.0001)/(1+B11)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
-      <c r="E11" s="52">
+      <c r="E11" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B11)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+E5)/MAX(B11-E5,0.0001)/(1+B11)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
-      <c r="F11" s="52">
+      <c r="F11" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B11)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+F5)/MAX(B11-F5,0.0001)/(1+B11)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
-      <c r="G11" s="52">
+      <c r="G11" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B11)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+G5)/MAX(B11-G5,0.0001)/(1+B11)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
-      <c r="H11" s="52">
+      <c r="H11" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B11)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+H5)/MAX(B11-H5,0.0001)/(1+B11)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="B12" s="58">
+      <c r="B12" s="59">
         <f>'DCF Valuation'!C4+(0.015)</f>
         <v/>
       </c>
-      <c r="C12" s="52">
+      <c r="C12" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B12)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+C5)/MAX(B12-C5,0.0001)/(1+B12)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
-      <c r="D12" s="52">
+      <c r="D12" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B12)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+D5)/MAX(B12-D5,0.0001)/(1+B12)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
-      <c r="E12" s="52">
+      <c r="E12" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B12)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+E5)/MAX(B12-E5,0.0001)/(1+B12)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
-      <c r="F12" s="52">
+      <c r="F12" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B12)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+F5)/MAX(B12-F5,0.0001)/(1+B12)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
-      <c r="G12" s="52">
+      <c r="G12" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B12)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+G5)/MAX(B12-G5,0.0001)/(1+B12)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
-      <c r="H12" s="52">
+      <c r="H12" s="53">
         <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B12)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+H5)/MAX(B12-H5,0.0001)/(1+B12)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="B14" s="55" t="inlineStr">
+      <c r="B14" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">  TABLE 2 - Implied Share Price  vs  EBITDA Margin  x  Y1 Revenue Growth</t>
         </is>
       </c>
-      <c r="C14" s="62" t="n"/>
-      <c r="D14" s="62" t="n"/>
-      <c r="E14" s="62" t="n"/>
-      <c r="F14" s="62" t="n"/>
-      <c r="G14" s="62" t="n"/>
-      <c r="H14" s="61" t="n"/>
+      <c r="C14" s="72" t="n"/>
+      <c r="D14" s="72" t="n"/>
+      <c r="E14" s="72" t="n"/>
+      <c r="F14" s="72" t="n"/>
+      <c r="G14" s="72" t="n"/>
+      <c r="H14" s="73" t="n"/>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="B15" s="56" t="inlineStr">
+      <c r="B15" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">  Rev Gr\EBITDA%</t>
         </is>
       </c>
-      <c r="C15" s="59">
+      <c r="C15" s="60">
         <f>Assumptions!E16+(-0.04)</f>
         <v/>
       </c>
-      <c r="D15" s="59">
+      <c r="D15" s="60">
         <f>Assumptions!E16+(-0.02)</f>
         <v/>
       </c>
-      <c r="E15" s="59">
+      <c r="E15" s="60">
         <f>Assumptions!E16+(0.0)</f>
         <v/>
       </c>
-      <c r="F15" s="59">
+      <c r="F15" s="60">
         <f>Assumptions!E16+(0.02)</f>
         <v/>
       </c>
-      <c r="G15" s="59">
+      <c r="G15" s="60">
         <f>Assumptions!E16+(0.04)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
-      <c r="B16" s="60">
+      <c r="B16" s="61">
         <f>Assumptions!C10+(-0.03)</f>
         <v/>
       </c>
-      <c r="C16" s="52">
+      <c r="C16" s="53">
         <f>IFERROR('DCF Valuation'!C26*((1+B16)/(1+Assumptions!C10))*(C15/Assumptions!E16),"—")</f>
         <v/>
       </c>
-      <c r="D16" s="52">
+      <c r="D16" s="53">
         <f>IFERROR('DCF Valuation'!C26*((1+B16)/(1+Assumptions!C10))*(D15/Assumptions!E16),"—")</f>
         <v/>
       </c>
-      <c r="E16" s="52">
+      <c r="E16" s="53">
         <f>IFERROR('DCF Valuation'!C26*((1+B16)/(1+Assumptions!C10))*(E15/Assumptions!E16),"—")</f>
         <v/>
       </c>
-      <c r="F16" s="52">
+      <c r="F16" s="53">
         <f>IFERROR('DCF Valuation'!C26*((1+B16)/(1+Assumptions!C10))*(F15/Assumptions!E16),"—")</f>
         <v/>
       </c>
-      <c r="G16" s="52">
+      <c r="G16" s="53">
         <f>IFERROR('DCF Valuation'!C26*((1+B16)/(1+Assumptions!C10))*(G15/Assumptions!E16),"—")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
-      <c r="B17" s="60">
+      <c r="B17" s="61">
         <f>Assumptions!C10+(-0.02)</f>
         <v/>
       </c>
-      <c r="C17" s="52">
+      <c r="C17" s="53">
         <f>IFERROR('DCF Valuation'!C26*((1+B17)/(1+Assumptions!C10))*(C15/Assumptions!E16),"—")</f>
         <v/>
       </c>
-      <c r="D17" s="52">
+      <c r="D17" s="53">
         <f>IFERROR('DCF Valuation'!C26*((1+B17)/(1+Assumptions!C10))*(D15/Assumptions!E16),"—")</f>
         <v/>
       </c>
-      <c r="E17" s="52">
+      <c r="E17" s="53">
         <f>IFERROR('DCF Valuation'!C26*((1+B17)/(1+Assumptions!C10))*(E15/Assumptions!E16),"—")</f>
         <v/>
       </c>
-      <c r="F17" s="52">
+      <c r="F17" s="53">
         <f>IFERROR('DCF Valuation'!C26*((1+B17)/(1+Assumptions!C10))*(F15/Assumptions!E16),"—")</f>
         <v/>
       </c>
-      <c r="G17" s="52">
+      <c r="G17" s="53">
         <f>IFERROR('DCF Valuation'!C26*((1+B17)/(1+Assumptions!C10))*(G15/Assumptions!E16),"—")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="17" customHeight="1">
-      <c r="B18" s="60">
+      <c r="B18" s="61">
         <f>Assumptions!C10+(-0.01)</f>
         <v/>
       </c>
-      <c r="C18" s="52">
+      <c r="C18" s="53">
         <f>IFERROR('DCF Valuation'!C26*((1+B18)/(1+Assumptions!C10))*(C15/Assumptions!E16),"—")</f>
         <v/>
       </c>
-      <c r="D18" s="52">
+      <c r="D18" s="53">
         <f>IFERROR('DCF Valuation'!C26*((1+B18)/(1+Assumptions!C10))*(D15/Assumptions!E16),"—")</f>
         <v/>
       </c>
-      <c r="E18" s="52">
+      <c r="E18" s="53">
         <f>IFERROR('DCF Valuation'!C26*((1+B18)/(1+Assumptions!C10))*(E15/Assumptions!E16),"—")</f>
         <v/>
       </c>
-      <c r="F18" s="52">
+      <c r="F18" s="53">
         <f>IFERROR('DCF Valuation'!C26*((1+B18)/(1+Assumptions!C10))*(F15/Assumptions!E16),"—")</f>
         <v/>
       </c>
-      <c r="G18" s="52">
+      <c r="G18" s="53">
         <f>IFERROR('DCF Valuation'!C26*((1+B18)/(1+Assumptions!C10))*(G15/Assumptions!E16),"—")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="17" customHeight="1">
-      <c r="B19" s="60">
+      <c r="B19" s="61">
         <f>Assumptions!C10+(0.0)</f>
         <v/>
       </c>
-      <c r="C19" s="52">
+      <c r="C19" s="53">
         <f>IFERROR('DCF Valuation'!C26*((1+B19)/(1+Assumptions!C10))*(C15/Assumptions!E16),"—")</f>
         <v/>
       </c>
-      <c r="D19" s="52">
+      <c r="D19" s="53">
         <f>IFERROR('DCF Valuation'!C26*((1+B19)/(1+Assumptions!C10))*(D15/Assumptions!E16),"—")</f>
         <v/>
       </c>
-      <c r="E19" s="52">
+      <c r="E19" s="53">
         <f>IFERROR('DCF Valuation'!C26*((1+B19)/(1+Assumptions!C10))*(E15/Assumptions!E16),"—")</f>
         <v/>
       </c>
-      <c r="F19" s="52">
+      <c r="F19" s="53">
         <f>IFERROR('DCF Valuation'!C26*((1+B19)/(1+Assumptions!C10))*(F15/Assumptions!E16),"—")</f>
         <v/>
       </c>
-      <c r="G19" s="52">
+      <c r="G19" s="53">
         <f>IFERROR('DCF Valuation'!C26*((1+B19)/(1+Assumptions!C10))*(G15/Assumptions!E16),"—")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
-      <c r="B20" s="60">
+      <c r="B20" s="61">
         <f>Assumptions!C10+(0.01)</f>
         <v/>
       </c>
-      <c r="C20" s="52">
+      <c r="C20" s="53">
         <f>IFERROR('DCF Valuation'!C26*((1+B20)/(1+Assumptions!C10))*(C15/Assumptions!E16),"—")</f>
         <v/>
       </c>
-      <c r="D20" s="52">
+      <c r="D20" s="53">
         <f>IFERROR('DCF Valuation'!C26*((1+B20)/(1+Assumptions!C10))*(D15/Assumptions!E16),"—")</f>
         <v/>
       </c>
-      <c r="E20" s="52">
+      <c r="E20" s="53">
         <f>IFERROR('DCF Valuation'!C26*((1+B20)/(1+Assumptions!C10))*(E15/Assumptions!E16),"—")</f>
         <v/>
       </c>
-      <c r="F20" s="52">
+      <c r="F20" s="53">
         <f>IFERROR('DCF Valuation'!C26*((1+B20)/(1+Assumptions!C10))*(F15/Assumptions!E16),"—")</f>
         <v/>
       </c>
-      <c r="G20" s="52">
+      <c r="G20" s="53">
         <f>IFERROR('DCF Valuation'!C26*((1+B20)/(1+Assumptions!C10))*(G15/Assumptions!E16),"—")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
-      <c r="B21" s="60">
+      <c r="B21" s="61">
         <f>Assumptions!C10+(0.02)</f>
         <v/>
       </c>
-      <c r="C21" s="52">
+      <c r="C21" s="53">
         <f>IFERROR('DCF Valuation'!C26*((1+B21)/(1+Assumptions!C10))*(C15/Assumptions!E16),"—")</f>
         <v/>
       </c>
-      <c r="D21" s="52">
+      <c r="D21" s="53">
         <f>IFERROR('DCF Valuation'!C26*((1+B21)/(1+Assumptions!C10))*(D15/Assumptions!E16),"—")</f>
         <v/>
       </c>
-      <c r="E21" s="52">
+      <c r="E21" s="53">
         <f>IFERROR('DCF Valuation'!C26*((1+B21)/(1+Assumptions!C10))*(E15/Assumptions!E16),"—")</f>
         <v/>
       </c>
-      <c r="F21" s="52">
+      <c r="F21" s="53">
         <f>IFERROR('DCF Valuation'!C26*((1+B21)/(1+Assumptions!C10))*(F15/Assumptions!E16),"—")</f>
         <v/>
       </c>
-      <c r="G21" s="52">
+      <c r="G21" s="53">
         <f>IFERROR('DCF Valuation'!C26*((1+B21)/(1+Assumptions!C10))*(G15/Assumptions!E16),"—")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1">
-      <c r="B22" s="60">
+      <c r="B22" s="61">
         <f>Assumptions!C10+(0.03)</f>
         <v/>
       </c>
-      <c r="C22" s="52">
+      <c r="C22" s="53">
         <f>IFERROR('DCF Valuation'!C26*((1+B22)/(1+Assumptions!C10))*(C15/Assumptions!E16),"—")</f>
         <v/>
       </c>
-      <c r="D22" s="52">
+      <c r="D22" s="53">
         <f>IFERROR('DCF Valuation'!C26*((1+B22)/(1+Assumptions!C10))*(D15/Assumptions!E16),"—")</f>
         <v/>
       </c>
-      <c r="E22" s="52">
+      <c r="E22" s="53">
         <f>IFERROR('DCF Valuation'!C26*((1+B22)/(1+Assumptions!C10))*(E15/Assumptions!E16),"—")</f>
         <v/>
       </c>
-      <c r="F22" s="52">
+      <c r="F22" s="53">
         <f>IFERROR('DCF Valuation'!C26*((1+B22)/(1+Assumptions!C10))*(F15/Assumptions!E16),"—")</f>
         <v/>
       </c>
-      <c r="G22" s="52">
+      <c r="G22" s="53">
         <f>IFERROR('DCF Valuation'!C26*((1+B22)/(1+Assumptions!C10))*(G15/Assumptions!E16),"—")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="B24" s="55" t="inlineStr">
+      <c r="B24" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">  FOOTBALL FIELD  -  Valuation Range Summary</t>
         </is>
       </c>
-      <c r="C24" s="62" t="n"/>
-      <c r="D24" s="62" t="n"/>
-      <c r="E24" s="62" t="n"/>
-      <c r="F24" s="62" t="n"/>
-      <c r="G24" s="62" t="n"/>
-      <c r="H24" s="61" t="n"/>
+      <c r="C24" s="72" t="n"/>
+      <c r="D24" s="72" t="n"/>
+      <c r="E24" s="72" t="n"/>
+      <c r="F24" s="72" t="n"/>
+      <c r="G24" s="72" t="n"/>
+      <c r="H24" s="73" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="B25" s="31" t="inlineStr">
@@ -4848,15 +5120,15 @@
           <t xml:space="preserve">  DCF  (base case)</t>
         </is>
       </c>
-      <c r="C26" s="52">
+      <c r="C26" s="53">
         <f>'DCF Valuation'!C26</f>
         <v/>
       </c>
-      <c r="D26" s="52">
+      <c r="D26" s="53">
         <f>'DCF Valuation'!C26</f>
         <v/>
       </c>
-      <c r="E26" s="52">
+      <c r="E26" s="53">
         <f>Assumptions!C7</f>
         <v/>
       </c>
@@ -4872,15 +5144,15 @@
           <t xml:space="preserve">  DCF  (bull: FCF+15%)</t>
         </is>
       </c>
-      <c r="C27" s="52">
+      <c r="C27" s="53">
         <f>'DCF Valuation'!C26*1.12</f>
         <v/>
       </c>
-      <c r="D27" s="52">
+      <c r="D27" s="53">
         <f>'DCF Valuation'!C26*1.22</f>
         <v/>
       </c>
-      <c r="E27" s="52">
+      <c r="E27" s="53">
         <f>Assumptions!C7</f>
         <v/>
       </c>
@@ -4896,15 +5168,15 @@
           <t xml:space="preserve">  DCF  (bear: FCF-15%)</t>
         </is>
       </c>
-      <c r="C28" s="52">
+      <c r="C28" s="53">
         <f>'DCF Valuation'!C26*0.78</f>
         <v/>
       </c>
-      <c r="D28" s="52">
+      <c r="D28" s="53">
         <f>'DCF Valuation'!C26*0.90</f>
         <v/>
       </c>
-      <c r="E28" s="52">
+      <c r="E28" s="53">
         <f>Assumptions!C7</f>
         <v/>
       </c>
@@ -4920,15 +5192,15 @@
           <t xml:space="preserve">  EV/EBITDA  (18-22x LTM)</t>
         </is>
       </c>
-      <c r="C29" s="52">
+      <c r="C29" s="53">
         <f>'Income Statement'!O13*18/Assumptions!E7</f>
         <v/>
       </c>
-      <c r="D29" s="52">
+      <c r="D29" s="53">
         <f>'Income Statement'!O13*22/Assumptions!E7</f>
         <v/>
       </c>
-      <c r="E29" s="52">
+      <c r="E29" s="53">
         <f>Assumptions!C7</f>
         <v/>
       </c>
@@ -4944,15 +5216,15 @@
           <t xml:space="preserve">  Current price  (mkt)</t>
         </is>
       </c>
-      <c r="C30" s="52">
+      <c r="C30" s="53">
         <f>Assumptions!C7</f>
         <v/>
       </c>
-      <c r="D30" s="52">
+      <c r="D30" s="53">
         <f>Assumptions!C7</f>
         <v/>
       </c>
-      <c r="E30" s="52">
+      <c r="E30" s="53">
         <f>Assumptions!C7</f>
         <v/>
       </c>
@@ -4996,4 +5268,821 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0070AD47"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="B1" s="20" t="inlineStr">
+        <is>
+          <t>SCENARIO ANALYSIS  -  Bear / Base / Bull</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="13" customHeight="1">
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Edit gold cells for Bear and Bull cases. Base links from Assumptions. Implied prices auto-calculate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="C4" s="63" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+      <c r="D4" s="64" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="E4" s="65" t="inlineStr">
+        <is>
+          <t>BULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  REVENUE GROWTH</t>
+        </is>
+      </c>
+      <c r="C5" s="72" t="n"/>
+      <c r="D5" s="72" t="n"/>
+      <c r="E5" s="73" t="n"/>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Y1-Y5 Revenue Growth (avg)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D6" s="34">
+        <f>(Assumptions!C10+Assumptions!E10+Assumptions!C11+Assumptions!E11+Assumptions!C12)/5</f>
+        <v/>
+      </c>
+      <c r="E6" s="21" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Y6-Y10 Revenue Growth (avg)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D7" s="34">
+        <f>(Assumptions!E12+Assumptions!C13+Assumptions!E13+Assumptions!C14+Assumptions!E14)/5</f>
+        <v/>
+      </c>
+      <c r="E7" s="21" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  MARGIN &amp; DISCOUNT RATE</t>
+        </is>
+      </c>
+      <c r="C8" s="72" t="n"/>
+      <c r="D8" s="72" t="n"/>
+      <c r="E8" s="73" t="n"/>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EBITDA Margin %</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="D9" s="34">
+        <f>Assumptions!E16</f>
+        <v/>
+      </c>
+      <c r="E9" s="21" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FCF Margin (% of Revenue)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="D10" s="34">
+        <f>(Assumptions!E16-Assumptions!E17-Assumptions!C18+Assumptions!C19)*(1-Assumptions!E18)</f>
+        <v/>
+      </c>
+      <c r="E10" s="21" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WACC</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="D11" s="34">
+        <f>WACC!E16</f>
+        <v/>
+      </c>
+      <c r="E11" s="21" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Terminal Growth Rate</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D12" s="34">
+        <f>Assumptions!C26</f>
+        <v/>
+      </c>
+      <c r="E12" s="21" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  COMMON INPUTS  (linked from model)</t>
+        </is>
+      </c>
+      <c r="C13" s="72" t="n"/>
+      <c r="D13" s="72" t="n"/>
+      <c r="E13" s="73" t="n"/>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Base Revenue Y0 ($M)</t>
+        </is>
+      </c>
+      <c r="C14" s="15">
+        <f>Assumptions!C28</f>
+        <v/>
+      </c>
+      <c r="D14" s="15">
+        <f>Assumptions!C28</f>
+        <v/>
+      </c>
+      <c r="E14" s="15">
+        <f>Assumptions!C28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Net Debt ($M)</t>
+        </is>
+      </c>
+      <c r="C15" s="15">
+        <f>Assumptions!C8-Assumptions!E8</f>
+        <v/>
+      </c>
+      <c r="D15" s="15">
+        <f>Assumptions!C8-Assumptions!E8</f>
+        <v/>
+      </c>
+      <c r="E15" s="15">
+        <f>Assumptions!C8-Assumptions!E8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Shares Outstanding (M)</t>
+        </is>
+      </c>
+      <c r="C16" s="15">
+        <f>Assumptions!E7</f>
+        <v/>
+      </c>
+      <c r="D16" s="15">
+        <f>Assumptions!E7</f>
+        <v/>
+      </c>
+      <c r="E16" s="15">
+        <f>Assumptions!E7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  VALUATION OUTPUT</t>
+        </is>
+      </c>
+      <c r="C17" s="72" t="n"/>
+      <c r="D17" s="72" t="n"/>
+      <c r="E17" s="73" t="n"/>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="B18" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  IMPLIED SHARE PRICE</t>
+        </is>
+      </c>
+      <c r="C18" s="66">
+        <f>IFERROR((SUMPRODUCT(C14*C10*(1+C6)^{1,2,3,4,5},1/(1+C11)^{1,2,3,4,5})+SUMPRODUCT(C14*C10*(1+C6)^5*(1+C7)^{1,2,3,4,5},1/(1+C11)^{6,7,8,9,10})+C14*C10*(1+C6)^5*(1+C7)^5*(1+C12)/MAX(C11-C12,0.0001)/(1+C11)^10-C15)/C16,"--")</f>
+        <v/>
+      </c>
+      <c r="D18" s="67">
+        <f>IFERROR((SUMPRODUCT(D14*D10*(1+D6)^{1,2,3,4,5},1/(1+D11)^{1,2,3,4,5})+SUMPRODUCT(D14*D10*(1+D6)^5*(1+D7)^{1,2,3,4,5},1/(1+D11)^{6,7,8,9,10})+D14*D10*(1+D6)^5*(1+D7)^5*(1+D12)/MAX(D11-D12,0.0001)/(1+D11)^10-D15)/D16,"--")</f>
+        <v/>
+      </c>
+      <c r="E18" s="68">
+        <f>IFERROR((SUMPRODUCT(E14*E10*(1+E6)^{1,2,3,4,5},1/(1+E11)^{1,2,3,4,5})+SUMPRODUCT(E14*E10*(1+E6)^5*(1+E7)^{1,2,3,4,5},1/(1+E11)^{6,7,8,9,10})+E14*E10*(1+E6)^5*(1+E7)^5*(1+E12)/MAX(E11-E12,0.0001)/(1+E11)^10-E15)/E16,"--")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Current Market Price ($)</t>
+        </is>
+      </c>
+      <c r="C19" s="53">
+        <f>Assumptions!C7</f>
+        <v/>
+      </c>
+      <c r="D19" s="53">
+        <f>Assumptions!C7</f>
+        <v/>
+      </c>
+      <c r="E19" s="53">
+        <f>Assumptions!C7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="17" customHeight="1">
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Upside / (Downside) %</t>
+        </is>
+      </c>
+      <c r="C20" s="69">
+        <f>IFERROR((C18-D19)/D19,"--")</f>
+        <v/>
+      </c>
+      <c r="D20" s="54">
+        <f>IFERROR((D18-D19)/D19,"--")</f>
+        <v/>
+      </c>
+      <c r="E20" s="70">
+        <f>IFERROR((E18-D19)/D19,"--")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EXPECTED VALUE SUMMARY</t>
+        </is>
+      </c>
+      <c r="C22" s="72" t="n"/>
+      <c r="D22" s="72" t="n"/>
+      <c r="E22" s="73" t="n"/>
+    </row>
+    <row r="23" ht="17" customHeight="1">
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Equal-Weighted Avg Price ($)</t>
+        </is>
+      </c>
+      <c r="C23" s="71">
+        <f>IFERROR((C18+D18+E18)/3,"--")</f>
+        <v/>
+      </c>
+      <c r="D23" s="72" t="n"/>
+      <c r="E23" s="73" t="n"/>
+    </row>
+    <row r="24" ht="17" customHeight="1">
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Expected Upside / (Downside) %</t>
+        </is>
+      </c>
+      <c r="C24" s="24">
+        <f>IFERROR((C23-D19)/D19,"--")</f>
+        <v/>
+      </c>
+      <c r="D24" s="72" t="n"/>
+      <c r="E24" s="73" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="C24:E24"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00833C00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="B1" s="20" t="inlineStr">
+        <is>
+          <t>REVERSE DCF  -  Implied Growth Rate at Current Price</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="13" customHeight="1">
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Find the column where implied price = current market price. That growth rate is what the market is pricing in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="17" customHeight="1">
+      <c r="B4" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Target / Market Price ($)</t>
+        </is>
+      </c>
+      <c r="C4" s="73" t="n"/>
+      <c r="D4" s="10">
+        <f>Assumptions!C7</f>
+        <v/>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Edit D4 to test any price. Green = implied price &gt;= D4 (potential buy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17" customHeight="1">
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FCF Margin (model-derived)</t>
+        </is>
+      </c>
+      <c r="C5" s="73" t="n"/>
+      <c r="D5" s="34">
+        <f>(Assumptions!E16-Assumptions!E17-Assumptions!C18+Assumptions!C19)*(1-Assumptions!E18)</f>
+        <v/>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Flows from Assumptions — edit margins there to see impact here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Terminal Growth Rate</t>
+        </is>
+      </c>
+      <c r="C6" s="73" t="n"/>
+      <c r="D6" s="34">
+        <f>'DCF Valuation'!C5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TABLE: Implied Share Price by Uniform Revenue Growth Rate x WACC -- find where implied price = market price</t>
+        </is>
+      </c>
+      <c r="C8" s="72" t="n"/>
+      <c r="D8" s="72" t="n"/>
+      <c r="E8" s="72" t="n"/>
+      <c r="F8" s="72" t="n"/>
+      <c r="G8" s="72" t="n"/>
+      <c r="H8" s="72" t="n"/>
+      <c r="I8" s="72" t="n"/>
+      <c r="J8" s="73" t="n"/>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="B9" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WACC \ Growth</t>
+        </is>
+      </c>
+      <c r="C9" s="75" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D9" s="75" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E9" s="75" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F9" s="75" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G9" s="75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H9" s="75" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I9" s="75" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J9" s="75" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="B10" s="59">
+        <f>'DCF Valuation'!C4+(-0.015)</f>
+        <v/>
+      </c>
+      <c r="C10" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+C9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B10)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+C9)^10*(1+D6)/MAX(B10-D6,0.0001)/(1+B10)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="D10" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+D9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B10)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+D9)^10*(1+D6)/MAX(B10-D6,0.0001)/(1+B10)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="E10" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+E9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B10)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+E9)^10*(1+D6)/MAX(B10-D6,0.0001)/(1+B10)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="F10" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+F9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B10)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+F9)^10*(1+D6)/MAX(B10-D6,0.0001)/(1+B10)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="G10" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+G9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B10)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+G9)^10*(1+D6)/MAX(B10-D6,0.0001)/(1+B10)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="H10" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+H9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B10)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+H9)^10*(1+D6)/MAX(B10-D6,0.0001)/(1+B10)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="I10" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+I9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B10)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+I9)^10*(1+D6)/MAX(B10-D6,0.0001)/(1+B10)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="J10" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+J9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B10)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+J9)^10*(1+D6)/MAX(B10-D6,0.0001)/(1+B10)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="B11" s="59">
+        <f>'DCF Valuation'!C4+(-0.01)</f>
+        <v/>
+      </c>
+      <c r="C11" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+C9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B11)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+C9)^10*(1+D6)/MAX(B11-D6,0.0001)/(1+B11)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="D11" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+D9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B11)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+D9)^10*(1+D6)/MAX(B11-D6,0.0001)/(1+B11)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="E11" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+E9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B11)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+E9)^10*(1+D6)/MAX(B11-D6,0.0001)/(1+B11)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="F11" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+F9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B11)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+F9)^10*(1+D6)/MAX(B11-D6,0.0001)/(1+B11)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="G11" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+G9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B11)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+G9)^10*(1+D6)/MAX(B11-D6,0.0001)/(1+B11)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="H11" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+H9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B11)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+H9)^10*(1+D6)/MAX(B11-D6,0.0001)/(1+B11)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="I11" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+I9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B11)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+I9)^10*(1+D6)/MAX(B11-D6,0.0001)/(1+B11)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="J11" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+J9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B11)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+J9)^10*(1+D6)/MAX(B11-D6,0.0001)/(1+B11)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="B12" s="59">
+        <f>'DCF Valuation'!C4+(-0.005)</f>
+        <v/>
+      </c>
+      <c r="C12" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+C9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B12)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+C9)^10*(1+D6)/MAX(B12-D6,0.0001)/(1+B12)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="D12" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+D9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B12)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+D9)^10*(1+D6)/MAX(B12-D6,0.0001)/(1+B12)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="E12" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+E9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B12)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+E9)^10*(1+D6)/MAX(B12-D6,0.0001)/(1+B12)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="F12" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+F9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B12)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+F9)^10*(1+D6)/MAX(B12-D6,0.0001)/(1+B12)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="G12" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+G9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B12)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+G9)^10*(1+D6)/MAX(B12-D6,0.0001)/(1+B12)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="H12" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+H9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B12)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+H9)^10*(1+D6)/MAX(B12-D6,0.0001)/(1+B12)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="I12" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+I9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B12)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+I9)^10*(1+D6)/MAX(B12-D6,0.0001)/(1+B12)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="J12" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+J9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B12)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+J9)^10*(1+D6)/MAX(B12-D6,0.0001)/(1+B12)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="B13" s="59">
+        <f>'DCF Valuation'!C4+(0.0)</f>
+        <v/>
+      </c>
+      <c r="C13" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+C9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B13)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+C9)^10*(1+D6)/MAX(B13-D6,0.0001)/(1+B13)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="D13" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+D9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B13)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+D9)^10*(1+D6)/MAX(B13-D6,0.0001)/(1+B13)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="E13" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+E9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B13)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+E9)^10*(1+D6)/MAX(B13-D6,0.0001)/(1+B13)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="F13" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+F9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B13)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+F9)^10*(1+D6)/MAX(B13-D6,0.0001)/(1+B13)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="G13" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+G9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B13)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+G9)^10*(1+D6)/MAX(B13-D6,0.0001)/(1+B13)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="H13" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+H9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B13)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+H9)^10*(1+D6)/MAX(B13-D6,0.0001)/(1+B13)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="I13" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+I9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B13)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+I9)^10*(1+D6)/MAX(B13-D6,0.0001)/(1+B13)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="J13" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+J9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B13)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+J9)^10*(1+D6)/MAX(B13-D6,0.0001)/(1+B13)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="B14" s="59">
+        <f>'DCF Valuation'!C4+(0.005)</f>
+        <v/>
+      </c>
+      <c r="C14" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+C9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B14)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+C9)^10*(1+D6)/MAX(B14-D6,0.0001)/(1+B14)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="D14" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+D9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B14)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+D9)^10*(1+D6)/MAX(B14-D6,0.0001)/(1+B14)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="E14" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+E9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B14)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+E9)^10*(1+D6)/MAX(B14-D6,0.0001)/(1+B14)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="F14" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+F9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B14)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+F9)^10*(1+D6)/MAX(B14-D6,0.0001)/(1+B14)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="G14" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+G9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B14)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+G9)^10*(1+D6)/MAX(B14-D6,0.0001)/(1+B14)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="H14" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+H9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B14)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+H9)^10*(1+D6)/MAX(B14-D6,0.0001)/(1+B14)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="I14" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+I9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B14)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+I9)^10*(1+D6)/MAX(B14-D6,0.0001)/(1+B14)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="J14" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+J9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B14)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+J9)^10*(1+D6)/MAX(B14-D6,0.0001)/(1+B14)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="B15" s="59">
+        <f>'DCF Valuation'!C4+(0.01)</f>
+        <v/>
+      </c>
+      <c r="C15" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+C9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B15)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+C9)^10*(1+D6)/MAX(B15-D6,0.0001)/(1+B15)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="D15" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+D9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B15)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+D9)^10*(1+D6)/MAX(B15-D6,0.0001)/(1+B15)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="E15" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+E9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B15)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+E9)^10*(1+D6)/MAX(B15-D6,0.0001)/(1+B15)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="F15" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+F9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B15)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+F9)^10*(1+D6)/MAX(B15-D6,0.0001)/(1+B15)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="G15" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+G9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B15)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+G9)^10*(1+D6)/MAX(B15-D6,0.0001)/(1+B15)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="H15" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+H9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B15)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+H9)^10*(1+D6)/MAX(B15-D6,0.0001)/(1+B15)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="I15" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+I9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B15)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+I9)^10*(1+D6)/MAX(B15-D6,0.0001)/(1+B15)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="J15" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+J9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B15)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+J9)^10*(1+D6)/MAX(B15-D6,0.0001)/(1+B15)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="B16" s="59">
+        <f>'DCF Valuation'!C4+(0.015)</f>
+        <v/>
+      </c>
+      <c r="C16" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+C9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B16)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+C9)^10*(1+D6)/MAX(B16-D6,0.0001)/(1+B16)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="D16" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+D9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B16)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+D9)^10*(1+D6)/MAX(B16-D6,0.0001)/(1+B16)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="E16" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+E9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B16)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+E9)^10*(1+D6)/MAX(B16-D6,0.0001)/(1+B16)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="F16" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+F9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B16)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+F9)^10*(1+D6)/MAX(B16-D6,0.0001)/(1+B16)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="G16" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+G9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B16)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+G9)^10*(1+D6)/MAX(B16-D6,0.0001)/(1+B16)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="H16" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+H9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B16)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+H9)^10*(1+D6)/MAX(B16-D6,0.0001)/(1+B16)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="I16" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+I9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B16)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+I9)^10*(1+D6)/MAX(B16-D6,0.0001)/(1+B16)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="J16" s="53">
+        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+J9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B16)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+J9)^10*(1+D6)/MAX(B16-D6,0.0001)/(1+B16)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="14" customHeight="1">
+      <c r="B18" s="76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  HOW TO READ: Find your WACC row (0.00% offset = model WACC). Scan right to find where implied price matches market price. That column = market-implied growth rate.</t>
+        </is>
+      </c>
+      <c r="C18" s="72" t="n"/>
+      <c r="D18" s="72" t="n"/>
+      <c r="E18" s="72" t="n"/>
+      <c r="F18" s="72" t="n"/>
+      <c r="G18" s="72" t="n"/>
+      <c r="H18" s="72" t="n"/>
+      <c r="I18" s="72" t="n"/>
+      <c r="J18" s="72" t="n"/>
+      <c r="K18" s="73" t="n"/>
+    </row>
+    <row r="19" ht="14" customHeight="1">
+      <c r="B19" s="76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  This uses a UNIFORM growth rate for all 10 years. For two-phase growth analysis, see the Scenarios sheet.</t>
+        </is>
+      </c>
+      <c r="C19" s="72" t="n"/>
+      <c r="D19" s="72" t="n"/>
+      <c r="E19" s="72" t="n"/>
+      <c r="F19" s="72" t="n"/>
+      <c r="G19" s="72" t="n"/>
+      <c r="H19" s="72" t="n"/>
+      <c r="I19" s="72" t="n"/>
+      <c r="J19" s="72" t="n"/>
+      <c r="K19" s="73" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="E5:K5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B1:K1"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B18:K18"/>
+    <mergeCell ref="E4:K4"/>
+    <mergeCell ref="B8:J8"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B19:K19"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C10:J16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00FFC7CE"/>
+        <color rgb="00FFEB9C"/>
+        <color rgb="00C6EFCE"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/DCF_Model_Sample.xlsx
+++ b/DCF_Model_Sample.xlsx
@@ -25,13 +25,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0##"/>
+    <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="169" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -114,6 +116,12 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00404040"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -284,7 +292,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -350,6 +358,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -357,7 +368,13 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -376,16 +393,13 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -394,10 +408,13 @@
     <xf numFmtId="2" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -409,25 +426,25 @@
     <xf numFmtId="10" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -448,7 +465,7 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -466,13 +483,13 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1015,7 +1032,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Built 2026-06-02  |  Gold cells = inputs  |  White cells = formulas</t>
+          <t xml:space="preserve">  Built 2026-06-14  |  Gold cells = inputs  |  White cells = formulas</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1042,7 @@
           <t xml:space="preserve">  [Stock Search]  One command to build and populate — pick your stock and date:</t>
         </is>
       </c>
-      <c r="C4" s="73" t="n"/>
+      <c r="C4" s="76" t="n"/>
     </row>
     <row r="5" ht="13" customHeight="1">
       <c r="B5" s="4" t="inlineStr">
@@ -1033,7 +1050,7 @@
           <t xml:space="preserve">         python build_dcf.py AAPL                     (live data)</t>
         </is>
       </c>
-      <c r="C5" s="73" t="n"/>
+      <c r="C5" s="76" t="n"/>
     </row>
     <row r="6" ht="13" customHeight="1">
       <c r="B6" s="4" t="inlineStr">
@@ -1041,7 +1058,7 @@
           <t xml:space="preserve">         python build_dcf.py AAPL --date 2020-03-23   (COVID crash low)</t>
         </is>
       </c>
-      <c r="C6" s="73" t="n"/>
+      <c r="C6" s="76" t="n"/>
     </row>
     <row r="7" ht="13" customHeight="1">
       <c r="B7" s="4" t="inlineStr">
@@ -1049,7 +1066,7 @@
           <t xml:space="preserve">         python build_dcf.py AAPL --date 2008         (financial crisis)</t>
         </is>
       </c>
-      <c r="C7" s="73" t="n"/>
+      <c r="C7" s="76" t="n"/>
     </row>
     <row r="8" ht="13" customHeight="1">
       <c r="B8" s="4" t="inlineStr">
@@ -1057,7 +1074,7 @@
           <t xml:space="preserve">       Microsoft 365: select B5 then Data &gt; Stocks to link live data.</t>
         </is>
       </c>
-      <c r="C8" s="73" t="n"/>
+      <c r="C8" s="76" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="B9" s="5" t="inlineStr">
@@ -1065,7 +1082,7 @@
           <t xml:space="preserve">  [Assumptions]  Edit all gold cells. Revenue growth, margins, WACC inputs, terminal value.</t>
         </is>
       </c>
-      <c r="C9" s="73" t="n"/>
+      <c r="C9" s="76" t="n"/>
     </row>
     <row r="10" ht="13" customHeight="1">
       <c r="B10" s="4" t="inlineStr">
@@ -1073,7 +1090,7 @@
           <t xml:space="preserve">       To refresh data only:  python update_dcf.py AAPL  (keeps your thesis intact)</t>
         </is>
       </c>
-      <c r="C10" s="73" t="n"/>
+      <c r="C10" s="76" t="n"/>
     </row>
     <row r="11" ht="14" customHeight="1">
       <c r="B11" s="5" t="inlineStr">
@@ -1081,7 +1098,7 @@
           <t xml:space="preserve">  [Income Statement]  Historical (grey) + 10-year projection. FCF computed automatically.</t>
         </is>
       </c>
-      <c r="C11" s="73" t="n"/>
+      <c r="C11" s="76" t="n"/>
     </row>
     <row r="12" ht="14" customHeight="1">
       <c r="B12" s="5" t="inlineStr">
@@ -1089,7 +1106,7 @@
           <t xml:space="preserve">  [WACC]  Cost of equity (CAPM), cost of debt, capital structure -&gt; WACC.</t>
         </is>
       </c>
-      <c r="C12" s="73" t="n"/>
+      <c r="C12" s="76" t="n"/>
     </row>
     <row r="13" ht="14" customHeight="1">
       <c r="B13" s="5" t="inlineStr">
@@ -1097,7 +1114,7 @@
           <t xml:space="preserve">  [DCF Valuation]  Discounted FCFs + terminal value -&gt; Enterprise Value -&gt; Implied Price.</t>
         </is>
       </c>
-      <c r="C13" s="73" t="n"/>
+      <c r="C13" s="76" t="n"/>
     </row>
     <row r="14" ht="14" customHeight="1">
       <c r="B14" s="5" t="inlineStr">
@@ -1105,7 +1122,7 @@
           <t xml:space="preserve">  [Sensitivity]  Implied price vs WACC x terminal growth rate. Green = upside.</t>
         </is>
       </c>
-      <c r="C14" s="73" t="n"/>
+      <c r="C14" s="76" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -1164,9 +1181,9 @@
           <t xml:space="preserve">  COMPANY</t>
         </is>
       </c>
-      <c r="C4" s="72" t="n"/>
-      <c r="D4" s="72" t="n"/>
-      <c r="E4" s="73" t="n"/>
+      <c r="C4" s="75" t="n"/>
+      <c r="D4" s="75" t="n"/>
+      <c r="E4" s="76" t="n"/>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="B5" s="18" t="inlineStr">
@@ -1174,7 +1191,7 @@
           <t xml:space="preserve">  Ticker</t>
         </is>
       </c>
-      <c r="C5" s="41">
+      <c r="C5" s="44">
         <f>'Stock Search'!B5</f>
         <v/>
       </c>
@@ -1183,7 +1200,7 @@
           <t xml:space="preserve">  Company</t>
         </is>
       </c>
-      <c r="E5" s="41">
+      <c r="E5" s="44">
         <f>'Stock Search'!D5</f>
         <v/>
       </c>
@@ -1194,7 +1211,7 @@
           <t xml:space="preserve">  Beta (1-yr vs S&amp;P 500)</t>
         </is>
       </c>
-      <c r="C6" s="38">
+      <c r="C6" s="40">
         <f>Assumptions!C22</f>
         <v/>
       </c>
@@ -1203,7 +1220,7 @@
           <t xml:space="preserve">  Last Updated</t>
         </is>
       </c>
-      <c r="E6" s="41">
+      <c r="E6" s="44">
         <f>TEXT('Stock Search'!E5,"YYYY-MM-DD")</f>
         <v/>
       </c>
@@ -1214,46 +1231,46 @@
           <t xml:space="preserve">  SESSION PRICES  (refreshed by update_dcf.py)</t>
         </is>
       </c>
-      <c r="C7" s="72" t="n"/>
-      <c r="D7" s="72" t="n"/>
-      <c r="E7" s="73" t="n"/>
+      <c r="C7" s="75" t="n"/>
+      <c r="D7" s="75" t="n"/>
+      <c r="E7" s="76" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  Open ($)</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>309.63</v>
-      </c>
-      <c r="D8" s="23" t="inlineStr">
+        <v>391.42</v>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  Market Status</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>HISTORICAL</t>
+          <t>CLOSED</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  Current ($)</t>
         </is>
       </c>
-      <c r="C9" s="71">
+      <c r="C9" s="74">
         <f>'Stock Search'!C5</f>
         <v/>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  Change from Open ($)</t>
         </is>
       </c>
-      <c r="E9" s="71">
+      <c r="E9" s="74">
         <f>'Stock Search'!C5-C8</f>
         <v/>
       </c>
@@ -1265,7 +1282,7 @@
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>310.94</v>
+        <v>391.74</v>
       </c>
       <c r="D10" s="18" t="inlineStr">
         <is>
@@ -1273,25 +1290,25 @@
         </is>
       </c>
       <c r="E10" s="10" t="n">
-        <v>305.02</v>
+        <v>382.27</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  Change from Open (%)</t>
         </is>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="25">
         <f>IF(C8=0,0,('Stock Search'!C5-C8)/C8)</f>
         <v/>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  High-Low Range ($)</t>
         </is>
       </c>
-      <c r="E11" s="71">
+      <c r="E11" s="74">
         <f>C10-E10</f>
         <v/>
       </c>
@@ -1302,9 +1319,9 @@
           <t xml:space="preserve">  52-WEEK RANGE</t>
         </is>
       </c>
-      <c r="C12" s="72" t="n"/>
-      <c r="D12" s="72" t="n"/>
-      <c r="E12" s="73" t="n"/>
+      <c r="C12" s="75" t="n"/>
+      <c r="D12" s="75" t="n"/>
+      <c r="E12" s="76" t="n"/>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="B13" s="18" t="inlineStr">
@@ -1312,7 +1329,7 @@
           <t xml:space="preserve">  52-Week High ($)</t>
         </is>
       </c>
-      <c r="C13" s="53">
+      <c r="C13" s="56">
         <f>'Stock Search'!D8</f>
         <v/>
       </c>
@@ -1321,7 +1338,7 @@
           <t xml:space="preserve">  52-Week Low ($)</t>
         </is>
       </c>
-      <c r="E13" s="53">
+      <c r="E13" s="56">
         <f>'Stock Search'!E8</f>
         <v/>
       </c>
@@ -1332,7 +1349,7 @@
           <t xml:space="preserve">  vs 52-Week High</t>
         </is>
       </c>
-      <c r="C14" s="34">
+      <c r="C14" s="23">
         <f>IF(C13=0,0,('Stock Search'!C5-C13)/C13)</f>
         <v/>
       </c>
@@ -1341,7 +1358,7 @@
           <t xml:space="preserve">  vs 52-Week Low</t>
         </is>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="23">
         <f>IF(E13=0,0,('Stock Search'!C5-E13)/E13)</f>
         <v/>
       </c>
@@ -1352,12 +1369,12 @@
           <t xml:space="preserve">  52-Week Percentile  (100% = at 52W high)</t>
         </is>
       </c>
-      <c r="C15" s="55">
+      <c r="C15" s="58">
         <f>IFERROR(('Stock Search'!C5-E13)/(C13-E13),0)</f>
         <v/>
       </c>
-      <c r="D15" s="72" t="n"/>
-      <c r="E15" s="73" t="n"/>
+      <c r="D15" s="75" t="n"/>
+      <c r="E15" s="76" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="B16" s="11" t="inlineStr">
@@ -1365,9 +1382,9 @@
           <t xml:space="preserve">  BETA-ADJUSTED PERFORMANCE  (vs S&amp;P 500 today)</t>
         </is>
       </c>
-      <c r="C16" s="72" t="n"/>
-      <c r="D16" s="72" t="n"/>
-      <c r="E16" s="73" t="n"/>
+      <c r="C16" s="75" t="n"/>
+      <c r="D16" s="75" t="n"/>
+      <c r="E16" s="76" t="n"/>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="B17" s="18" t="inlineStr">
@@ -1376,7 +1393,7 @@
         </is>
       </c>
       <c r="C17" s="21" t="n">
-        <v>0.0023</v>
+        <v>0.0028</v>
       </c>
       <c r="D17" s="18" t="inlineStr">
         <is>
@@ -1391,7 +1408,7 @@
           <t xml:space="preserve">  Expected Move  (Beta x S&amp;P move)</t>
         </is>
       </c>
-      <c r="C18" s="34">
+      <c r="C18" s="23">
         <f>Assumptions!C22*C17</f>
         <v/>
       </c>
@@ -1400,33 +1417,33 @@
           <t xml:space="preserve">  Actual Move (vs open)</t>
         </is>
       </c>
-      <c r="E18" s="34">
+      <c r="E18" s="23">
         <f>C11</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  Alpha Today  (actual - expected)</t>
         </is>
       </c>
-      <c r="C19" s="24">
+      <c r="C19" s="25">
         <f>C11-Assumptions!C22*C17</f>
         <v/>
       </c>
-      <c r="D19" s="72" t="n"/>
-      <c r="E19" s="73" t="n"/>
+      <c r="D19" s="75" t="n"/>
+      <c r="E19" s="76" t="n"/>
     </row>
     <row r="20" ht="14" customHeight="1">
-      <c r="B20" s="45" t="inlineStr">
+      <c r="B20" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">  Alpha = actual stock move minus CAPM-predicted move (beta x market). Positive alpha = stock outperformed its risk-adjusted expectation today.</t>
         </is>
       </c>
-      <c r="C20" s="72" t="n"/>
-      <c r="D20" s="72" t="n"/>
-      <c r="E20" s="73" t="n"/>
+      <c r="C20" s="75" t="n"/>
+      <c r="D20" s="75" t="n"/>
+      <c r="E20" s="76" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -1500,20 +1517,20 @@
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>306.31</v>
+        <v>390.34</v>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>2026-06-01 (historical)</t>
+          <t>2026-06-14</t>
         </is>
       </c>
     </row>
@@ -1523,9 +1540,9 @@
           <t xml:space="preserve">  PRICE &amp; RANGE</t>
         </is>
       </c>
-      <c r="C7" s="72" t="n"/>
-      <c r="D7" s="72" t="n"/>
-      <c r="E7" s="73" t="n"/>
+      <c r="C7" s="75" t="n"/>
+      <c r="D7" s="75" t="n"/>
+      <c r="E7" s="76" t="n"/>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="B8" s="12" t="inlineStr">
@@ -1534,13 +1551,13 @@
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>306.31</v>
+        <v>390.34</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>315</v>
+        <v>551.05</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>194.3</v>
+        <v>355.51</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
@@ -1549,9 +1566,9 @@
           <t xml:space="preserve">  SHARES &amp; MARKET CAP</t>
         </is>
       </c>
-      <c r="C9" s="72" t="n"/>
-      <c r="D9" s="72" t="n"/>
-      <c r="E9" s="73" t="n"/>
+      <c r="C9" s="75" t="n"/>
+      <c r="D9" s="75" t="n"/>
+      <c r="E9" s="76" t="n"/>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="B10" s="12" t="inlineStr">
@@ -1560,13 +1577,13 @@
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>4498884</v>
+        <v>2902586.6</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>14687.4</v>
+        <v>7428.4</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>0.99</v>
+        <v>0.9985000000000001</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
@@ -1575,9 +1592,9 @@
           <t xml:space="preserve">  INCOME (TTM, $M)</t>
         </is>
       </c>
-      <c r="C11" s="72" t="n"/>
-      <c r="D11" s="72" t="n"/>
-      <c r="E11" s="73" t="n"/>
+      <c r="C11" s="75" t="n"/>
+      <c r="D11" s="75" t="n"/>
+      <c r="E11" s="76" t="n"/>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="B12" s="12" t="inlineStr">
@@ -1586,13 +1603,13 @@
         </is>
       </c>
       <c r="C12" s="13" t="n">
-        <v>416161</v>
+        <v>318273</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>144748</v>
+        <v>184457</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>112010</v>
+        <v>125216</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
@@ -1601,9 +1618,9 @@
           <t xml:space="preserve">  BALANCE SHEET ($M)</t>
         </is>
       </c>
-      <c r="C13" s="72" t="n"/>
-      <c r="D13" s="72" t="n"/>
-      <c r="E13" s="73" t="n"/>
+      <c r="C13" s="75" t="n"/>
+      <c r="D13" s="75" t="n"/>
+      <c r="E13" s="76" t="n"/>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="B14" s="12" t="inlineStr">
@@ -1612,10 +1629,10 @@
         </is>
       </c>
       <c r="C14" s="13" t="n">
-        <v>98657</v>
+        <v>125432</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>35934</v>
+        <v>78228</v>
       </c>
       <c r="E14" s="15">
         <f>C16-D16</f>
@@ -1628,9 +1645,9 @@
           <t xml:space="preserve">  VALUATION</t>
         </is>
       </c>
-      <c r="C15" s="72" t="n"/>
-      <c r="D15" s="72" t="n"/>
-      <c r="E15" s="73" t="n"/>
+      <c r="C15" s="75" t="n"/>
+      <c r="D15" s="75" t="n"/>
+      <c r="E15" s="76" t="n"/>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="B16" s="12" t="inlineStr">
@@ -1639,13 +1656,13 @@
         </is>
       </c>
       <c r="C16" s="16" t="n">
-        <v>40.2</v>
+        <v>23.3</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>31.5</v>
+        <v>16</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
@@ -1654,9 +1671,9 @@
           <t xml:space="preserve">  MICROSOFT 365 STOCKS DATA TYPE - INSTRUCTIONS</t>
         </is>
       </c>
-      <c r="C18" s="72" t="n"/>
-      <c r="D18" s="72" t="n"/>
-      <c r="E18" s="73" t="n"/>
+      <c r="C18" s="75" t="n"/>
+      <c r="D18" s="75" t="n"/>
+      <c r="E18" s="76" t="n"/>
     </row>
     <row r="19" ht="13" customHeight="1">
       <c r="B19" s="18" t="inlineStr">
@@ -1664,9 +1681,9 @@
           <t xml:space="preserve">  1. Type ticker in B5  (e.g. AAPL, MSFT, GOOGL, NVDA)</t>
         </is>
       </c>
-      <c r="C19" s="72" t="n"/>
-      <c r="D19" s="72" t="n"/>
-      <c r="E19" s="73" t="n"/>
+      <c r="C19" s="75" t="n"/>
+      <c r="D19" s="75" t="n"/>
+      <c r="E19" s="76" t="n"/>
     </row>
     <row r="20" ht="13" customHeight="1">
       <c r="B20" s="18" t="inlineStr">
@@ -1674,9 +1691,9 @@
           <t xml:space="preserve">  2. With B5 selected: click  Data  tab  &gt;  Stocks  button in ribbon</t>
         </is>
       </c>
-      <c r="C20" s="72" t="n"/>
-      <c r="D20" s="72" t="n"/>
-      <c r="E20" s="73" t="n"/>
+      <c r="C20" s="75" t="n"/>
+      <c r="D20" s="75" t="n"/>
+      <c r="E20" s="76" t="n"/>
     </row>
     <row r="21" ht="13" customHeight="1">
       <c r="B21" s="18" t="inlineStr">
@@ -1684,9 +1701,9 @@
           <t xml:space="preserve">  3. Excel converts the text to a linked Stocks data type (shows stock icon)</t>
         </is>
       </c>
-      <c r="C21" s="72" t="n"/>
-      <c r="D21" s="72" t="n"/>
-      <c r="E21" s="73" t="n"/>
+      <c r="C21" s="75" t="n"/>
+      <c r="D21" s="75" t="n"/>
+      <c r="E21" s="76" t="n"/>
     </row>
     <row r="22" ht="13" customHeight="1">
       <c r="B22" s="18" t="inlineStr">
@@ -1694,9 +1711,9 @@
           <t xml:space="preserve">  4. Click the icon to browse available fields, or type  =B5.Price  to extract any field</t>
         </is>
       </c>
-      <c r="C22" s="72" t="n"/>
-      <c r="D22" s="72" t="n"/>
-      <c r="E22" s="73" t="n"/>
+      <c r="C22" s="75" t="n"/>
+      <c r="D22" s="75" t="n"/>
+      <c r="E22" s="76" t="n"/>
     </row>
     <row r="23" ht="13" customHeight="1">
       <c r="B23" s="18" t="inlineStr">
@@ -1704,9 +1721,9 @@
           <t xml:space="preserve">  5. STOCKHISTORY(B5, start_date, end_date)  returns historical price table</t>
         </is>
       </c>
-      <c r="C23" s="72" t="n"/>
-      <c r="D23" s="72" t="n"/>
-      <c r="E23" s="73" t="n"/>
+      <c r="C23" s="75" t="n"/>
+      <c r="D23" s="75" t="n"/>
+      <c r="E23" s="76" t="n"/>
     </row>
     <row r="24" ht="13" customHeight="1">
       <c r="B24" s="18" t="inlineStr">
@@ -1714,9 +1731,9 @@
           <t xml:space="preserve">  </t>
         </is>
       </c>
-      <c r="C24" s="72" t="n"/>
-      <c r="D24" s="72" t="n"/>
-      <c r="E24" s="73" t="n"/>
+      <c r="C24" s="75" t="n"/>
+      <c r="D24" s="75" t="n"/>
+      <c r="E24" s="76" t="n"/>
     </row>
     <row r="25" ht="13" customHeight="1">
       <c r="B25" s="5" t="inlineStr">
@@ -1724,9 +1741,9 @@
           <t xml:space="preserve">  PYTHON AUTO-FILL (works with any Excel version):</t>
         </is>
       </c>
-      <c r="C25" s="72" t="n"/>
-      <c r="D25" s="72" t="n"/>
-      <c r="E25" s="73" t="n"/>
+      <c r="C25" s="75" t="n"/>
+      <c r="D25" s="75" t="n"/>
+      <c r="E25" s="76" t="n"/>
     </row>
     <row r="26" ht="13" customHeight="1">
       <c r="B26" s="19" t="inlineStr">
@@ -1734,9 +1751,9 @@
           <t xml:space="preserve">     pip install yfinance openpyxl</t>
         </is>
       </c>
-      <c r="C26" s="72" t="n"/>
-      <c r="D26" s="72" t="n"/>
-      <c r="E26" s="73" t="n"/>
+      <c r="C26" s="75" t="n"/>
+      <c r="D26" s="75" t="n"/>
+      <c r="E26" s="76" t="n"/>
     </row>
     <row r="27" ht="13" customHeight="1">
       <c r="B27" s="19" t="inlineStr">
@@ -1744,9 +1761,9 @@
           <t xml:space="preserve">     python update_dcf.py AAPL</t>
         </is>
       </c>
-      <c r="C27" s="72" t="n"/>
-      <c r="D27" s="72" t="n"/>
-      <c r="E27" s="73" t="n"/>
+      <c r="C27" s="75" t="n"/>
+      <c r="D27" s="75" t="n"/>
+      <c r="E27" s="76" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -1784,7 +1801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E34"/>
+  <dimension ref="B1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1814,9 +1831,9 @@
           <t xml:space="preserve">  COMPANY</t>
         </is>
       </c>
-      <c r="C4" s="72" t="n"/>
-      <c r="D4" s="72" t="n"/>
-      <c r="E4" s="73" t="n"/>
+      <c r="C4" s="75" t="n"/>
+      <c r="D4" s="75" t="n"/>
+      <c r="E4" s="76" t="n"/>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="B5" s="18" t="inlineStr">
@@ -1826,7 +1843,7 @@
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="D5" s="18" t="inlineStr">
@@ -1836,7 +1853,7 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>MSFT</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1886,7 @@
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>306.31</v>
+        <v>390.34</v>
       </c>
       <c r="D7" s="18" t="inlineStr">
         <is>
@@ -1877,7 +1894,7 @@
         </is>
       </c>
       <c r="E7" s="13" t="n">
-        <v>14687.4</v>
+        <v>7428.4</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
@@ -1887,7 +1904,7 @@
         </is>
       </c>
       <c r="C8" s="13" t="n">
-        <v>98657</v>
+        <v>125432</v>
       </c>
       <c r="D8" s="18" t="inlineStr">
         <is>
@@ -1895,7 +1912,7 @@
         </is>
       </c>
       <c r="E8" s="13" t="n">
-        <v>35934</v>
+        <v>78228</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
@@ -1904,9 +1921,9 @@
           <t xml:space="preserve">  REVENUE GROWTH  (10-year projection ramp)</t>
         </is>
       </c>
-      <c r="C9" s="72" t="n"/>
-      <c r="D9" s="72" t="n"/>
-      <c r="E9" s="73" t="n"/>
+      <c r="C9" s="75" t="n"/>
+      <c r="D9" s="75" t="n"/>
+      <c r="E9" s="76" t="n"/>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="B10" s="18" t="inlineStr">
@@ -1915,7 +1932,7 @@
         </is>
       </c>
       <c r="C10" s="21" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2182</v>
       </c>
       <c r="D10" s="18" t="inlineStr">
         <is>
@@ -1923,7 +1940,7 @@
         </is>
       </c>
       <c r="E10" s="21" t="n">
-        <v>0.065</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
@@ -1933,7 +1950,7 @@
         </is>
       </c>
       <c r="C11" s="21" t="n">
-        <v>0.06</v>
+        <v>0.1633</v>
       </c>
       <c r="D11" s="18" t="inlineStr">
         <is>
@@ -1941,7 +1958,7 @@
         </is>
       </c>
       <c r="E11" s="21" t="n">
-        <v>0.055</v>
+        <v>0.1382</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
@@ -1951,7 +1968,7 @@
         </is>
       </c>
       <c r="C12" s="21" t="n">
-        <v>0.05</v>
+        <v>0.1148</v>
       </c>
       <c r="D12" s="18" t="inlineStr">
         <is>
@@ -1959,7 +1976,7 @@
         </is>
       </c>
       <c r="E12" s="21" t="n">
-        <v>0.045</v>
+        <v>0.09329999999999999</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -1969,7 +1986,7 @@
         </is>
       </c>
       <c r="C13" s="21" t="n">
-        <v>0.04</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="D13" s="18" t="inlineStr">
         <is>
@@ -1977,7 +1994,7 @@
         </is>
       </c>
       <c r="E13" s="21" t="n">
-        <v>0.035</v>
+        <v>0.0568</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -1987,7 +2004,7 @@
         </is>
       </c>
       <c r="C14" s="21" t="n">
-        <v>0.03</v>
+        <v>0.0423</v>
       </c>
       <c r="D14" s="18" t="inlineStr">
         <is>
@@ -1995,18 +2012,18 @@
         </is>
       </c>
       <c r="E14" s="21" t="n">
-        <v>0.03</v>
+        <v>0.0311</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  MARGIN ASSUMPTIONS</t>
-        </is>
-      </c>
-      <c r="C15" s="72" t="n"/>
-      <c r="D15" s="72" t="n"/>
-      <c r="E15" s="73" t="n"/>
+          <t xml:space="preserve">  MARGIN ASSUMPTIONS  ·  NWC source: Damodaran wcdata.html — pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/wcdata.html  (sector-specific benchmark auto-applied by update_dcf.py)</t>
+        </is>
+      </c>
+      <c r="C15" s="75" t="n"/>
+      <c r="D15" s="75" t="n"/>
+      <c r="E15" s="76" t="n"/>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="B16" s="18" t="inlineStr">
@@ -2015,7 +2032,7 @@
         </is>
       </c>
       <c r="C16" s="21" t="n">
-        <v>0.435</v>
+        <v>0.6092</v>
       </c>
       <c r="D16" s="18" t="inlineStr">
         <is>
@@ -2023,7 +2040,7 @@
         </is>
       </c>
       <c r="E16" s="21" t="n">
-        <v>0.335</v>
+        <v>0.5796</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -2033,7 +2050,7 @@
         </is>
       </c>
       <c r="C17" s="21" t="n">
-        <v>0.025</v>
+        <v>0.1073</v>
       </c>
       <c r="D17" s="18" t="inlineStr">
         <is>
@@ -2041,7 +2058,7 @@
         </is>
       </c>
       <c r="E17" s="21" t="n">
-        <v>0.028</v>
+        <v>0.2028</v>
       </c>
     </row>
     <row r="18" ht="17" customHeight="1">
@@ -2051,7 +2068,7 @@
         </is>
       </c>
       <c r="C18" s="21" t="n">
-        <v>0.035</v>
+        <v>-0.0224</v>
       </c>
       <c r="D18" s="18" t="inlineStr">
         <is>
@@ -2077,12 +2094,12 @@
     <row r="20" ht="17" customHeight="1">
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  WACC INPUTS</t>
-        </is>
-      </c>
-      <c r="C20" s="72" t="n"/>
-      <c r="D20" s="72" t="n"/>
-      <c r="E20" s="73" t="n"/>
+          <t xml:space="preserve">  WACC INPUTS  ·  Source: Damodaran Implied ERP — pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histimpl.html  (2025: Rf=4.18%, ERP=4.23%)</t>
+        </is>
+      </c>
+      <c r="C20" s="75" t="n"/>
+      <c r="D20" s="75" t="n"/>
+      <c r="E20" s="76" t="n"/>
     </row>
     <row r="21" ht="17" customHeight="1">
       <c r="B21" s="18" t="inlineStr">
@@ -2091,7 +2108,7 @@
         </is>
       </c>
       <c r="C21" s="21" t="n">
-        <v>0.04475</v>
+        <v>0.0418</v>
       </c>
       <c r="D21" s="18" t="inlineStr">
         <is>
@@ -2099,7 +2116,7 @@
         </is>
       </c>
       <c r="E21" s="21" t="n">
-        <v>0.055</v>
+        <v>0.0423</v>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1">
@@ -2109,7 +2126,7 @@
         </is>
       </c>
       <c r="C22" s="17" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.07</v>
       </c>
       <c r="D22" s="18" t="inlineStr">
         <is>
@@ -2123,33 +2140,35 @@
     <row r="23" ht="17" customHeight="1">
       <c r="B23" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Debt / Total Capital</t>
-        </is>
-      </c>
-      <c r="C23" s="21" t="n">
-        <v>0.18</v>
+          <t xml:space="preserve">  Debt / Capital (Wd)  [market-value, auto-computed]</t>
+        </is>
+      </c>
+      <c r="C23" s="23">
+        <f>1-E23</f>
+        <v/>
       </c>
       <c r="D23" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Equity / Capital</t>
-        </is>
-      </c>
-      <c r="E23" s="21" t="n">
-        <v>0.82</v>
+          <t xml:space="preserve">  Equity / Capital (We)  [Price × Shares / (Mkt Cap + Debt)]</t>
+        </is>
+      </c>
+      <c r="E23" s="23">
+        <f>(C7*E7)/((C7*E7)+C8)</f>
+        <v/>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B24" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  WACC (from WACC sheet)</t>
         </is>
       </c>
-      <c r="C24" s="24">
-        <f>WACC!E16</f>
-        <v/>
-      </c>
-      <c r="D24" s="25" t="inlineStr"/>
-      <c r="E24" s="25" t="inlineStr"/>
+      <c r="C24" s="25">
+        <f>WACC!E17</f>
+        <v/>
+      </c>
+      <c r="D24" s="26" t="inlineStr"/>
+      <c r="E24" s="26" t="inlineStr"/>
     </row>
     <row r="25" ht="17" customHeight="1">
       <c r="B25" s="11" t="inlineStr">
@@ -2157,9 +2176,9 @@
           <t xml:space="preserve">  TERMINAL VALUE</t>
         </is>
       </c>
-      <c r="C25" s="72" t="n"/>
-      <c r="D25" s="72" t="n"/>
-      <c r="E25" s="73" t="n"/>
+      <c r="C25" s="75" t="n"/>
+      <c r="D25" s="75" t="n"/>
+      <c r="E25" s="76" t="n"/>
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="B26" s="18" t="inlineStr">
@@ -2185,9 +2204,9 @@
           <t xml:space="preserve">  HISTORICAL REVENUE (for Y0 base)</t>
         </is>
       </c>
-      <c r="C27" s="72" t="n"/>
-      <c r="D27" s="72" t="n"/>
-      <c r="E27" s="73" t="n"/>
+      <c r="C27" s="75" t="n"/>
+      <c r="D27" s="75" t="n"/>
+      <c r="E27" s="76" t="n"/>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="B28" s="18" t="inlineStr">
@@ -2196,7 +2215,7 @@
         </is>
       </c>
       <c r="C28" s="13" t="n">
-        <v>416161</v>
+        <v>318273</v>
       </c>
       <c r="D28" s="18" t="inlineStr">
         <is>
@@ -2204,7 +2223,7 @@
         </is>
       </c>
       <c r="E28" s="13" t="n">
-        <v>365000</v>
+        <v>245122</v>
       </c>
     </row>
     <row r="29" ht="17" customHeight="1">
@@ -2214,65 +2233,105 @@
         </is>
       </c>
       <c r="C29" s="13" t="n">
-        <v>348000</v>
+        <v>211915</v>
       </c>
       <c r="D29" s="22" t="inlineStr"/>
       <c r="E29" s="22" t="inlineStr"/>
     </row>
+    <row r="30" ht="17" customHeight="1">
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ADVANCED SETTINGS  (change here — all sheets update automatically)</t>
+        </is>
+      </c>
+      <c r="C30" s="75" t="n"/>
+      <c r="D30" s="75" t="n"/>
+      <c r="E30" s="76" t="n"/>
+    </row>
     <row r="31" ht="17" customHeight="1">
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Mid-Year Offset  (0 = yr-end, 0.5 = mid-yr)</t>
+        </is>
+      </c>
+      <c r="C31" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SBC Add-Back Scale  (1 = full, 0 = exclude)</t>
+        </is>
+      </c>
+      <c r="E31" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="13" customHeight="1">
+      <c r="B32" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Mid-Year: 0 = cash flows arrive year-end (default) | 0.5 = mid-year convention (raises implied price ~4–6%) | 0.3 or 0.7 also valid. SBC: 1 = full add-back | 0.5 = partial | 0 = exclude (most conservative).</t>
+        </is>
+      </c>
+      <c r="C32" s="75" t="n"/>
+      <c r="D32" s="75" t="n"/>
+      <c r="E32" s="76" t="n"/>
+    </row>
+    <row r="34" ht="17" customHeight="1">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  INVESTMENT THESIS (free text)</t>
         </is>
       </c>
-      <c r="C31" s="72" t="n"/>
-      <c r="D31" s="72" t="n"/>
-      <c r="E31" s="73" t="n"/>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="B32" s="9" t="inlineStr">
+      <c r="C34" s="75" t="n"/>
+      <c r="D34" s="75" t="n"/>
+      <c r="E34" s="76" t="n"/>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>Company and thesis notes here.</t>
         </is>
       </c>
-      <c r="C32" s="72" t="n"/>
-      <c r="D32" s="72" t="n"/>
-      <c r="E32" s="73" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="B33" s="9" t="inlineStr">
+      <c r="C35" s="75" t="n"/>
+      <c r="D35" s="75" t="n"/>
+      <c r="E35" s="76" t="n"/>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>Key risks:</t>
         </is>
       </c>
-      <c r="C33" s="72" t="n"/>
-      <c r="D33" s="72" t="n"/>
-      <c r="E33" s="73" t="n"/>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="B34" s="9" t="inlineStr">
+      <c r="C36" s="75" t="n"/>
+      <c r="D36" s="75" t="n"/>
+      <c r="E36" s="76" t="n"/>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>Key catalysts:</t>
         </is>
       </c>
-      <c r="C34" s="72" t="n"/>
-      <c r="D34" s="72" t="n"/>
-      <c r="E34" s="73" t="n"/>
+      <c r="C37" s="75" t="n"/>
+      <c r="D37" s="75" t="n"/>
+      <c r="E37" s="76" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="B31:E31"/>
+  <mergeCells count="14">
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B35:E35"/>
     <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B30:E30"/>
     <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B33:E33"/>
     <mergeCell ref="B25:E25"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="B20:E20"/>
-    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B32:E32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2306,92 +2365,92 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="B1" s="26" t="inlineStr">
+      <c r="B1" s="29" t="inlineStr">
         <is>
           <t>INCOME STATEMENT &amp; FREE CASH FLOW  (USD $M)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="13" customHeight="1">
-      <c r="B3" s="27" t="inlineStr"/>
-      <c r="C3" s="28" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr"/>
+      <c r="C3" s="31" t="inlineStr">
         <is>
           <t>HISTORICAL</t>
         </is>
       </c>
-      <c r="F3" s="29" t="inlineStr">
+      <c r="F3" s="32" t="inlineStr">
         <is>
           <t>PROJECTED  (10 years)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  Metric (USD $M)</t>
         </is>
       </c>
-      <c r="C4" s="31" t="inlineStr">
+      <c r="C4" s="34" t="inlineStr">
         <is>
           <t>FY2024A</t>
         </is>
       </c>
-      <c r="D4" s="31" t="inlineStr">
+      <c r="D4" s="34" t="inlineStr">
         <is>
           <t>FY2025A</t>
         </is>
       </c>
-      <c r="E4" s="31" t="inlineStr">
+      <c r="E4" s="34" t="inlineStr">
         <is>
           <t>FY2026A</t>
         </is>
       </c>
-      <c r="F4" s="32" t="inlineStr">
+      <c r="F4" s="35" t="inlineStr">
         <is>
           <t>FY2027E</t>
         </is>
       </c>
-      <c r="G4" s="32" t="inlineStr">
+      <c r="G4" s="35" t="inlineStr">
         <is>
           <t>FY2028E</t>
         </is>
       </c>
-      <c r="H4" s="32" t="inlineStr">
+      <c r="H4" s="35" t="inlineStr">
         <is>
           <t>FY2029E</t>
         </is>
       </c>
-      <c r="I4" s="32" t="inlineStr">
+      <c r="I4" s="35" t="inlineStr">
         <is>
           <t>FY2030E</t>
         </is>
       </c>
-      <c r="J4" s="32" t="inlineStr">
+      <c r="J4" s="35" t="inlineStr">
         <is>
           <t>FY2031E</t>
         </is>
       </c>
-      <c r="K4" s="32" t="inlineStr">
+      <c r="K4" s="35" t="inlineStr">
         <is>
           <t>FY2032E</t>
         </is>
       </c>
-      <c r="L4" s="32" t="inlineStr">
+      <c r="L4" s="35" t="inlineStr">
         <is>
           <t>FY2033E</t>
         </is>
       </c>
-      <c r="M4" s="32" t="inlineStr">
+      <c r="M4" s="35" t="inlineStr">
         <is>
           <t>FY2034E</t>
         </is>
       </c>
-      <c r="N4" s="32" t="inlineStr">
+      <c r="N4" s="35" t="inlineStr">
         <is>
           <t>FY2035E</t>
         </is>
       </c>
-      <c r="O4" s="32" t="inlineStr">
+      <c r="O4" s="35" t="inlineStr">
         <is>
           <t>FY2036E</t>
         </is>
@@ -2403,19 +2462,19 @@
           <t xml:space="preserve">  REVENUE</t>
         </is>
       </c>
-      <c r="C5" s="72" t="n"/>
-      <c r="D5" s="72" t="n"/>
-      <c r="E5" s="72" t="n"/>
-      <c r="F5" s="72" t="n"/>
-      <c r="G5" s="72" t="n"/>
-      <c r="H5" s="72" t="n"/>
-      <c r="I5" s="72" t="n"/>
-      <c r="J5" s="72" t="n"/>
-      <c r="K5" s="72" t="n"/>
-      <c r="L5" s="72" t="n"/>
-      <c r="M5" s="72" t="n"/>
-      <c r="N5" s="72" t="n"/>
-      <c r="O5" s="73" t="n"/>
+      <c r="C5" s="75" t="n"/>
+      <c r="D5" s="75" t="n"/>
+      <c r="E5" s="75" t="n"/>
+      <c r="F5" s="75" t="n"/>
+      <c r="G5" s="75" t="n"/>
+      <c r="H5" s="75" t="n"/>
+      <c r="I5" s="75" t="n"/>
+      <c r="J5" s="75" t="n"/>
+      <c r="K5" s="75" t="n"/>
+      <c r="L5" s="75" t="n"/>
+      <c r="M5" s="75" t="n"/>
+      <c r="N5" s="75" t="n"/>
+      <c r="O5" s="76" t="n"/>
     </row>
     <row r="6" ht="14" customHeight="1">
       <c r="B6" s="19" t="inlineStr">
@@ -2423,62 +2482,62 @@
           <t xml:space="preserve">  Revenue Growth %</t>
         </is>
       </c>
-      <c r="C6" s="33" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D6" s="34">
+      <c r="D6" s="23">
         <f>(D7-C7)/C7</f>
         <v/>
       </c>
-      <c r="E6" s="34">
+      <c r="E6" s="23">
         <f>(E7-D7)/D7</f>
         <v/>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="23">
         <f>Assumptions!C10</f>
         <v/>
       </c>
-      <c r="G6" s="34">
+      <c r="G6" s="23">
         <f>Assumptions!E10</f>
         <v/>
       </c>
-      <c r="H6" s="34">
+      <c r="H6" s="23">
         <f>Assumptions!C11</f>
         <v/>
       </c>
-      <c r="I6" s="34">
+      <c r="I6" s="23">
         <f>Assumptions!E11</f>
         <v/>
       </c>
-      <c r="J6" s="34">
+      <c r="J6" s="23">
         <f>Assumptions!C12</f>
         <v/>
       </c>
-      <c r="K6" s="34">
+      <c r="K6" s="23">
         <f>Assumptions!E12</f>
         <v/>
       </c>
-      <c r="L6" s="34">
+      <c r="L6" s="23">
         <f>Assumptions!C13</f>
         <v/>
       </c>
-      <c r="M6" s="34">
+      <c r="M6" s="23">
         <f>Assumptions!E13</f>
         <v/>
       </c>
-      <c r="N6" s="34">
+      <c r="N6" s="23">
         <f>Assumptions!C14</f>
         <v/>
       </c>
-      <c r="O6" s="34">
+      <c r="O6" s="23">
         <f>Assumptions!E14</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue</t>
         </is>
@@ -2495,43 +2554,43 @@
         <f>Assumptions!C28</f>
         <v/>
       </c>
-      <c r="F7" s="35">
+      <c r="F7" s="37">
         <f>E7*(1+Assumptions!C10)</f>
         <v/>
       </c>
-      <c r="G7" s="35">
+      <c r="G7" s="37">
         <f>F7*(1+Assumptions!E10)</f>
         <v/>
       </c>
-      <c r="H7" s="35">
+      <c r="H7" s="37">
         <f>G7*(1+Assumptions!C11)</f>
         <v/>
       </c>
-      <c r="I7" s="35">
+      <c r="I7" s="37">
         <f>H7*(1+Assumptions!E11)</f>
         <v/>
       </c>
-      <c r="J7" s="35">
+      <c r="J7" s="37">
         <f>I7*(1+Assumptions!C12)</f>
         <v/>
       </c>
-      <c r="K7" s="35">
+      <c r="K7" s="37">
         <f>J7*(1+Assumptions!E12)</f>
         <v/>
       </c>
-      <c r="L7" s="35">
+      <c r="L7" s="37">
         <f>K7*(1+Assumptions!C13)</f>
         <v/>
       </c>
-      <c r="M7" s="35">
+      <c r="M7" s="37">
         <f>L7*(1+Assumptions!E13)</f>
         <v/>
       </c>
-      <c r="N7" s="35">
+      <c r="N7" s="37">
         <f>M7*(1+Assumptions!C14)</f>
         <v/>
       </c>
-      <c r="O7" s="35">
+      <c r="O7" s="37">
         <f>N7*(1+Assumptions!E14)</f>
         <v/>
       </c>
@@ -2542,19 +2601,19 @@
           <t xml:space="preserve">  GROSS PROFIT</t>
         </is>
       </c>
-      <c r="C8" s="72" t="n"/>
-      <c r="D8" s="72" t="n"/>
-      <c r="E8" s="72" t="n"/>
-      <c r="F8" s="72" t="n"/>
-      <c r="G8" s="72" t="n"/>
-      <c r="H8" s="72" t="n"/>
-      <c r="I8" s="72" t="n"/>
-      <c r="J8" s="72" t="n"/>
-      <c r="K8" s="72" t="n"/>
-      <c r="L8" s="72" t="n"/>
-      <c r="M8" s="72" t="n"/>
-      <c r="N8" s="72" t="n"/>
-      <c r="O8" s="73" t="n"/>
+      <c r="C8" s="75" t="n"/>
+      <c r="D8" s="75" t="n"/>
+      <c r="E8" s="75" t="n"/>
+      <c r="F8" s="75" t="n"/>
+      <c r="G8" s="75" t="n"/>
+      <c r="H8" s="75" t="n"/>
+      <c r="I8" s="75" t="n"/>
+      <c r="J8" s="75" t="n"/>
+      <c r="K8" s="75" t="n"/>
+      <c r="L8" s="75" t="n"/>
+      <c r="M8" s="75" t="n"/>
+      <c r="N8" s="75" t="n"/>
+      <c r="O8" s="76" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="B9" s="19" t="inlineStr">
@@ -2571,102 +2630,102 @@
       <c r="E9" s="21" t="n">
         <v>0.435</v>
       </c>
-      <c r="F9" s="34">
+      <c r="F9" s="23">
         <f>Assumptions!C16</f>
         <v/>
       </c>
-      <c r="G9" s="34">
+      <c r="G9" s="23">
         <f>Assumptions!C16</f>
         <v/>
       </c>
-      <c r="H9" s="34">
+      <c r="H9" s="23">
         <f>Assumptions!C16</f>
         <v/>
       </c>
-      <c r="I9" s="34">
+      <c r="I9" s="23">
         <f>Assumptions!C16</f>
         <v/>
       </c>
-      <c r="J9" s="34">
+      <c r="J9" s="23">
         <f>Assumptions!C16</f>
         <v/>
       </c>
-      <c r="K9" s="34">
+      <c r="K9" s="23">
         <f>Assumptions!C16</f>
         <v/>
       </c>
-      <c r="L9" s="34">
+      <c r="L9" s="23">
         <f>Assumptions!C16</f>
         <v/>
       </c>
-      <c r="M9" s="34">
+      <c r="M9" s="23">
         <f>Assumptions!C16</f>
         <v/>
       </c>
-      <c r="N9" s="34">
+      <c r="N9" s="23">
         <f>Assumptions!C16</f>
         <v/>
       </c>
-      <c r="O9" s="34">
+      <c r="O9" s="23">
         <f>Assumptions!C16</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  Gross Profit</t>
         </is>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="37">
         <f>C7*C9</f>
         <v/>
       </c>
-      <c r="D10" s="35">
+      <c r="D10" s="37">
         <f>D7*D9</f>
         <v/>
       </c>
-      <c r="E10" s="35">
+      <c r="E10" s="37">
         <f>E7*E9</f>
         <v/>
       </c>
-      <c r="F10" s="35">
+      <c r="F10" s="37">
         <f>F7*F9</f>
         <v/>
       </c>
-      <c r="G10" s="35">
+      <c r="G10" s="37">
         <f>G7*G9</f>
         <v/>
       </c>
-      <c r="H10" s="35">
+      <c r="H10" s="37">
         <f>H7*H9</f>
         <v/>
       </c>
-      <c r="I10" s="35">
+      <c r="I10" s="37">
         <f>I7*I9</f>
         <v/>
       </c>
-      <c r="J10" s="35">
+      <c r="J10" s="37">
         <f>J7*J9</f>
         <v/>
       </c>
-      <c r="K10" s="35">
+      <c r="K10" s="37">
         <f>K7*K9</f>
         <v/>
       </c>
-      <c r="L10" s="35">
+      <c r="L10" s="37">
         <f>L7*L9</f>
         <v/>
       </c>
-      <c r="M10" s="35">
+      <c r="M10" s="37">
         <f>M7*M9</f>
         <v/>
       </c>
-      <c r="N10" s="35">
+      <c r="N10" s="37">
         <f>N7*N9</f>
         <v/>
       </c>
-      <c r="O10" s="35">
+      <c r="O10" s="37">
         <f>O7*O9</f>
         <v/>
       </c>
@@ -2677,19 +2736,19 @@
           <t xml:space="preserve">  OPERATING EXPENSES -&gt; EBITDA</t>
         </is>
       </c>
-      <c r="C11" s="72" t="n"/>
-      <c r="D11" s="72" t="n"/>
-      <c r="E11" s="72" t="n"/>
-      <c r="F11" s="72" t="n"/>
-      <c r="G11" s="72" t="n"/>
-      <c r="H11" s="72" t="n"/>
-      <c r="I11" s="72" t="n"/>
-      <c r="J11" s="72" t="n"/>
-      <c r="K11" s="72" t="n"/>
-      <c r="L11" s="72" t="n"/>
-      <c r="M11" s="72" t="n"/>
-      <c r="N11" s="72" t="n"/>
-      <c r="O11" s="73" t="n"/>
+      <c r="C11" s="75" t="n"/>
+      <c r="D11" s="75" t="n"/>
+      <c r="E11" s="75" t="n"/>
+      <c r="F11" s="75" t="n"/>
+      <c r="G11" s="75" t="n"/>
+      <c r="H11" s="75" t="n"/>
+      <c r="I11" s="75" t="n"/>
+      <c r="J11" s="75" t="n"/>
+      <c r="K11" s="75" t="n"/>
+      <c r="L11" s="75" t="n"/>
+      <c r="M11" s="75" t="n"/>
+      <c r="N11" s="75" t="n"/>
+      <c r="O11" s="76" t="n"/>
     </row>
     <row r="12" ht="14" customHeight="1">
       <c r="B12" s="19" t="inlineStr">
@@ -2706,102 +2765,102 @@
       <c r="E12" s="21" t="n">
         <v>0.335</v>
       </c>
-      <c r="F12" s="34">
+      <c r="F12" s="23">
         <f>Assumptions!E16</f>
         <v/>
       </c>
-      <c r="G12" s="34">
+      <c r="G12" s="23">
         <f>Assumptions!E16</f>
         <v/>
       </c>
-      <c r="H12" s="34">
+      <c r="H12" s="23">
         <f>Assumptions!E16</f>
         <v/>
       </c>
-      <c r="I12" s="34">
+      <c r="I12" s="23">
         <f>Assumptions!E16</f>
         <v/>
       </c>
-      <c r="J12" s="34">
+      <c r="J12" s="23">
         <f>Assumptions!E16</f>
         <v/>
       </c>
-      <c r="K12" s="34">
+      <c r="K12" s="23">
         <f>Assumptions!E16</f>
         <v/>
       </c>
-      <c r="L12" s="34">
+      <c r="L12" s="23">
         <f>Assumptions!E16</f>
         <v/>
       </c>
-      <c r="M12" s="34">
+      <c r="M12" s="23">
         <f>Assumptions!E16</f>
         <v/>
       </c>
-      <c r="N12" s="34">
+      <c r="N12" s="23">
         <f>Assumptions!E16</f>
         <v/>
       </c>
-      <c r="O12" s="34">
+      <c r="O12" s="23">
         <f>Assumptions!E16</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBITDA</t>
         </is>
       </c>
-      <c r="C13" s="35">
+      <c r="C13" s="37">
         <f>C7*C12</f>
         <v/>
       </c>
-      <c r="D13" s="35">
+      <c r="D13" s="37">
         <f>D7*D12</f>
         <v/>
       </c>
-      <c r="E13" s="35">
+      <c r="E13" s="37">
         <f>E7*E12</f>
         <v/>
       </c>
-      <c r="F13" s="35">
+      <c r="F13" s="37">
         <f>F7*F12</f>
         <v/>
       </c>
-      <c r="G13" s="35">
+      <c r="G13" s="37">
         <f>G7*G12</f>
         <v/>
       </c>
-      <c r="H13" s="35">
+      <c r="H13" s="37">
         <f>H7*H12</f>
         <v/>
       </c>
-      <c r="I13" s="35">
+      <c r="I13" s="37">
         <f>I7*I12</f>
         <v/>
       </c>
-      <c r="J13" s="35">
+      <c r="J13" s="37">
         <f>J7*J12</f>
         <v/>
       </c>
-      <c r="K13" s="35">
+      <c r="K13" s="37">
         <f>K7*K12</f>
         <v/>
       </c>
-      <c r="L13" s="35">
+      <c r="L13" s="37">
         <f>L7*L12</f>
         <v/>
       </c>
-      <c r="M13" s="35">
+      <c r="M13" s="37">
         <f>M7*M12</f>
         <v/>
       </c>
-      <c r="N13" s="35">
+      <c r="N13" s="37">
         <f>N7*N12</f>
         <v/>
       </c>
-      <c r="O13" s="35">
+      <c r="O13" s="37">
         <f>O7*O12</f>
         <v/>
       </c>
@@ -2871,19 +2930,19 @@
           <t xml:space="preserve">  D&amp;A  -&gt;  EBIT</t>
         </is>
       </c>
-      <c r="C15" s="72" t="n"/>
-      <c r="D15" s="72" t="n"/>
-      <c r="E15" s="72" t="n"/>
-      <c r="F15" s="72" t="n"/>
-      <c r="G15" s="72" t="n"/>
-      <c r="H15" s="72" t="n"/>
-      <c r="I15" s="72" t="n"/>
-      <c r="J15" s="72" t="n"/>
-      <c r="K15" s="72" t="n"/>
-      <c r="L15" s="72" t="n"/>
-      <c r="M15" s="72" t="n"/>
-      <c r="N15" s="72" t="n"/>
-      <c r="O15" s="73" t="n"/>
+      <c r="C15" s="75" t="n"/>
+      <c r="D15" s="75" t="n"/>
+      <c r="E15" s="75" t="n"/>
+      <c r="F15" s="75" t="n"/>
+      <c r="G15" s="75" t="n"/>
+      <c r="H15" s="75" t="n"/>
+      <c r="I15" s="75" t="n"/>
+      <c r="J15" s="75" t="n"/>
+      <c r="K15" s="75" t="n"/>
+      <c r="L15" s="75" t="n"/>
+      <c r="M15" s="75" t="n"/>
+      <c r="N15" s="75" t="n"/>
+      <c r="O15" s="76" t="n"/>
     </row>
     <row r="16" ht="14" customHeight="1">
       <c r="B16" s="19" t="inlineStr">
@@ -2900,43 +2959,43 @@
       <c r="E16" s="21" t="n">
         <v>0.025</v>
       </c>
-      <c r="F16" s="34">
+      <c r="F16" s="23">
         <f>Assumptions!C17</f>
         <v/>
       </c>
-      <c r="G16" s="34">
+      <c r="G16" s="23">
         <f>Assumptions!C17</f>
         <v/>
       </c>
-      <c r="H16" s="34">
+      <c r="H16" s="23">
         <f>Assumptions!C17</f>
         <v/>
       </c>
-      <c r="I16" s="34">
+      <c r="I16" s="23">
         <f>Assumptions!C17</f>
         <v/>
       </c>
-      <c r="J16" s="34">
+      <c r="J16" s="23">
         <f>Assumptions!C17</f>
         <v/>
       </c>
-      <c r="K16" s="34">
+      <c r="K16" s="23">
         <f>Assumptions!C17</f>
         <v/>
       </c>
-      <c r="L16" s="34">
+      <c r="L16" s="23">
         <f>Assumptions!C17</f>
         <v/>
       </c>
-      <c r="M16" s="34">
+      <c r="M16" s="23">
         <f>Assumptions!C17</f>
         <v/>
       </c>
-      <c r="N16" s="34">
+      <c r="N16" s="23">
         <f>Assumptions!C17</f>
         <v/>
       </c>
-      <c r="O16" s="34">
+      <c r="O16" s="23">
         <f>Assumptions!C17</f>
         <v/>
       </c>
@@ -3001,60 +3060,60 @@
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT (Operating Income)</t>
         </is>
       </c>
-      <c r="C18" s="35">
+      <c r="C18" s="37">
         <f>C13-C17</f>
         <v/>
       </c>
-      <c r="D18" s="35">
+      <c r="D18" s="37">
         <f>D13-D17</f>
         <v/>
       </c>
-      <c r="E18" s="35">
+      <c r="E18" s="37">
         <f>E13-E17</f>
         <v/>
       </c>
-      <c r="F18" s="35">
+      <c r="F18" s="37">
         <f>F13-F17</f>
         <v/>
       </c>
-      <c r="G18" s="35">
+      <c r="G18" s="37">
         <f>G13-G17</f>
         <v/>
       </c>
-      <c r="H18" s="35">
+      <c r="H18" s="37">
         <f>H13-H17</f>
         <v/>
       </c>
-      <c r="I18" s="35">
+      <c r="I18" s="37">
         <f>I13-I17</f>
         <v/>
       </c>
-      <c r="J18" s="35">
+      <c r="J18" s="37">
         <f>J13-J17</f>
         <v/>
       </c>
-      <c r="K18" s="35">
+      <c r="K18" s="37">
         <f>K13-K17</f>
         <v/>
       </c>
-      <c r="L18" s="35">
+      <c r="L18" s="37">
         <f>L13-L17</f>
         <v/>
       </c>
-      <c r="M18" s="35">
+      <c r="M18" s="37">
         <f>M13-M17</f>
         <v/>
       </c>
-      <c r="N18" s="35">
+      <c r="N18" s="37">
         <f>N13-N17</f>
         <v/>
       </c>
-      <c r="O18" s="35">
+      <c r="O18" s="37">
         <f>O13-O17</f>
         <v/>
       </c>
@@ -3065,55 +3124,55 @@
           <t xml:space="preserve">  EBIT Margin %</t>
         </is>
       </c>
-      <c r="C19" s="34">
+      <c r="C19" s="23">
         <f>IF(C7=0,0,C18/C7)</f>
         <v/>
       </c>
-      <c r="D19" s="34">
+      <c r="D19" s="23">
         <f>IF(D7=0,0,D18/D7)</f>
         <v/>
       </c>
-      <c r="E19" s="34">
+      <c r="E19" s="23">
         <f>IF(E7=0,0,E18/E7)</f>
         <v/>
       </c>
-      <c r="F19" s="34">
+      <c r="F19" s="23">
         <f>IF(F7=0,0,F18/F7)</f>
         <v/>
       </c>
-      <c r="G19" s="34">
+      <c r="G19" s="23">
         <f>IF(G7=0,0,G18/G7)</f>
         <v/>
       </c>
-      <c r="H19" s="34">
+      <c r="H19" s="23">
         <f>IF(H7=0,0,H18/H7)</f>
         <v/>
       </c>
-      <c r="I19" s="34">
+      <c r="I19" s="23">
         <f>IF(I7=0,0,I18/I7)</f>
         <v/>
       </c>
-      <c r="J19" s="34">
+      <c r="J19" s="23">
         <f>IF(J7=0,0,J18/J7)</f>
         <v/>
       </c>
-      <c r="K19" s="34">
+      <c r="K19" s="23">
         <f>IF(K7=0,0,K18/K7)</f>
         <v/>
       </c>
-      <c r="L19" s="34">
+      <c r="L19" s="23">
         <f>IF(L7=0,0,L18/L7)</f>
         <v/>
       </c>
-      <c r="M19" s="34">
+      <c r="M19" s="23">
         <f>IF(M7=0,0,M18/M7)</f>
         <v/>
       </c>
-      <c r="N19" s="34">
+      <c r="N19" s="23">
         <f>IF(N7=0,0,N18/N7)</f>
         <v/>
       </c>
-      <c r="O19" s="34">
+      <c r="O19" s="23">
         <f>IF(O7=0,0,O18/O7)</f>
         <v/>
       </c>
@@ -3124,19 +3183,19 @@
           <t xml:space="preserve">  NOPAT  (Net Operating Profit After Tax)</t>
         </is>
       </c>
-      <c r="C20" s="72" t="n"/>
-      <c r="D20" s="72" t="n"/>
-      <c r="E20" s="72" t="n"/>
-      <c r="F20" s="72" t="n"/>
-      <c r="G20" s="72" t="n"/>
-      <c r="H20" s="72" t="n"/>
-      <c r="I20" s="72" t="n"/>
-      <c r="J20" s="72" t="n"/>
-      <c r="K20" s="72" t="n"/>
-      <c r="L20" s="72" t="n"/>
-      <c r="M20" s="72" t="n"/>
-      <c r="N20" s="72" t="n"/>
-      <c r="O20" s="73" t="n"/>
+      <c r="C20" s="75" t="n"/>
+      <c r="D20" s="75" t="n"/>
+      <c r="E20" s="75" t="n"/>
+      <c r="F20" s="75" t="n"/>
+      <c r="G20" s="75" t="n"/>
+      <c r="H20" s="75" t="n"/>
+      <c r="I20" s="75" t="n"/>
+      <c r="J20" s="75" t="n"/>
+      <c r="K20" s="75" t="n"/>
+      <c r="L20" s="75" t="n"/>
+      <c r="M20" s="75" t="n"/>
+      <c r="N20" s="75" t="n"/>
+      <c r="O20" s="76" t="n"/>
     </row>
     <row r="21" ht="14" customHeight="1">
       <c r="B21" s="19" t="inlineStr">
@@ -3153,102 +3212,102 @@
       <c r="E21" s="21" t="n">
         <v>0.155</v>
       </c>
-      <c r="F21" s="34">
+      <c r="F21" s="23">
         <f>Assumptions!E18</f>
         <v/>
       </c>
-      <c r="G21" s="34">
+      <c r="G21" s="23">
         <f>Assumptions!E18</f>
         <v/>
       </c>
-      <c r="H21" s="34">
+      <c r="H21" s="23">
         <f>Assumptions!E18</f>
         <v/>
       </c>
-      <c r="I21" s="34">
+      <c r="I21" s="23">
         <f>Assumptions!E18</f>
         <v/>
       </c>
-      <c r="J21" s="34">
+      <c r="J21" s="23">
         <f>Assumptions!E18</f>
         <v/>
       </c>
-      <c r="K21" s="34">
+      <c r="K21" s="23">
         <f>Assumptions!E18</f>
         <v/>
       </c>
-      <c r="L21" s="34">
+      <c r="L21" s="23">
         <f>Assumptions!E18</f>
         <v/>
       </c>
-      <c r="M21" s="34">
+      <c r="M21" s="23">
         <f>Assumptions!E18</f>
         <v/>
       </c>
-      <c r="N21" s="34">
+      <c r="N21" s="23">
         <f>Assumptions!E18</f>
         <v/>
       </c>
-      <c r="O21" s="34">
+      <c r="O21" s="23">
         <f>Assumptions!E18</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT = EBIT x (1 - Tax Rate)</t>
         </is>
       </c>
-      <c r="C22" s="35">
+      <c r="C22" s="37">
         <f>C18*(1-C21)</f>
         <v/>
       </c>
-      <c r="D22" s="35">
+      <c r="D22" s="37">
         <f>D18*(1-D21)</f>
         <v/>
       </c>
-      <c r="E22" s="35">
+      <c r="E22" s="37">
         <f>E18*(1-E21)</f>
         <v/>
       </c>
-      <c r="F22" s="35">
+      <c r="F22" s="37">
         <f>F18*(1-F21)</f>
         <v/>
       </c>
-      <c r="G22" s="35">
+      <c r="G22" s="37">
         <f>G18*(1-G21)</f>
         <v/>
       </c>
-      <c r="H22" s="35">
+      <c r="H22" s="37">
         <f>H18*(1-H21)</f>
         <v/>
       </c>
-      <c r="I22" s="35">
+      <c r="I22" s="37">
         <f>I18*(1-I21)</f>
         <v/>
       </c>
-      <c r="J22" s="35">
+      <c r="J22" s="37">
         <f>J18*(1-J21)</f>
         <v/>
       </c>
-      <c r="K22" s="35">
+      <c r="K22" s="37">
         <f>K18*(1-K21)</f>
         <v/>
       </c>
-      <c r="L22" s="35">
+      <c r="L22" s="37">
         <f>L18*(1-L21)</f>
         <v/>
       </c>
-      <c r="M22" s="35">
+      <c r="M22" s="37">
         <f>M18*(1-M21)</f>
         <v/>
       </c>
-      <c r="N22" s="35">
+      <c r="N22" s="37">
         <f>N18*(1-N21)</f>
         <v/>
       </c>
-      <c r="O22" s="35">
+      <c r="O22" s="37">
         <f>O18*(1-O21)</f>
         <v/>
       </c>
@@ -3259,19 +3318,19 @@
           <t xml:space="preserve">  FREE CASH FLOW TO FIRM (FCFF)</t>
         </is>
       </c>
-      <c r="C23" s="72" t="n"/>
-      <c r="D23" s="72" t="n"/>
-      <c r="E23" s="72" t="n"/>
-      <c r="F23" s="72" t="n"/>
-      <c r="G23" s="72" t="n"/>
-      <c r="H23" s="72" t="n"/>
-      <c r="I23" s="72" t="n"/>
-      <c r="J23" s="72" t="n"/>
-      <c r="K23" s="72" t="n"/>
-      <c r="L23" s="72" t="n"/>
-      <c r="M23" s="72" t="n"/>
-      <c r="N23" s="72" t="n"/>
-      <c r="O23" s="73" t="n"/>
+      <c r="C23" s="75" t="n"/>
+      <c r="D23" s="75" t="n"/>
+      <c r="E23" s="75" t="n"/>
+      <c r="F23" s="75" t="n"/>
+      <c r="G23" s="75" t="n"/>
+      <c r="H23" s="75" t="n"/>
+      <c r="I23" s="75" t="n"/>
+      <c r="J23" s="75" t="n"/>
+      <c r="K23" s="75" t="n"/>
+      <c r="L23" s="75" t="n"/>
+      <c r="M23" s="75" t="n"/>
+      <c r="N23" s="75" t="n"/>
+      <c r="O23" s="76" t="n"/>
     </row>
     <row r="24" ht="14" customHeight="1">
       <c r="B24" s="19" t="inlineStr">
@@ -3347,43 +3406,43 @@
       <c r="E25" s="21" t="n">
         <v>0.028</v>
       </c>
-      <c r="F25" s="34">
+      <c r="F25" s="23">
         <f>Assumptions!E17</f>
         <v/>
       </c>
-      <c r="G25" s="34">
+      <c r="G25" s="23">
         <f>Assumptions!E17</f>
         <v/>
       </c>
-      <c r="H25" s="34">
+      <c r="H25" s="23">
         <f>Assumptions!E17</f>
         <v/>
       </c>
-      <c r="I25" s="34">
+      <c r="I25" s="23">
         <f>Assumptions!E17</f>
         <v/>
       </c>
-      <c r="J25" s="34">
+      <c r="J25" s="23">
         <f>Assumptions!E17</f>
         <v/>
       </c>
-      <c r="K25" s="34">
+      <c r="K25" s="23">
         <f>Assumptions!E17</f>
         <v/>
       </c>
-      <c r="L25" s="34">
+      <c r="L25" s="23">
         <f>Assumptions!E17</f>
         <v/>
       </c>
-      <c r="M25" s="34">
+      <c r="M25" s="23">
         <f>Assumptions!E17</f>
         <v/>
       </c>
-      <c r="N25" s="34">
+      <c r="N25" s="23">
         <f>Assumptions!E17</f>
         <v/>
       </c>
-      <c r="O25" s="34">
+      <c r="O25" s="23">
         <f>Assumptions!E17</f>
         <v/>
       </c>
@@ -3460,7 +3519,7 @@
         <v>-3800</v>
       </c>
       <c r="E27" s="15">
-        <f>-Assumptions!C18*E7</f>
+        <f>-Assumptions!C18*(E7-D7)</f>
         <v/>
       </c>
       <c r="F27" s="15">
@@ -3562,61 +3621,61 @@
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="B29" s="36" t="inlineStr">
+      <c r="B29" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  FCFF  (Free Cash Flow to Firm)</t>
         </is>
       </c>
-      <c r="C29" s="37">
-        <f>C22+C24-C26+C27+C28</f>
-        <v/>
-      </c>
-      <c r="D29" s="37">
-        <f>D22+D24-D26+D27+D28</f>
-        <v/>
-      </c>
-      <c r="E29" s="37">
-        <f>E22+E24-E26+E27+E28</f>
-        <v/>
-      </c>
-      <c r="F29" s="37">
-        <f>F22+F24-F26+F27+F28</f>
-        <v/>
-      </c>
-      <c r="G29" s="37">
-        <f>G22+G24-G26+G27+G28</f>
-        <v/>
-      </c>
-      <c r="H29" s="37">
-        <f>H22+H24-H26+H27+H28</f>
-        <v/>
-      </c>
-      <c r="I29" s="37">
-        <f>I22+I24-I26+I27+I28</f>
-        <v/>
-      </c>
-      <c r="J29" s="37">
-        <f>J22+J24-J26+J27+J28</f>
-        <v/>
-      </c>
-      <c r="K29" s="37">
-        <f>K22+K24-K26+K27+K28</f>
-        <v/>
-      </c>
-      <c r="L29" s="37">
-        <f>L22+L24-L26+L27+L28</f>
-        <v/>
-      </c>
-      <c r="M29" s="37">
-        <f>M22+M24-M26+M27+M28</f>
-        <v/>
-      </c>
-      <c r="N29" s="37">
-        <f>N22+N24-N26+N27+N28</f>
-        <v/>
-      </c>
-      <c r="O29" s="37">
-        <f>O22+O24-O26+O27+O28</f>
+      <c r="C29" s="39">
+        <f>MAX(0,C22+C24-C26+C27+C28*Assumptions!E31)</f>
+        <v/>
+      </c>
+      <c r="D29" s="39">
+        <f>MAX(0,D22+D24-D26+D27+D28*Assumptions!E31)</f>
+        <v/>
+      </c>
+      <c r="E29" s="39">
+        <f>MAX(0,E22+E24-E26+E27+E28*Assumptions!E31)</f>
+        <v/>
+      </c>
+      <c r="F29" s="39">
+        <f>MAX(0,F22+F24-F26+F27+F28*Assumptions!E31)</f>
+        <v/>
+      </c>
+      <c r="G29" s="39">
+        <f>MAX(0,G22+G24-G26+G27+G28*Assumptions!E31)</f>
+        <v/>
+      </c>
+      <c r="H29" s="39">
+        <f>MAX(0,H22+H24-H26+H27+H28*Assumptions!E31)</f>
+        <v/>
+      </c>
+      <c r="I29" s="39">
+        <f>MAX(0,I22+I24-I26+I27+I28*Assumptions!E31)</f>
+        <v/>
+      </c>
+      <c r="J29" s="39">
+        <f>MAX(0,J22+J24-J26+J27+J28*Assumptions!E31)</f>
+        <v/>
+      </c>
+      <c r="K29" s="39">
+        <f>MAX(0,K22+K24-K26+K27+K28*Assumptions!E31)</f>
+        <v/>
+      </c>
+      <c r="L29" s="39">
+        <f>MAX(0,L22+L24-L26+L27+L28*Assumptions!E31)</f>
+        <v/>
+      </c>
+      <c r="M29" s="39">
+        <f>MAX(0,M22+M24-M26+M27+M28*Assumptions!E31)</f>
+        <v/>
+      </c>
+      <c r="N29" s="39">
+        <f>MAX(0,N22+N24-N26+N27+N28*Assumptions!E31)</f>
+        <v/>
+      </c>
+      <c r="O29" s="39">
+        <f>MAX(0,O22+O24-O26+O27+O28*Assumptions!E31)</f>
         <v/>
       </c>
     </row>
@@ -3626,55 +3685,55 @@
           <t xml:space="preserve">  FCF Margin %</t>
         </is>
       </c>
-      <c r="C30" s="34">
+      <c r="C30" s="23">
         <f>IF(C7=0,0,C29/C7)</f>
         <v/>
       </c>
-      <c r="D30" s="34">
+      <c r="D30" s="23">
         <f>IF(D7=0,0,D29/D7)</f>
         <v/>
       </c>
-      <c r="E30" s="34">
+      <c r="E30" s="23">
         <f>IF(E7=0,0,E29/E7)</f>
         <v/>
       </c>
-      <c r="F30" s="34">
+      <c r="F30" s="23">
         <f>IF(F7=0,0,F29/F7)</f>
         <v/>
       </c>
-      <c r="G30" s="34">
+      <c r="G30" s="23">
         <f>IF(G7=0,0,G29/G7)</f>
         <v/>
       </c>
-      <c r="H30" s="34">
+      <c r="H30" s="23">
         <f>IF(H7=0,0,H29/H7)</f>
         <v/>
       </c>
-      <c r="I30" s="34">
+      <c r="I30" s="23">
         <f>IF(I7=0,0,I29/I7)</f>
         <v/>
       </c>
-      <c r="J30" s="34">
+      <c r="J30" s="23">
         <f>IF(J7=0,0,J29/J7)</f>
         <v/>
       </c>
-      <c r="K30" s="34">
+      <c r="K30" s="23">
         <f>IF(K7=0,0,K29/K7)</f>
         <v/>
       </c>
-      <c r="L30" s="34">
+      <c r="L30" s="23">
         <f>IF(L7=0,0,L29/L7)</f>
         <v/>
       </c>
-      <c r="M30" s="34">
+      <c r="M30" s="23">
         <f>IF(M7=0,0,M29/M7)</f>
         <v/>
       </c>
-      <c r="N30" s="34">
+      <c r="N30" s="23">
         <f>IF(N7=0,0,N29/N7)</f>
         <v/>
       </c>
-      <c r="O30" s="34">
+      <c r="O30" s="23">
         <f>IF(O7=0,0,O29/O7)</f>
         <v/>
       </c>
@@ -3685,19 +3744,19 @@
           <t xml:space="preserve">  10-YEAR FCF PROJECTION (from model above)</t>
         </is>
       </c>
-      <c r="C32" s="72" t="n"/>
-      <c r="D32" s="72" t="n"/>
-      <c r="E32" s="72" t="n"/>
-      <c r="F32" s="72" t="n"/>
-      <c r="G32" s="72" t="n"/>
-      <c r="H32" s="72" t="n"/>
-      <c r="I32" s="72" t="n"/>
-      <c r="J32" s="72" t="n"/>
-      <c r="K32" s="72" t="n"/>
-      <c r="L32" s="72" t="n"/>
-      <c r="M32" s="72" t="n"/>
-      <c r="N32" s="72" t="n"/>
-      <c r="O32" s="73" t="n"/>
+      <c r="C32" s="75" t="n"/>
+      <c r="D32" s="75" t="n"/>
+      <c r="E32" s="75" t="n"/>
+      <c r="F32" s="75" t="n"/>
+      <c r="G32" s="75" t="n"/>
+      <c r="H32" s="75" t="n"/>
+      <c r="I32" s="75" t="n"/>
+      <c r="J32" s="75" t="n"/>
+      <c r="K32" s="75" t="n"/>
+      <c r="L32" s="75" t="n"/>
+      <c r="M32" s="75" t="n"/>
+      <c r="N32" s="75" t="n"/>
+      <c r="O32" s="76" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -3724,7 +3783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E18"/>
+  <dimension ref="B1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -3751,12 +3810,12 @@
     <row r="4" ht="16" customHeight="1">
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  COST OF EQUITY  -  CAPM:  Ke = Rf + beta x ERP</t>
-        </is>
-      </c>
-      <c r="C4" s="72" t="n"/>
-      <c r="D4" s="72" t="n"/>
-      <c r="E4" s="73" t="n"/>
+          <t xml:space="preserve">  COST OF EQUITY  -  CAPM:  Ke = Rf + Beta x ERP  (Hamada re-levering)</t>
+        </is>
+      </c>
+      <c r="C4" s="75" t="n"/>
+      <c r="D4" s="75" t="n"/>
+      <c r="E4" s="76" t="n"/>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="B5" s="18" t="inlineStr">
@@ -3764,7 +3823,7 @@
           <t xml:space="preserve">  Risk-Free Rate (Rf)</t>
         </is>
       </c>
-      <c r="C5" s="34">
+      <c r="C5" s="23">
         <f>Assumptions!C21</f>
         <v/>
       </c>
@@ -3773,7 +3832,7 @@
           <t xml:space="preserve">  Equity Risk Premium</t>
         </is>
       </c>
-      <c r="E5" s="34">
+      <c r="E5" s="23">
         <f>Assumptions!E21</f>
         <v/>
       </c>
@@ -3781,165 +3840,185 @@
     <row r="6" ht="17" customHeight="1">
       <c r="B6" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Beta (Levered)</t>
-        </is>
-      </c>
-      <c r="C6" s="38">
+          <t xml:space="preserve">  Beta (Levered, from market data)</t>
+        </is>
+      </c>
+      <c r="C6" s="40">
         <f>Assumptions!C22</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="B7" s="39" t="inlineStr">
+    <row r="7" ht="17" customHeight="1">
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Unlevered Beta  [Hamada: Beta_L / (1+(1-t)×Wd/We)]</t>
+        </is>
+      </c>
+      <c r="C7" s="41">
+        <f>Assumptions!C22/(1+(1-Assumptions!E18)*Assumptions!C23/Assumptions!E23)</f>
+        <v/>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Re-levered Beta  [Beta_U × (1+(1-t)×Wd/We)]</t>
+        </is>
+      </c>
+      <c r="E7" s="41">
+        <f>C7*(1+(1-Assumptions!E18)*Assumptions!C23/Assumptions!E23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="B8" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">  COST OF EQUITY (Ke)</t>
         </is>
       </c>
-      <c r="C7" s="72" t="n"/>
-      <c r="D7" s="73" t="n"/>
-      <c r="E7" s="40">
-        <f>Assumptions!C21+Assumptions!C22*Assumptions!E21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="B8" s="11" t="inlineStr">
+      <c r="C8" s="75" t="n"/>
+      <c r="D8" s="76" t="n"/>
+      <c r="E8" s="43">
+        <f>Assumptions!C21+E7*Assumptions!E21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  COST OF DEBT  -  After Tax:  Kd_at = Kd x (1 - Tax Rate)</t>
         </is>
       </c>
-      <c r="C8" s="72" t="n"/>
-      <c r="D8" s="72" t="n"/>
-      <c r="E8" s="73" t="n"/>
-    </row>
-    <row r="9" ht="17" customHeight="1">
-      <c r="B9" s="18" t="inlineStr">
+      <c r="C9" s="75" t="n"/>
+      <c r="D9" s="75" t="n"/>
+      <c r="E9" s="76" t="n"/>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  Pre-Tax Cost of Debt (Kd)</t>
         </is>
       </c>
-      <c r="C9" s="34">
+      <c r="C10" s="23">
         <f>Assumptions!E22</f>
         <v/>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D10" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  Tax Rate</t>
         </is>
       </c>
-      <c r="E9" s="34">
+      <c r="E10" s="23">
         <f>Assumptions!E18</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="B10" s="39" t="inlineStr">
+    <row r="11" ht="20" customHeight="1">
+      <c r="B11" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">  AFTER-TAX COST OF DEBT (Kd)</t>
         </is>
       </c>
-      <c r="C10" s="72" t="n"/>
-      <c r="D10" s="73" t="n"/>
-      <c r="E10" s="40">
-        <f>C9*(1-E9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="B11" s="11" t="inlineStr">
+      <c r="C11" s="75" t="n"/>
+      <c r="D11" s="76" t="n"/>
+      <c r="E11" s="43">
+        <f>C10*(1-E10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  CAPITAL STRUCTURE WEIGHTS</t>
         </is>
       </c>
-      <c r="C11" s="72" t="n"/>
-      <c r="D11" s="72" t="n"/>
-      <c r="E11" s="73" t="n"/>
-    </row>
-    <row r="12" ht="17" customHeight="1">
-      <c r="B12" s="18" t="inlineStr">
+      <c r="C12" s="75" t="n"/>
+      <c r="D12" s="75" t="n"/>
+      <c r="E12" s="76" t="n"/>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  Equity / Capital (We)</t>
         </is>
       </c>
-      <c r="C12" s="34">
+      <c r="C13" s="23">
         <f>Assumptions!E23</f>
         <v/>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D13" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  Debt / Capital (Wd)</t>
         </is>
       </c>
-      <c r="E12" s="34">
+      <c r="E13" s="23">
         <f>Assumptions!C23</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="B13" s="19" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  Check: We + Wd should = 1.0</t>
         </is>
       </c>
-      <c r="C13" s="34">
-        <f>C12+E12</f>
-        <v/>
-      </c>
-      <c r="D13" s="19" t="inlineStr">
+      <c r="C14" s="23">
+        <f>C13+E13</f>
+        <v/>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  Status:</t>
         </is>
       </c>
-      <c r="E13" s="41">
-        <f>IF(ABS(C12+E12-1)&lt;0.001,"OK - sums to 100%","CHECK WEIGHTS")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="B14" s="11" t="inlineStr">
+      <c r="E14" s="44">
+        <f>IF(ABS(C13+E13-1)&lt;0.001,"OK - sums to 100%","CHECK WEIGHTS")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  WACC CALCULATION</t>
         </is>
       </c>
-      <c r="C14" s="72" t="n"/>
-      <c r="D14" s="72" t="n"/>
-      <c r="E14" s="73" t="n"/>
-    </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="B15" s="18" t="inlineStr">
+      <c r="C15" s="75" t="n"/>
+      <c r="D15" s="75" t="n"/>
+      <c r="E15" s="76" t="n"/>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  Ke x We  (equity component)</t>
         </is>
       </c>
-      <c r="C15" s="34">
-        <f>WACC!E7*C12</f>
-        <v/>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="C16" s="23">
+        <f>WACC!E8*C13</f>
+        <v/>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  Kd(1-t) x Wd  (debt component)</t>
         </is>
       </c>
-      <c r="E15" s="34">
-        <f>WACC!E10*E12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="B16" s="42" t="inlineStr">
+      <c r="E16" s="23">
+        <f>WACC!E11*E13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="B17" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">  WACC  =  Ke x We  +  Kd(1-t) x Wd</t>
         </is>
       </c>
-      <c r="C16" s="72" t="n"/>
-      <c r="D16" s="73" t="n"/>
-      <c r="E16" s="43">
-        <f>C15+E15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="44" t="inlineStr">
+      <c r="C17" s="75" t="n"/>
+      <c r="D17" s="76" t="n"/>
+      <c r="E17" s="46">
+        <f>C16+E16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="47" t="inlineStr">
         <is>
           <t>Note: WACC above flows into DCF Valuation sheet automatically. Sensitivity analysis spans +/-150bps in the Sensitivity sheet.</t>
         </is>
@@ -3947,16 +4026,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B9:E9"/>
     <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B8:E8"/>
     <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B15:E15"/>
     <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="B19:E19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3997,9 +4076,9 @@
           <t xml:space="preserve">  DISCOUNT RATE &amp; KEY INPUTS</t>
         </is>
       </c>
-      <c r="C3" s="72" t="n"/>
-      <c r="D3" s="72" t="n"/>
-      <c r="E3" s="73" t="n"/>
+      <c r="C3" s="75" t="n"/>
+      <c r="D3" s="75" t="n"/>
+      <c r="E3" s="76" t="n"/>
     </row>
     <row r="4" ht="17" customHeight="1">
       <c r="B4" s="18" t="inlineStr">
@@ -4007,16 +4086,16 @@
           <t xml:space="preserve">  WACC</t>
         </is>
       </c>
-      <c r="C4" s="34">
-        <f>WACC!E16</f>
-        <v/>
-      </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="C4" s="23">
+        <f>WACC!E17</f>
+        <v/>
+      </c>
+      <c r="D4" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">  Ke×We + Kd(1-t)×Wd  —  from WACC sheet</t>
         </is>
       </c>
-      <c r="E4" s="73" t="n"/>
+      <c r="E4" s="76" t="n"/>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="B5" s="18" t="inlineStr">
@@ -4024,16 +4103,16 @@
           <t xml:space="preserve">  Terminal Growth Rate (g)</t>
         </is>
       </c>
-      <c r="C5" s="34">
+      <c r="C5" s="23">
         <f>Assumptions!C26</f>
         <v/>
       </c>
-      <c r="D5" s="45" t="inlineStr">
+      <c r="D5" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">  Long-run FCF growth after Year 10  —  Assumptions</t>
         </is>
       </c>
-      <c r="E5" s="73" t="n"/>
+      <c r="E5" s="76" t="n"/>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="B6" s="18" t="inlineStr">
@@ -4041,16 +4120,16 @@
           <t xml:space="preserve">  Exit EBITDA Multiple</t>
         </is>
       </c>
-      <c r="C6" s="46">
+      <c r="C6" s="49">
         <f>Assumptions!E26</f>
         <v/>
       </c>
-      <c r="D6" s="45" t="inlineStr">
+      <c r="D6" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">  Reference only; Gordon Growth is primary TV method</t>
         </is>
       </c>
-      <c r="E6" s="73" t="n"/>
+      <c r="E6" s="76" t="n"/>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="B7" s="18" t="inlineStr">
@@ -4062,12 +4141,12 @@
         <f>Assumptions!C8-Assumptions!E8</f>
         <v/>
       </c>
-      <c r="D7" s="45" t="inlineStr">
+      <c r="D7" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">  Total Debt minus Cash  —  from Assumptions</t>
         </is>
       </c>
-      <c r="E7" s="73" t="n"/>
+      <c r="E7" s="76" t="n"/>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="B8" s="18" t="inlineStr">
@@ -4079,12 +4158,12 @@
         <f>Assumptions!E7</f>
         <v/>
       </c>
-      <c r="D8" s="45" t="inlineStr">
+      <c r="D8" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">  Diluted share count  —  from Assumptions</t>
         </is>
       </c>
-      <c r="E8" s="73" t="n"/>
+      <c r="E8" s="76" t="n"/>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="B9" s="11" t="inlineStr">
@@ -4092,9 +4171,9 @@
           <t xml:space="preserve">  PROJECTED FCF BY YEAR  (from Income Statement)</t>
         </is>
       </c>
-      <c r="C9" s="72" t="n"/>
-      <c r="D9" s="72" t="n"/>
-      <c r="E9" s="73" t="n"/>
+      <c r="C9" s="75" t="n"/>
+      <c r="D9" s="75" t="n"/>
+      <c r="E9" s="76" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
       <c r="B10" s="18" t="inlineStr">
@@ -4102,100 +4181,100 @@
           <t xml:space="preserve">  Year</t>
         </is>
       </c>
-      <c r="C10" s="47" t="inlineStr">
+      <c r="C10" s="50" t="inlineStr">
         <is>
           <t>FY2027</t>
         </is>
       </c>
-      <c r="D10" s="47" t="inlineStr">
+      <c r="D10" s="50" t="inlineStr">
         <is>
           <t>FY2028</t>
         </is>
       </c>
-      <c r="E10" s="47" t="inlineStr">
+      <c r="E10" s="50" t="inlineStr">
         <is>
           <t>FY2029</t>
         </is>
       </c>
-      <c r="F10" s="47" t="inlineStr">
+      <c r="F10" s="50" t="inlineStr">
         <is>
           <t>FY2030</t>
         </is>
       </c>
-      <c r="G10" s="47" t="inlineStr">
+      <c r="G10" s="50" t="inlineStr">
         <is>
           <t>FY2031</t>
         </is>
       </c>
-      <c r="H10" s="47" t="inlineStr">
+      <c r="H10" s="50" t="inlineStr">
         <is>
           <t>FY2032</t>
         </is>
       </c>
-      <c r="I10" s="47" t="inlineStr">
+      <c r="I10" s="50" t="inlineStr">
         <is>
           <t>FY2033</t>
         </is>
       </c>
-      <c r="J10" s="47" t="inlineStr">
+      <c r="J10" s="50" t="inlineStr">
         <is>
           <t>FY2034</t>
         </is>
       </c>
-      <c r="K10" s="47" t="inlineStr">
+      <c r="K10" s="50" t="inlineStr">
         <is>
           <t>FY2035</t>
         </is>
       </c>
-      <c r="L10" s="47" t="inlineStr">
+      <c r="L10" s="50" t="inlineStr">
         <is>
           <t>FY2036</t>
         </is>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  FCFF ($M)</t>
         </is>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="37">
         <f>'Income Statement'!F29</f>
         <v/>
       </c>
-      <c r="D11" s="35">
+      <c r="D11" s="37">
         <f>'Income Statement'!G29</f>
         <v/>
       </c>
-      <c r="E11" s="35">
+      <c r="E11" s="37">
         <f>'Income Statement'!H29</f>
         <v/>
       </c>
-      <c r="F11" s="35">
+      <c r="F11" s="37">
         <f>'Income Statement'!I29</f>
         <v/>
       </c>
-      <c r="G11" s="35">
+      <c r="G11" s="37">
         <f>'Income Statement'!J29</f>
         <v/>
       </c>
-      <c r="H11" s="35">
+      <c r="H11" s="37">
         <f>'Income Statement'!K29</f>
         <v/>
       </c>
-      <c r="I11" s="35">
+      <c r="I11" s="37">
         <f>'Income Statement'!L29</f>
         <v/>
       </c>
-      <c r="J11" s="35">
+      <c r="J11" s="37">
         <f>'Income Statement'!M29</f>
         <v/>
       </c>
-      <c r="K11" s="35">
+      <c r="K11" s="37">
         <f>'Income Statement'!N29</f>
         <v/>
       </c>
-      <c r="L11" s="35">
+      <c r="L11" s="37">
         <f>'Income Statement'!O29</f>
         <v/>
       </c>
@@ -4206,127 +4285,127 @@
           <t xml:space="preserve">  Discount Period (t)</t>
         </is>
       </c>
-      <c r="C12" s="46" t="n">
+      <c r="C12" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="46" t="n">
+      <c r="D12" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="46" t="n">
+      <c r="E12" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="F12" s="46" t="n">
+      <c r="F12" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="G12" s="46" t="n">
+      <c r="G12" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="H12" s="46" t="n">
+      <c r="H12" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="I12" s="46" t="n">
+      <c r="I12" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="J12" s="46" t="n">
+      <c r="J12" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="K12" s="46" t="n">
+      <c r="K12" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="L12" s="46" t="n">
+      <c r="L12" s="49" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="13" ht="14" customHeight="1">
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Discount Factor  [1/(1+WACC)^t]</t>
-        </is>
-      </c>
-      <c r="C13" s="48">
-        <f>1/(1+C4)^C12</f>
-        <v/>
-      </c>
-      <c r="D13" s="48">
-        <f>1/(1+C4)^D12</f>
-        <v/>
-      </c>
-      <c r="E13" s="48">
-        <f>1/(1+C4)^E12</f>
-        <v/>
-      </c>
-      <c r="F13" s="48">
-        <f>1/(1+C4)^F12</f>
-        <v/>
-      </c>
-      <c r="G13" s="48">
-        <f>1/(1+C4)^G12</f>
-        <v/>
-      </c>
-      <c r="H13" s="48">
-        <f>1/(1+C4)^H12</f>
-        <v/>
-      </c>
-      <c r="I13" s="48">
-        <f>1/(1+C4)^I12</f>
-        <v/>
-      </c>
-      <c r="J13" s="48">
-        <f>1/(1+C4)^J12</f>
-        <v/>
-      </c>
-      <c r="K13" s="48">
-        <f>1/(1+C4)^K12</f>
-        <v/>
-      </c>
-      <c r="L13" s="48">
-        <f>1/(1+C4)^L12</f>
+          <t xml:space="preserve">  Discount Factor  [1/(1+WACC)^(t − mid-yr offset)]</t>
+        </is>
+      </c>
+      <c r="C13" s="51">
+        <f>1/(1+C4)^(C12-Assumptions!C31)</f>
+        <v/>
+      </c>
+      <c r="D13" s="51">
+        <f>1/(1+C4)^(D12-Assumptions!C31)</f>
+        <v/>
+      </c>
+      <c r="E13" s="51">
+        <f>1/(1+C4)^(E12-Assumptions!C31)</f>
+        <v/>
+      </c>
+      <c r="F13" s="51">
+        <f>1/(1+C4)^(F12-Assumptions!C31)</f>
+        <v/>
+      </c>
+      <c r="G13" s="51">
+        <f>1/(1+C4)^(G12-Assumptions!C31)</f>
+        <v/>
+      </c>
+      <c r="H13" s="51">
+        <f>1/(1+C4)^(H12-Assumptions!C31)</f>
+        <v/>
+      </c>
+      <c r="I13" s="51">
+        <f>1/(1+C4)^(I12-Assumptions!C31)</f>
+        <v/>
+      </c>
+      <c r="J13" s="51">
+        <f>1/(1+C4)^(J12-Assumptions!C31)</f>
+        <v/>
+      </c>
+      <c r="K13" s="51">
+        <f>1/(1+C4)^(K12-Assumptions!C31)</f>
+        <v/>
+      </c>
+      <c r="L13" s="51">
+        <f>1/(1+C4)^(L12-Assumptions!C31)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  PV of FCFF ($M)</t>
         </is>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="37">
         <f>C11*C13</f>
         <v/>
       </c>
-      <c r="D14" s="35">
+      <c r="D14" s="37">
         <f>D11*D13</f>
         <v/>
       </c>
-      <c r="E14" s="35">
+      <c r="E14" s="37">
         <f>E11*E13</f>
         <v/>
       </c>
-      <c r="F14" s="35">
+      <c r="F14" s="37">
         <f>F11*F13</f>
         <v/>
       </c>
-      <c r="G14" s="35">
+      <c r="G14" s="37">
         <f>G11*G13</f>
         <v/>
       </c>
-      <c r="H14" s="35">
+      <c r="H14" s="37">
         <f>H11*H13</f>
         <v/>
       </c>
-      <c r="I14" s="35">
+      <c r="I14" s="37">
         <f>I11*I13</f>
         <v/>
       </c>
-      <c r="J14" s="35">
+      <c r="J14" s="37">
         <f>J11*J13</f>
         <v/>
       </c>
-      <c r="K14" s="35">
+      <c r="K14" s="37">
         <f>K11*K13</f>
         <v/>
       </c>
-      <c r="L14" s="35">
+      <c r="L14" s="37">
         <f>L11*L13</f>
         <v/>
       </c>
@@ -4337,7 +4416,7 @@
           <t xml:space="preserve">  Sum of PV(FCFF), Years 1-10</t>
         </is>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="37">
         <f>SUM(C14:L14)</f>
         <v/>
       </c>
@@ -4348,9 +4427,9 @@
           <t xml:space="preserve">  TERMINAL VALUE</t>
         </is>
       </c>
-      <c r="C16" s="72" t="n"/>
-      <c r="D16" s="72" t="n"/>
-      <c r="E16" s="73" t="n"/>
+      <c r="C16" s="75" t="n"/>
+      <c r="D16" s="75" t="n"/>
+      <c r="E16" s="76" t="n"/>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="B17" s="18" t="inlineStr">
@@ -4359,7 +4438,7 @@
         </is>
       </c>
       <c r="C17" s="15">
-        <f>L11*(1+C5)/(C4-C5)</f>
+        <f>L11*(1+C5)/MAX(C4-C5,0.01)</f>
         <v/>
       </c>
       <c r="D17" s="18" t="inlineStr">
@@ -4367,19 +4446,19 @@
           <t xml:space="preserve">  PV of TV (Gordon Growth)</t>
         </is>
       </c>
-      <c r="E17" s="35">
-        <f>C17/(1+C4)^10</f>
+      <c r="E17" s="37">
+        <f>C17/(1+C4)^(10-Assumptions!C31)</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="17" customHeight="1">
       <c r="B18" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Exit Multiple TV = EBITDA_Y10 x Multiple  [reference only]</t>
+          <t xml:space="preserve">  Exit Multiple TV = EBITDA_Y11 x Multiple  [forward; reference only]</t>
         </is>
       </c>
       <c r="C18" s="15">
-        <f>'Income Statement'!O13*C6</f>
+        <f>'Income Statement'!O13*(1+C5)*C6</f>
         <v/>
       </c>
       <c r="D18" s="18" t="inlineStr">
@@ -4388,7 +4467,7 @@
         </is>
       </c>
       <c r="E18" s="15">
-        <f>C18/(1+C4)^10</f>
+        <f>C18/(1+C4)^(10-Assumptions!C31)</f>
         <v/>
       </c>
     </row>
@@ -4398,9 +4477,9 @@
           <t xml:space="preserve">  VALUATION BRIDGE</t>
         </is>
       </c>
-      <c r="C19" s="72" t="n"/>
-      <c r="D19" s="72" t="n"/>
-      <c r="E19" s="73" t="n"/>
+      <c r="C19" s="75" t="n"/>
+      <c r="D19" s="75" t="n"/>
+      <c r="E19" s="76" t="n"/>
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="B20" s="18" t="inlineStr">
@@ -4408,29 +4487,29 @@
           <t xml:space="preserve">  (+) Sum of PV(FCF) - Years 1-10</t>
         </is>
       </c>
-      <c r="C20" s="35">
+      <c r="C20" s="37">
         <f>C15</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B21" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  (+) PV of Terminal Value (Gordon Growth - PRIMARY)</t>
         </is>
       </c>
-      <c r="C21" s="35">
+      <c r="C21" s="37">
         <f>E17</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="B22" s="49" t="inlineStr">
+      <c r="B22" s="52" t="inlineStr">
         <is>
           <t xml:space="preserve">  ENTERPRISE VALUE</t>
         </is>
       </c>
-      <c r="C22" s="50">
+      <c r="C22" s="53">
         <f>C20+C21</f>
         <v/>
       </c>
@@ -4447,13 +4526,13 @@
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="B24" s="49" t="inlineStr">
+      <c r="B24" s="52" t="inlineStr">
         <is>
           <t xml:space="preserve">  EQUITY VALUE</t>
         </is>
       </c>
-      <c r="C24" s="50">
-        <f>C22-C23</f>
+      <c r="C24" s="53">
+        <f>MAX(0,C22-C23)</f>
         <v/>
       </c>
     </row>
@@ -4469,12 +4548,12 @@
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
-      <c r="B26" s="51" t="inlineStr">
+      <c r="B26" s="54" t="inlineStr">
         <is>
           <t xml:space="preserve">  IMPLIED SHARE PRICE (DCF)</t>
         </is>
       </c>
-      <c r="C26" s="52">
+      <c r="C26" s="55">
         <f>C24/C25</f>
         <v/>
       </c>
@@ -4485,18 +4564,18 @@
           <t xml:space="preserve">  Current Stock Price ($)</t>
         </is>
       </c>
-      <c r="C27" s="53">
+      <c r="C27" s="56">
         <f>Assumptions!C7</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1">
-      <c r="B28" s="23" t="inlineStr">
+      <c r="B28" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  Upside / (Downside) %</t>
         </is>
       </c>
-      <c r="C28" s="54">
+      <c r="C28" s="57">
         <f>(C26-C27)/C27</f>
         <v/>
       </c>
@@ -4507,9 +4586,9 @@
           <t xml:space="preserve">  VALUATION COMPOSITION</t>
         </is>
       </c>
-      <c r="C29" s="72" t="n"/>
-      <c r="D29" s="72" t="n"/>
-      <c r="E29" s="73" t="n"/>
+      <c r="C29" s="75" t="n"/>
+      <c r="D29" s="75" t="n"/>
+      <c r="E29" s="76" t="n"/>
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="B30" s="18" t="inlineStr">
@@ -4517,7 +4596,7 @@
           <t xml:space="preserve">  PV of FCFs as % of Enterprise Value</t>
         </is>
       </c>
-      <c r="C30" s="55">
+      <c r="C30" s="58">
         <f>IF(C22=0,0,C20/C22)</f>
         <v/>
       </c>
@@ -4528,7 +4607,7 @@
           <t xml:space="preserve">  PV of Terminal Value as % of Enterprise Value</t>
         </is>
       </c>
-      <c r="C31" s="55">
+      <c r="C31" s="58">
         <f>IF(C22=0,0,C21/C22)</f>
         <v/>
       </c>
@@ -4539,7 +4618,7 @@
           <t xml:space="preserve">  Implied EV / EBITDA Multiple (LTM)</t>
         </is>
       </c>
-      <c r="C32" s="46">
+      <c r="C32" s="49">
         <f>IF('Income Statement'!E13=0,0,C22/'Income Statement'!E13)</f>
         <v/>
       </c>
@@ -4569,7 +4648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:L30"/>
+  <dimension ref="B1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -4598,517 +4677,517 @@
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="B4" s="56" t="inlineStr">
+      <c r="B4" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">  TABLE 1 - Implied Share Price  vs  WACC  x  Terminal Growth Rate</t>
         </is>
       </c>
-      <c r="C4" s="72" t="n"/>
-      <c r="D4" s="72" t="n"/>
-      <c r="E4" s="72" t="n"/>
-      <c r="F4" s="72" t="n"/>
-      <c r="G4" s="72" t="n"/>
-      <c r="H4" s="72" t="n"/>
-      <c r="I4" s="73" t="n"/>
+      <c r="C4" s="75" t="n"/>
+      <c r="D4" s="75" t="n"/>
+      <c r="E4" s="75" t="n"/>
+      <c r="F4" s="75" t="n"/>
+      <c r="G4" s="75" t="n"/>
+      <c r="H4" s="75" t="n"/>
+      <c r="I4" s="76" t="n"/>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="B5" s="57" t="inlineStr">
+      <c r="B5" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">  WACC \ TGR</t>
         </is>
       </c>
-      <c r="C5" s="58">
+      <c r="C5" s="61">
         <f>'DCF Valuation'!C5+(-0.01)</f>
         <v/>
       </c>
-      <c r="D5" s="58">
+      <c r="D5" s="61">
         <f>'DCF Valuation'!C5+(-0.005)</f>
         <v/>
       </c>
-      <c r="E5" s="58">
+      <c r="E5" s="61">
         <f>'DCF Valuation'!C5+(0.0)</f>
         <v/>
       </c>
-      <c r="F5" s="58">
+      <c r="F5" s="61">
         <f>'DCF Valuation'!C5+(0.005)</f>
         <v/>
       </c>
-      <c r="G5" s="58">
+      <c r="G5" s="61">
         <f>'DCF Valuation'!C5+(0.01)</f>
         <v/>
       </c>
-      <c r="H5" s="58">
+      <c r="H5" s="61">
         <f>'DCF Valuation'!C5+(0.015)</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="B6" s="59">
+      <c r="B6" s="62">
         <f>'DCF Valuation'!C4+(-0.015)</f>
         <v/>
       </c>
-      <c r="C6" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B6)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+C5)/MAX(B6-C5,0.0001)/(1+B6)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
-        <v/>
-      </c>
-      <c r="D6" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B6)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+D5)/MAX(B6-D5,0.0001)/(1+B6)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
-        <v/>
-      </c>
-      <c r="E6" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B6)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+E5)/MAX(B6-E5,0.0001)/(1+B6)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
-        <v/>
-      </c>
-      <c r="F6" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B6)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+F5)/MAX(B6-F5,0.0001)/(1+B6)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
-        <v/>
-      </c>
-      <c r="G6" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B6)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+G5)/MAX(B6-G5,0.0001)/(1+B6)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
-        <v/>
-      </c>
-      <c r="H6" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B6)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+H5)/MAX(B6-H5,0.0001)/(1+B6)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+      <c r="C6" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B6)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+C5)/MAX(B6-C5,0.01)/(1+B6)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="D6" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B6)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+D5)/MAX(B6-D5,0.01)/(1+B6)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="E6" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B6)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+E5)/MAX(B6-E5,0.01)/(1+B6)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="F6" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B6)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+F5)/MAX(B6-F5,0.01)/(1+B6)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="G6" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B6)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+G5)/MAX(B6-G5,0.01)/(1+B6)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="H6" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B6)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+H5)/MAX(B6-H5,0.01)/(1+B6)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="B7" s="59">
+      <c r="B7" s="62">
         <f>'DCF Valuation'!C4+(-0.01)</f>
         <v/>
       </c>
-      <c r="C7" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B7)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+C5)/MAX(B7-C5,0.0001)/(1+B7)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
-        <v/>
-      </c>
-      <c r="D7" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B7)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+D5)/MAX(B7-D5,0.0001)/(1+B7)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
-        <v/>
-      </c>
-      <c r="E7" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B7)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+E5)/MAX(B7-E5,0.0001)/(1+B7)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
-        <v/>
-      </c>
-      <c r="F7" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B7)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+F5)/MAX(B7-F5,0.0001)/(1+B7)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
-        <v/>
-      </c>
-      <c r="G7" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B7)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+G5)/MAX(B7-G5,0.0001)/(1+B7)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
-        <v/>
-      </c>
-      <c r="H7" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B7)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+H5)/MAX(B7-H5,0.0001)/(1+B7)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+      <c r="C7" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B7)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+C5)/MAX(B7-C5,0.01)/(1+B7)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="D7" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B7)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+D5)/MAX(B7-D5,0.01)/(1+B7)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="E7" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B7)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+E5)/MAX(B7-E5,0.01)/(1+B7)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="F7" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B7)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+F5)/MAX(B7-F5,0.01)/(1+B7)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="G7" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B7)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+G5)/MAX(B7-G5,0.01)/(1+B7)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="H7" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B7)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+H5)/MAX(B7-H5,0.01)/(1+B7)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="B8" s="59">
+      <c r="B8" s="62">
         <f>'DCF Valuation'!C4+(-0.005)</f>
         <v/>
       </c>
-      <c r="C8" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B8)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+C5)/MAX(B8-C5,0.0001)/(1+B8)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
-        <v/>
-      </c>
-      <c r="D8" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B8)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+D5)/MAX(B8-D5,0.0001)/(1+B8)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
-        <v/>
-      </c>
-      <c r="E8" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B8)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+E5)/MAX(B8-E5,0.0001)/(1+B8)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
-        <v/>
-      </c>
-      <c r="F8" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B8)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+F5)/MAX(B8-F5,0.0001)/(1+B8)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
-        <v/>
-      </c>
-      <c r="G8" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B8)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+G5)/MAX(B8-G5,0.0001)/(1+B8)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
-        <v/>
-      </c>
-      <c r="H8" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B8)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+H5)/MAX(B8-H5,0.0001)/(1+B8)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+      <c r="C8" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B8)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+C5)/MAX(B8-C5,0.01)/(1+B8)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="D8" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B8)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+D5)/MAX(B8-D5,0.01)/(1+B8)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="E8" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B8)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+E5)/MAX(B8-E5,0.01)/(1+B8)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="F8" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B8)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+F5)/MAX(B8-F5,0.01)/(1+B8)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="G8" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B8)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+G5)/MAX(B8-G5,0.01)/(1+B8)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="H8" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B8)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+H5)/MAX(B8-H5,0.01)/(1+B8)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="B9" s="59">
+      <c r="B9" s="62">
         <f>'DCF Valuation'!C4+(0.0)</f>
         <v/>
       </c>
-      <c r="C9" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B9)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+C5)/MAX(B9-C5,0.0001)/(1+B9)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
-        <v/>
-      </c>
-      <c r="D9" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B9)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+D5)/MAX(B9-D5,0.0001)/(1+B9)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
-        <v/>
-      </c>
-      <c r="E9" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B9)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+E5)/MAX(B9-E5,0.0001)/(1+B9)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
-        <v/>
-      </c>
-      <c r="F9" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B9)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+F5)/MAX(B9-F5,0.0001)/(1+B9)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
-        <v/>
-      </c>
-      <c r="G9" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B9)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+G5)/MAX(B9-G5,0.0001)/(1+B9)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
-        <v/>
-      </c>
-      <c r="H9" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B9)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+H5)/MAX(B9-H5,0.0001)/(1+B9)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+      <c r="C9" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B9)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+C5)/MAX(B9-C5,0.01)/(1+B9)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="D9" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B9)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+D5)/MAX(B9-D5,0.01)/(1+B9)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="E9" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B9)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+E5)/MAX(B9-E5,0.01)/(1+B9)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="F9" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B9)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+F5)/MAX(B9-F5,0.01)/(1+B9)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="G9" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B9)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+G5)/MAX(B9-G5,0.01)/(1+B9)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="H9" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B9)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+H5)/MAX(B9-H5,0.01)/(1+B9)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="B10" s="59">
+      <c r="B10" s="62">
         <f>'DCF Valuation'!C4+(0.005)</f>
         <v/>
       </c>
-      <c r="C10" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B10)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+C5)/MAX(B10-C5,0.0001)/(1+B10)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
-        <v/>
-      </c>
-      <c r="D10" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B10)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+D5)/MAX(B10-D5,0.0001)/(1+B10)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
-        <v/>
-      </c>
-      <c r="E10" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B10)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+E5)/MAX(B10-E5,0.0001)/(1+B10)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
-        <v/>
-      </c>
-      <c r="F10" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B10)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+F5)/MAX(B10-F5,0.0001)/(1+B10)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
-        <v/>
-      </c>
-      <c r="G10" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B10)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+G5)/MAX(B10-G5,0.0001)/(1+B10)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
-        <v/>
-      </c>
-      <c r="H10" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B10)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+H5)/MAX(B10-H5,0.0001)/(1+B10)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+      <c r="C10" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B10)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+C5)/MAX(B10-C5,0.01)/(1+B10)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="D10" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B10)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+D5)/MAX(B10-D5,0.01)/(1+B10)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="E10" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B10)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+E5)/MAX(B10-E5,0.01)/(1+B10)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="F10" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B10)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+F5)/MAX(B10-F5,0.01)/(1+B10)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="G10" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B10)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+G5)/MAX(B10-G5,0.01)/(1+B10)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="H10" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B10)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+H5)/MAX(B10-H5,0.01)/(1+B10)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="B11" s="59">
+      <c r="B11" s="62">
         <f>'DCF Valuation'!C4+(0.01)</f>
         <v/>
       </c>
-      <c r="C11" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B11)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+C5)/MAX(B11-C5,0.0001)/(1+B11)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
-        <v/>
-      </c>
-      <c r="D11" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B11)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+D5)/MAX(B11-D5,0.0001)/(1+B11)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
-        <v/>
-      </c>
-      <c r="E11" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B11)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+E5)/MAX(B11-E5,0.0001)/(1+B11)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
-        <v/>
-      </c>
-      <c r="F11" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B11)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+F5)/MAX(B11-F5,0.0001)/(1+B11)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
-        <v/>
-      </c>
-      <c r="G11" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B11)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+G5)/MAX(B11-G5,0.0001)/(1+B11)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
-        <v/>
-      </c>
-      <c r="H11" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B11)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+H5)/MAX(B11-H5,0.0001)/(1+B11)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+      <c r="C11" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B11)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+C5)/MAX(B11-C5,0.01)/(1+B11)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="D11" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B11)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+D5)/MAX(B11-D5,0.01)/(1+B11)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="E11" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B11)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+E5)/MAX(B11-E5,0.01)/(1+B11)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="F11" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B11)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+F5)/MAX(B11-F5,0.01)/(1+B11)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="G11" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B11)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+G5)/MAX(B11-G5,0.01)/(1+B11)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="H11" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B11)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+H5)/MAX(B11-H5,0.01)/(1+B11)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="B12" s="59">
+      <c r="B12" s="62">
         <f>'DCF Valuation'!C4+(0.015)</f>
         <v/>
       </c>
-      <c r="C12" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B12)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+C5)/MAX(B12-C5,0.0001)/(1+B12)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
-        <v/>
-      </c>
-      <c r="D12" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B12)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+D5)/MAX(B12-D5,0.0001)/(1+B12)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
-        <v/>
-      </c>
-      <c r="E12" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B12)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+E5)/MAX(B12-E5,0.0001)/(1+B12)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
-        <v/>
-      </c>
-      <c r="F12" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B12)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+F5)/MAX(B12-F5,0.0001)/(1+B12)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
-        <v/>
-      </c>
-      <c r="G12" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B12)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+G5)/MAX(B12-G5,0.0001)/(1+B12)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
-        <v/>
-      </c>
-      <c r="H12" s="53">
-        <f>IFERROR((SUMPRODUCT('Income Statement'!F29:O29,1/(1+B12)^{1,2,3,4,5,6,7,8,9,10})+'Income Statement'!O29*(1+H5)/MAX(B12-H5,0.0001)/(1+B12)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+      <c r="C12" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B12)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+C5)/MAX(B12-C5,0.01)/(1+B12)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="D12" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B12)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+D5)/MAX(B12-D5,0.01)/(1+B12)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="E12" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B12)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+E5)/MAX(B12-E5,0.01)/(1+B12)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="F12" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B12)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+F5)/MAX(B12-F5,0.01)/(1+B12)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="G12" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B12)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+G5)/MAX(B12-G5,0.01)/(1+B12)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="H12" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT('Income Statement'!F29:O29,1/(1+B12)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+'Income Statement'!O29*(1+H5)/MAX(B12-H5,0.01)/(1+B12)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="B14" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  TABLE 2 - Implied Share Price  vs  EBITDA Margin  x  Y1 Revenue Growth</t>
-        </is>
-      </c>
-      <c r="C14" s="72" t="n"/>
-      <c r="D14" s="72" t="n"/>
-      <c r="E14" s="72" t="n"/>
-      <c r="F14" s="72" t="n"/>
-      <c r="G14" s="72" t="n"/>
-      <c r="H14" s="73" t="n"/>
+      <c r="B14" s="59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TABLE 2 - Implied Share Price  vs  EBITDA Margin  x  Uniform Revenue Growth  [full DCF re-calc per cell; growth applied to all 10 yrs]</t>
+        </is>
+      </c>
+      <c r="C14" s="75" t="n"/>
+      <c r="D14" s="75" t="n"/>
+      <c r="E14" s="75" t="n"/>
+      <c r="F14" s="75" t="n"/>
+      <c r="G14" s="75" t="n"/>
+      <c r="H14" s="76" t="n"/>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="B15" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Rev Gr\EBITDA%</t>
-        </is>
-      </c>
-      <c r="C15" s="60">
+      <c r="B15" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Gr\EBITDA%</t>
+        </is>
+      </c>
+      <c r="C15" s="63">
         <f>Assumptions!E16+(-0.04)</f>
         <v/>
       </c>
-      <c r="D15" s="60">
+      <c r="D15" s="63">
         <f>Assumptions!E16+(-0.02)</f>
         <v/>
       </c>
-      <c r="E15" s="60">
+      <c r="E15" s="63">
         <f>Assumptions!E16+(0.0)</f>
         <v/>
       </c>
-      <c r="F15" s="60">
+      <c r="F15" s="63">
         <f>Assumptions!E16+(0.02)</f>
         <v/>
       </c>
-      <c r="G15" s="60">
+      <c r="G15" s="63">
         <f>Assumptions!E16+(0.04)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
-      <c r="B16" s="61">
+      <c r="B16" s="64">
         <f>Assumptions!C10+(-0.03)</f>
         <v/>
       </c>
-      <c r="C16" s="53">
-        <f>IFERROR('DCF Valuation'!C26*((1+B16)/(1+Assumptions!C10))*(C15/Assumptions!E16),"—")</f>
-        <v/>
-      </c>
-      <c r="D16" s="53">
-        <f>IFERROR('DCF Valuation'!C26*((1+B16)/(1+Assumptions!C10))*(D15/Assumptions!E16),"—")</f>
-        <v/>
-      </c>
-      <c r="E16" s="53">
-        <f>IFERROR('DCF Valuation'!C26*((1+B16)/(1+Assumptions!C10))*(E15/Assumptions!E16),"—")</f>
-        <v/>
-      </c>
-      <c r="F16" s="53">
-        <f>IFERROR('DCF Valuation'!C26*((1+B16)/(1+Assumptions!C10))*(F15/Assumptions!E16),"—")</f>
-        <v/>
-      </c>
-      <c r="G16" s="53">
-        <f>IFERROR('DCF Valuation'!C26*((1+B16)/(1+Assumptions!C10))*(G15/Assumptions!E16),"—")</f>
+      <c r="C16" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT((Assumptions!C28)*(((C15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B16)/(1+(B16))+(Assumptions!C19)*(Assumptions!E31))*(1+(B16))^{1,2,3,4,5,6,7,8,9,10},1/(1+'DCF Valuation'!C4)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+(Assumptions!C28)*(((C15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B16)/(1+(B16))+(Assumptions!C19)*(Assumptions!E31))*(1+(B16))^10*(1+('DCF Valuation'!C5))/MAX('DCF Valuation'!C4-('DCF Valuation'!C5),0.01)/(1+'DCF Valuation'!C4)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="D16" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT((Assumptions!C28)*(((D15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B16)/(1+(B16))+(Assumptions!C19)*(Assumptions!E31))*(1+(B16))^{1,2,3,4,5,6,7,8,9,10},1/(1+'DCF Valuation'!C4)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+(Assumptions!C28)*(((D15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B16)/(1+(B16))+(Assumptions!C19)*(Assumptions!E31))*(1+(B16))^10*(1+('DCF Valuation'!C5))/MAX('DCF Valuation'!C4-('DCF Valuation'!C5),0.01)/(1+'DCF Valuation'!C4)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="E16" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT((Assumptions!C28)*(((E15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B16)/(1+(B16))+(Assumptions!C19)*(Assumptions!E31))*(1+(B16))^{1,2,3,4,5,6,7,8,9,10},1/(1+'DCF Valuation'!C4)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+(Assumptions!C28)*(((E15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B16)/(1+(B16))+(Assumptions!C19)*(Assumptions!E31))*(1+(B16))^10*(1+('DCF Valuation'!C5))/MAX('DCF Valuation'!C4-('DCF Valuation'!C5),0.01)/(1+'DCF Valuation'!C4)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="F16" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT((Assumptions!C28)*(((F15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B16)/(1+(B16))+(Assumptions!C19)*(Assumptions!E31))*(1+(B16))^{1,2,3,4,5,6,7,8,9,10},1/(1+'DCF Valuation'!C4)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+(Assumptions!C28)*(((F15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B16)/(1+(B16))+(Assumptions!C19)*(Assumptions!E31))*(1+(B16))^10*(1+('DCF Valuation'!C5))/MAX('DCF Valuation'!C4-('DCF Valuation'!C5),0.01)/(1+'DCF Valuation'!C4)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="G16" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT((Assumptions!C28)*(((G15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B16)/(1+(B16))+(Assumptions!C19)*(Assumptions!E31))*(1+(B16))^{1,2,3,4,5,6,7,8,9,10},1/(1+'DCF Valuation'!C4)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+(Assumptions!C28)*(((G15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B16)/(1+(B16))+(Assumptions!C19)*(Assumptions!E31))*(1+(B16))^10*(1+('DCF Valuation'!C5))/MAX('DCF Valuation'!C4-('DCF Valuation'!C5),0.01)/(1+'DCF Valuation'!C4)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
-      <c r="B17" s="61">
+      <c r="B17" s="64">
         <f>Assumptions!C10+(-0.02)</f>
         <v/>
       </c>
-      <c r="C17" s="53">
-        <f>IFERROR('DCF Valuation'!C26*((1+B17)/(1+Assumptions!C10))*(C15/Assumptions!E16),"—")</f>
-        <v/>
-      </c>
-      <c r="D17" s="53">
-        <f>IFERROR('DCF Valuation'!C26*((1+B17)/(1+Assumptions!C10))*(D15/Assumptions!E16),"—")</f>
-        <v/>
-      </c>
-      <c r="E17" s="53">
-        <f>IFERROR('DCF Valuation'!C26*((1+B17)/(1+Assumptions!C10))*(E15/Assumptions!E16),"—")</f>
-        <v/>
-      </c>
-      <c r="F17" s="53">
-        <f>IFERROR('DCF Valuation'!C26*((1+B17)/(1+Assumptions!C10))*(F15/Assumptions!E16),"—")</f>
-        <v/>
-      </c>
-      <c r="G17" s="53">
-        <f>IFERROR('DCF Valuation'!C26*((1+B17)/(1+Assumptions!C10))*(G15/Assumptions!E16),"—")</f>
+      <c r="C17" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT((Assumptions!C28)*(((C15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B17)/(1+(B17))+(Assumptions!C19)*(Assumptions!E31))*(1+(B17))^{1,2,3,4,5,6,7,8,9,10},1/(1+'DCF Valuation'!C4)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+(Assumptions!C28)*(((C15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B17)/(1+(B17))+(Assumptions!C19)*(Assumptions!E31))*(1+(B17))^10*(1+('DCF Valuation'!C5))/MAX('DCF Valuation'!C4-('DCF Valuation'!C5),0.01)/(1+'DCF Valuation'!C4)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="D17" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT((Assumptions!C28)*(((D15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B17)/(1+(B17))+(Assumptions!C19)*(Assumptions!E31))*(1+(B17))^{1,2,3,4,5,6,7,8,9,10},1/(1+'DCF Valuation'!C4)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+(Assumptions!C28)*(((D15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B17)/(1+(B17))+(Assumptions!C19)*(Assumptions!E31))*(1+(B17))^10*(1+('DCF Valuation'!C5))/MAX('DCF Valuation'!C4-('DCF Valuation'!C5),0.01)/(1+'DCF Valuation'!C4)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="E17" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT((Assumptions!C28)*(((E15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B17)/(1+(B17))+(Assumptions!C19)*(Assumptions!E31))*(1+(B17))^{1,2,3,4,5,6,7,8,9,10},1/(1+'DCF Valuation'!C4)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+(Assumptions!C28)*(((E15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B17)/(1+(B17))+(Assumptions!C19)*(Assumptions!E31))*(1+(B17))^10*(1+('DCF Valuation'!C5))/MAX('DCF Valuation'!C4-('DCF Valuation'!C5),0.01)/(1+'DCF Valuation'!C4)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="F17" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT((Assumptions!C28)*(((F15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B17)/(1+(B17))+(Assumptions!C19)*(Assumptions!E31))*(1+(B17))^{1,2,3,4,5,6,7,8,9,10},1/(1+'DCF Valuation'!C4)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+(Assumptions!C28)*(((F15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B17)/(1+(B17))+(Assumptions!C19)*(Assumptions!E31))*(1+(B17))^10*(1+('DCF Valuation'!C5))/MAX('DCF Valuation'!C4-('DCF Valuation'!C5),0.01)/(1+'DCF Valuation'!C4)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="G17" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT((Assumptions!C28)*(((G15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B17)/(1+(B17))+(Assumptions!C19)*(Assumptions!E31))*(1+(B17))^{1,2,3,4,5,6,7,8,9,10},1/(1+'DCF Valuation'!C4)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+(Assumptions!C28)*(((G15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B17)/(1+(B17))+(Assumptions!C19)*(Assumptions!E31))*(1+(B17))^10*(1+('DCF Valuation'!C5))/MAX('DCF Valuation'!C4-('DCF Valuation'!C5),0.01)/(1+'DCF Valuation'!C4)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="17" customHeight="1">
-      <c r="B18" s="61">
+      <c r="B18" s="64">
         <f>Assumptions!C10+(-0.01)</f>
         <v/>
       </c>
-      <c r="C18" s="53">
-        <f>IFERROR('DCF Valuation'!C26*((1+B18)/(1+Assumptions!C10))*(C15/Assumptions!E16),"—")</f>
-        <v/>
-      </c>
-      <c r="D18" s="53">
-        <f>IFERROR('DCF Valuation'!C26*((1+B18)/(1+Assumptions!C10))*(D15/Assumptions!E16),"—")</f>
-        <v/>
-      </c>
-      <c r="E18" s="53">
-        <f>IFERROR('DCF Valuation'!C26*((1+B18)/(1+Assumptions!C10))*(E15/Assumptions!E16),"—")</f>
-        <v/>
-      </c>
-      <c r="F18" s="53">
-        <f>IFERROR('DCF Valuation'!C26*((1+B18)/(1+Assumptions!C10))*(F15/Assumptions!E16),"—")</f>
-        <v/>
-      </c>
-      <c r="G18" s="53">
-        <f>IFERROR('DCF Valuation'!C26*((1+B18)/(1+Assumptions!C10))*(G15/Assumptions!E16),"—")</f>
+      <c r="C18" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT((Assumptions!C28)*(((C15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B18)/(1+(B18))+(Assumptions!C19)*(Assumptions!E31))*(1+(B18))^{1,2,3,4,5,6,7,8,9,10},1/(1+'DCF Valuation'!C4)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+(Assumptions!C28)*(((C15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B18)/(1+(B18))+(Assumptions!C19)*(Assumptions!E31))*(1+(B18))^10*(1+('DCF Valuation'!C5))/MAX('DCF Valuation'!C4-('DCF Valuation'!C5),0.01)/(1+'DCF Valuation'!C4)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="D18" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT((Assumptions!C28)*(((D15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B18)/(1+(B18))+(Assumptions!C19)*(Assumptions!E31))*(1+(B18))^{1,2,3,4,5,6,7,8,9,10},1/(1+'DCF Valuation'!C4)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+(Assumptions!C28)*(((D15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B18)/(1+(B18))+(Assumptions!C19)*(Assumptions!E31))*(1+(B18))^10*(1+('DCF Valuation'!C5))/MAX('DCF Valuation'!C4-('DCF Valuation'!C5),0.01)/(1+'DCF Valuation'!C4)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="E18" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT((Assumptions!C28)*(((E15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B18)/(1+(B18))+(Assumptions!C19)*(Assumptions!E31))*(1+(B18))^{1,2,3,4,5,6,7,8,9,10},1/(1+'DCF Valuation'!C4)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+(Assumptions!C28)*(((E15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B18)/(1+(B18))+(Assumptions!C19)*(Assumptions!E31))*(1+(B18))^10*(1+('DCF Valuation'!C5))/MAX('DCF Valuation'!C4-('DCF Valuation'!C5),0.01)/(1+'DCF Valuation'!C4)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="F18" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT((Assumptions!C28)*(((F15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B18)/(1+(B18))+(Assumptions!C19)*(Assumptions!E31))*(1+(B18))^{1,2,3,4,5,6,7,8,9,10},1/(1+'DCF Valuation'!C4)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+(Assumptions!C28)*(((F15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B18)/(1+(B18))+(Assumptions!C19)*(Assumptions!E31))*(1+(B18))^10*(1+('DCF Valuation'!C5))/MAX('DCF Valuation'!C4-('DCF Valuation'!C5),0.01)/(1+'DCF Valuation'!C4)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="G18" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT((Assumptions!C28)*(((G15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B18)/(1+(B18))+(Assumptions!C19)*(Assumptions!E31))*(1+(B18))^{1,2,3,4,5,6,7,8,9,10},1/(1+'DCF Valuation'!C4)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+(Assumptions!C28)*(((G15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B18)/(1+(B18))+(Assumptions!C19)*(Assumptions!E31))*(1+(B18))^10*(1+('DCF Valuation'!C5))/MAX('DCF Valuation'!C4-('DCF Valuation'!C5),0.01)/(1+'DCF Valuation'!C4)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="17" customHeight="1">
-      <c r="B19" s="61">
+      <c r="B19" s="64">
         <f>Assumptions!C10+(0.0)</f>
         <v/>
       </c>
-      <c r="C19" s="53">
-        <f>IFERROR('DCF Valuation'!C26*((1+B19)/(1+Assumptions!C10))*(C15/Assumptions!E16),"—")</f>
-        <v/>
-      </c>
-      <c r="D19" s="53">
-        <f>IFERROR('DCF Valuation'!C26*((1+B19)/(1+Assumptions!C10))*(D15/Assumptions!E16),"—")</f>
-        <v/>
-      </c>
-      <c r="E19" s="53">
-        <f>IFERROR('DCF Valuation'!C26*((1+B19)/(1+Assumptions!C10))*(E15/Assumptions!E16),"—")</f>
-        <v/>
-      </c>
-      <c r="F19" s="53">
-        <f>IFERROR('DCF Valuation'!C26*((1+B19)/(1+Assumptions!C10))*(F15/Assumptions!E16),"—")</f>
-        <v/>
-      </c>
-      <c r="G19" s="53">
-        <f>IFERROR('DCF Valuation'!C26*((1+B19)/(1+Assumptions!C10))*(G15/Assumptions!E16),"—")</f>
+      <c r="C19" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT((Assumptions!C28)*(((C15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B19)/(1+(B19))+(Assumptions!C19)*(Assumptions!E31))*(1+(B19))^{1,2,3,4,5,6,7,8,9,10},1/(1+'DCF Valuation'!C4)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+(Assumptions!C28)*(((C15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B19)/(1+(B19))+(Assumptions!C19)*(Assumptions!E31))*(1+(B19))^10*(1+('DCF Valuation'!C5))/MAX('DCF Valuation'!C4-('DCF Valuation'!C5),0.01)/(1+'DCF Valuation'!C4)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="D19" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT((Assumptions!C28)*(((D15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B19)/(1+(B19))+(Assumptions!C19)*(Assumptions!E31))*(1+(B19))^{1,2,3,4,5,6,7,8,9,10},1/(1+'DCF Valuation'!C4)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+(Assumptions!C28)*(((D15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B19)/(1+(B19))+(Assumptions!C19)*(Assumptions!E31))*(1+(B19))^10*(1+('DCF Valuation'!C5))/MAX('DCF Valuation'!C4-('DCF Valuation'!C5),0.01)/(1+'DCF Valuation'!C4)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="E19" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT((Assumptions!C28)*(((E15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B19)/(1+(B19))+(Assumptions!C19)*(Assumptions!E31))*(1+(B19))^{1,2,3,4,5,6,7,8,9,10},1/(1+'DCF Valuation'!C4)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+(Assumptions!C28)*(((E15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B19)/(1+(B19))+(Assumptions!C19)*(Assumptions!E31))*(1+(B19))^10*(1+('DCF Valuation'!C5))/MAX('DCF Valuation'!C4-('DCF Valuation'!C5),0.01)/(1+'DCF Valuation'!C4)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="F19" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT((Assumptions!C28)*(((F15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B19)/(1+(B19))+(Assumptions!C19)*(Assumptions!E31))*(1+(B19))^{1,2,3,4,5,6,7,8,9,10},1/(1+'DCF Valuation'!C4)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+(Assumptions!C28)*(((F15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B19)/(1+(B19))+(Assumptions!C19)*(Assumptions!E31))*(1+(B19))^10*(1+('DCF Valuation'!C5))/MAX('DCF Valuation'!C4-('DCF Valuation'!C5),0.01)/(1+'DCF Valuation'!C4)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="G19" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT((Assumptions!C28)*(((G15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B19)/(1+(B19))+(Assumptions!C19)*(Assumptions!E31))*(1+(B19))^{1,2,3,4,5,6,7,8,9,10},1/(1+'DCF Valuation'!C4)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+(Assumptions!C28)*(((G15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B19)/(1+(B19))+(Assumptions!C19)*(Assumptions!E31))*(1+(B19))^10*(1+('DCF Valuation'!C5))/MAX('DCF Valuation'!C4-('DCF Valuation'!C5),0.01)/(1+'DCF Valuation'!C4)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
-      <c r="B20" s="61">
+      <c r="B20" s="64">
         <f>Assumptions!C10+(0.01)</f>
         <v/>
       </c>
-      <c r="C20" s="53">
-        <f>IFERROR('DCF Valuation'!C26*((1+B20)/(1+Assumptions!C10))*(C15/Assumptions!E16),"—")</f>
-        <v/>
-      </c>
-      <c r="D20" s="53">
-        <f>IFERROR('DCF Valuation'!C26*((1+B20)/(1+Assumptions!C10))*(D15/Assumptions!E16),"—")</f>
-        <v/>
-      </c>
-      <c r="E20" s="53">
-        <f>IFERROR('DCF Valuation'!C26*((1+B20)/(1+Assumptions!C10))*(E15/Assumptions!E16),"—")</f>
-        <v/>
-      </c>
-      <c r="F20" s="53">
-        <f>IFERROR('DCF Valuation'!C26*((1+B20)/(1+Assumptions!C10))*(F15/Assumptions!E16),"—")</f>
-        <v/>
-      </c>
-      <c r="G20" s="53">
-        <f>IFERROR('DCF Valuation'!C26*((1+B20)/(1+Assumptions!C10))*(G15/Assumptions!E16),"—")</f>
+      <c r="C20" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT((Assumptions!C28)*(((C15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B20)/(1+(B20))+(Assumptions!C19)*(Assumptions!E31))*(1+(B20))^{1,2,3,4,5,6,7,8,9,10},1/(1+'DCF Valuation'!C4)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+(Assumptions!C28)*(((C15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B20)/(1+(B20))+(Assumptions!C19)*(Assumptions!E31))*(1+(B20))^10*(1+('DCF Valuation'!C5))/MAX('DCF Valuation'!C4-('DCF Valuation'!C5),0.01)/(1+'DCF Valuation'!C4)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="D20" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT((Assumptions!C28)*(((D15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B20)/(1+(B20))+(Assumptions!C19)*(Assumptions!E31))*(1+(B20))^{1,2,3,4,5,6,7,8,9,10},1/(1+'DCF Valuation'!C4)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+(Assumptions!C28)*(((D15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B20)/(1+(B20))+(Assumptions!C19)*(Assumptions!E31))*(1+(B20))^10*(1+('DCF Valuation'!C5))/MAX('DCF Valuation'!C4-('DCF Valuation'!C5),0.01)/(1+'DCF Valuation'!C4)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="E20" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT((Assumptions!C28)*(((E15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B20)/(1+(B20))+(Assumptions!C19)*(Assumptions!E31))*(1+(B20))^{1,2,3,4,5,6,7,8,9,10},1/(1+'DCF Valuation'!C4)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+(Assumptions!C28)*(((E15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B20)/(1+(B20))+(Assumptions!C19)*(Assumptions!E31))*(1+(B20))^10*(1+('DCF Valuation'!C5))/MAX('DCF Valuation'!C4-('DCF Valuation'!C5),0.01)/(1+'DCF Valuation'!C4)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="F20" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT((Assumptions!C28)*(((F15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B20)/(1+(B20))+(Assumptions!C19)*(Assumptions!E31))*(1+(B20))^{1,2,3,4,5,6,7,8,9,10},1/(1+'DCF Valuation'!C4)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+(Assumptions!C28)*(((F15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B20)/(1+(B20))+(Assumptions!C19)*(Assumptions!E31))*(1+(B20))^10*(1+('DCF Valuation'!C5))/MAX('DCF Valuation'!C4-('DCF Valuation'!C5),0.01)/(1+'DCF Valuation'!C4)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="G20" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT((Assumptions!C28)*(((G15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B20)/(1+(B20))+(Assumptions!C19)*(Assumptions!E31))*(1+(B20))^{1,2,3,4,5,6,7,8,9,10},1/(1+'DCF Valuation'!C4)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+(Assumptions!C28)*(((G15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B20)/(1+(B20))+(Assumptions!C19)*(Assumptions!E31))*(1+(B20))^10*(1+('DCF Valuation'!C5))/MAX('DCF Valuation'!C4-('DCF Valuation'!C5),0.01)/(1+'DCF Valuation'!C4)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
-      <c r="B21" s="61">
+      <c r="B21" s="64">
         <f>Assumptions!C10+(0.02)</f>
         <v/>
       </c>
-      <c r="C21" s="53">
-        <f>IFERROR('DCF Valuation'!C26*((1+B21)/(1+Assumptions!C10))*(C15/Assumptions!E16),"—")</f>
-        <v/>
-      </c>
-      <c r="D21" s="53">
-        <f>IFERROR('DCF Valuation'!C26*((1+B21)/(1+Assumptions!C10))*(D15/Assumptions!E16),"—")</f>
-        <v/>
-      </c>
-      <c r="E21" s="53">
-        <f>IFERROR('DCF Valuation'!C26*((1+B21)/(1+Assumptions!C10))*(E15/Assumptions!E16),"—")</f>
-        <v/>
-      </c>
-      <c r="F21" s="53">
-        <f>IFERROR('DCF Valuation'!C26*((1+B21)/(1+Assumptions!C10))*(F15/Assumptions!E16),"—")</f>
-        <v/>
-      </c>
-      <c r="G21" s="53">
-        <f>IFERROR('DCF Valuation'!C26*((1+B21)/(1+Assumptions!C10))*(G15/Assumptions!E16),"—")</f>
+      <c r="C21" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT((Assumptions!C28)*(((C15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B21)/(1+(B21))+(Assumptions!C19)*(Assumptions!E31))*(1+(B21))^{1,2,3,4,5,6,7,8,9,10},1/(1+'DCF Valuation'!C4)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+(Assumptions!C28)*(((C15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B21)/(1+(B21))+(Assumptions!C19)*(Assumptions!E31))*(1+(B21))^10*(1+('DCF Valuation'!C5))/MAX('DCF Valuation'!C4-('DCF Valuation'!C5),0.01)/(1+'DCF Valuation'!C4)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="D21" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT((Assumptions!C28)*(((D15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B21)/(1+(B21))+(Assumptions!C19)*(Assumptions!E31))*(1+(B21))^{1,2,3,4,5,6,7,8,9,10},1/(1+'DCF Valuation'!C4)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+(Assumptions!C28)*(((D15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B21)/(1+(B21))+(Assumptions!C19)*(Assumptions!E31))*(1+(B21))^10*(1+('DCF Valuation'!C5))/MAX('DCF Valuation'!C4-('DCF Valuation'!C5),0.01)/(1+'DCF Valuation'!C4)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="E21" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT((Assumptions!C28)*(((E15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B21)/(1+(B21))+(Assumptions!C19)*(Assumptions!E31))*(1+(B21))^{1,2,3,4,5,6,7,8,9,10},1/(1+'DCF Valuation'!C4)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+(Assumptions!C28)*(((E15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B21)/(1+(B21))+(Assumptions!C19)*(Assumptions!E31))*(1+(B21))^10*(1+('DCF Valuation'!C5))/MAX('DCF Valuation'!C4-('DCF Valuation'!C5),0.01)/(1+'DCF Valuation'!C4)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="F21" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT((Assumptions!C28)*(((F15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B21)/(1+(B21))+(Assumptions!C19)*(Assumptions!E31))*(1+(B21))^{1,2,3,4,5,6,7,8,9,10},1/(1+'DCF Valuation'!C4)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+(Assumptions!C28)*(((F15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B21)/(1+(B21))+(Assumptions!C19)*(Assumptions!E31))*(1+(B21))^10*(1+('DCF Valuation'!C5))/MAX('DCF Valuation'!C4-('DCF Valuation'!C5),0.01)/(1+'DCF Valuation'!C4)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="G21" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT((Assumptions!C28)*(((G15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B21)/(1+(B21))+(Assumptions!C19)*(Assumptions!E31))*(1+(B21))^{1,2,3,4,5,6,7,8,9,10},1/(1+'DCF Valuation'!C4)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+(Assumptions!C28)*(((G15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B21)/(1+(B21))+(Assumptions!C19)*(Assumptions!E31))*(1+(B21))^10*(1+('DCF Valuation'!C5))/MAX('DCF Valuation'!C4-('DCF Valuation'!C5),0.01)/(1+'DCF Valuation'!C4)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1">
-      <c r="B22" s="61">
+      <c r="B22" s="64">
         <f>Assumptions!C10+(0.03)</f>
         <v/>
       </c>
-      <c r="C22" s="53">
-        <f>IFERROR('DCF Valuation'!C26*((1+B22)/(1+Assumptions!C10))*(C15/Assumptions!E16),"—")</f>
-        <v/>
-      </c>
-      <c r="D22" s="53">
-        <f>IFERROR('DCF Valuation'!C26*((1+B22)/(1+Assumptions!C10))*(D15/Assumptions!E16),"—")</f>
-        <v/>
-      </c>
-      <c r="E22" s="53">
-        <f>IFERROR('DCF Valuation'!C26*((1+B22)/(1+Assumptions!C10))*(E15/Assumptions!E16),"—")</f>
-        <v/>
-      </c>
-      <c r="F22" s="53">
-        <f>IFERROR('DCF Valuation'!C26*((1+B22)/(1+Assumptions!C10))*(F15/Assumptions!E16),"—")</f>
-        <v/>
-      </c>
-      <c r="G22" s="53">
-        <f>IFERROR('DCF Valuation'!C26*((1+B22)/(1+Assumptions!C10))*(G15/Assumptions!E16),"—")</f>
+      <c r="C22" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT((Assumptions!C28)*(((C15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B22)/(1+(B22))+(Assumptions!C19)*(Assumptions!E31))*(1+(B22))^{1,2,3,4,5,6,7,8,9,10},1/(1+'DCF Valuation'!C4)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+(Assumptions!C28)*(((C15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B22)/(1+(B22))+(Assumptions!C19)*(Assumptions!E31))*(1+(B22))^10*(1+('DCF Valuation'!C5))/MAX('DCF Valuation'!C4-('DCF Valuation'!C5),0.01)/(1+'DCF Valuation'!C4)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="D22" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT((Assumptions!C28)*(((D15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B22)/(1+(B22))+(Assumptions!C19)*(Assumptions!E31))*(1+(B22))^{1,2,3,4,5,6,7,8,9,10},1/(1+'DCF Valuation'!C4)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+(Assumptions!C28)*(((D15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B22)/(1+(B22))+(Assumptions!C19)*(Assumptions!E31))*(1+(B22))^10*(1+('DCF Valuation'!C5))/MAX('DCF Valuation'!C4-('DCF Valuation'!C5),0.01)/(1+'DCF Valuation'!C4)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="E22" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT((Assumptions!C28)*(((E15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B22)/(1+(B22))+(Assumptions!C19)*(Assumptions!E31))*(1+(B22))^{1,2,3,4,5,6,7,8,9,10},1/(1+'DCF Valuation'!C4)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+(Assumptions!C28)*(((E15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B22)/(1+(B22))+(Assumptions!C19)*(Assumptions!E31))*(1+(B22))^10*(1+('DCF Valuation'!C5))/MAX('DCF Valuation'!C4-('DCF Valuation'!C5),0.01)/(1+'DCF Valuation'!C4)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="F22" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT((Assumptions!C28)*(((F15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B22)/(1+(B22))+(Assumptions!C19)*(Assumptions!E31))*(1+(B22))^{1,2,3,4,5,6,7,8,9,10},1/(1+'DCF Valuation'!C4)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+(Assumptions!C28)*(((F15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B22)/(1+(B22))+(Assumptions!C19)*(Assumptions!E31))*(1+(B22))^10*(1+('DCF Valuation'!C5))/MAX('DCF Valuation'!C4-('DCF Valuation'!C5),0.01)/(1+'DCF Valuation'!C4)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
+        <v/>
+      </c>
+      <c r="G22" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT((Assumptions!C28)*(((G15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B22)/(1+(B22))+(Assumptions!C19)*(Assumptions!E31))*(1+(B22))^{1,2,3,4,5,6,7,8,9,10},1/(1+'DCF Valuation'!C4)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+(Assumptions!C28)*(((G15)-(Assumptions!C17))*(1-(Assumptions!E18))+(Assumptions!C17)-(Assumptions!E17)-(Assumptions!C18)*(B22)/(1+(B22))+(Assumptions!C19)*(Assumptions!E31))*(1+(B22))^10*(1+('DCF Valuation'!C5))/MAX('DCF Valuation'!C4-('DCF Valuation'!C5),0.01)/(1+'DCF Valuation'!C4)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"—")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="B24" s="56" t="inlineStr">
+      <c r="B24" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">  FOOTBALL FIELD  -  Valuation Range Summary</t>
         </is>
       </c>
-      <c r="C24" s="72" t="n"/>
-      <c r="D24" s="72" t="n"/>
-      <c r="E24" s="72" t="n"/>
-      <c r="F24" s="72" t="n"/>
-      <c r="G24" s="72" t="n"/>
-      <c r="H24" s="73" t="n"/>
+      <c r="C24" s="75" t="n"/>
+      <c r="D24" s="75" t="n"/>
+      <c r="E24" s="75" t="n"/>
+      <c r="F24" s="75" t="n"/>
+      <c r="G24" s="75" t="n"/>
+      <c r="H24" s="76" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="B25" s="31" t="inlineStr">
+      <c r="B25" s="34" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="C25" s="31" t="inlineStr">
+      <c r="C25" s="34" t="inlineStr">
         <is>
           <t>Low ($)</t>
         </is>
       </c>
-      <c r="D25" s="31" t="inlineStr">
+      <c r="D25" s="34" t="inlineStr">
         <is>
           <t>High ($)</t>
         </is>
       </c>
-      <c r="E25" s="31" t="inlineStr">
+      <c r="E25" s="34" t="inlineStr">
         <is>
           <t>Current ($)</t>
         </is>
       </c>
-      <c r="F25" s="31" t="inlineStr">
+      <c r="F25" s="34" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -5120,15 +5199,15 @@
           <t xml:space="preserve">  DCF  (base case)</t>
         </is>
       </c>
-      <c r="C26" s="53">
+      <c r="C26" s="56">
         <f>'DCF Valuation'!C26</f>
         <v/>
       </c>
-      <c r="D26" s="53">
+      <c r="D26" s="56">
         <f>'DCF Valuation'!C26</f>
         <v/>
       </c>
-      <c r="E26" s="53">
+      <c r="E26" s="56">
         <f>Assumptions!C7</f>
         <v/>
       </c>
@@ -5141,94 +5220,70 @@
     <row r="27" ht="17" customHeight="1">
       <c r="B27" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  DCF  (bull: FCF+15%)</t>
-        </is>
-      </c>
-      <c r="C27" s="53">
-        <f>'DCF Valuation'!C26*1.12</f>
-        <v/>
-      </c>
-      <c r="D27" s="53">
-        <f>'DCF Valuation'!C26*1.22</f>
-        <v/>
-      </c>
-      <c r="E27" s="53">
+          <t xml:space="preserve">  DCF  scenarios (Bear→Bull)</t>
+        </is>
+      </c>
+      <c r="C27" s="56">
+        <f>Scenarios!C18</f>
+        <v/>
+      </c>
+      <c r="D27" s="56">
+        <f>Scenarios!E18</f>
+        <v/>
+      </c>
+      <c r="E27" s="56">
         <f>Assumptions!C7</f>
         <v/>
       </c>
       <c r="F27" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Upside scenario</t>
+          <t xml:space="preserve">  Linked from Scenarios sheet</t>
         </is>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  DCF  (bear: FCF-15%)</t>
-        </is>
-      </c>
-      <c r="C28" s="53">
-        <f>'DCF Valuation'!C26*0.78</f>
-        <v/>
-      </c>
-      <c r="D28" s="53">
-        <f>'DCF Valuation'!C26*0.90</f>
-        <v/>
-      </c>
-      <c r="E28" s="53">
+          <t xml:space="preserve">  EV/EBITDA  (18-22x fwd)</t>
+        </is>
+      </c>
+      <c r="C28" s="56">
+        <f>'Income Statement'!O13*(1+'DCF Valuation'!C5)*18/Assumptions!E7</f>
+        <v/>
+      </c>
+      <c r="D28" s="56">
+        <f>'Income Statement'!O13*(1+'DCF Valuation'!C5)*22/Assumptions!E7</f>
+        <v/>
+      </c>
+      <c r="E28" s="56">
         <f>Assumptions!C7</f>
         <v/>
       </c>
       <c r="F28" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Downside scenario</t>
+          <t xml:space="preserve">  Forward EBITDA × multiple</t>
         </is>
       </c>
     </row>
     <row r="29" ht="17" customHeight="1">
       <c r="B29" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EV/EBITDA  (18-22x LTM)</t>
-        </is>
-      </c>
-      <c r="C29" s="53">
-        <f>'Income Statement'!O13*18/Assumptions!E7</f>
-        <v/>
-      </c>
-      <c r="D29" s="53">
-        <f>'Income Statement'!O13*22/Assumptions!E7</f>
-        <v/>
-      </c>
-      <c r="E29" s="53">
+          <t xml:space="preserve">  Current price  (mkt)</t>
+        </is>
+      </c>
+      <c r="C29" s="56">
         <f>Assumptions!C7</f>
         <v/>
       </c>
+      <c r="D29" s="56">
+        <f>Assumptions!C7</f>
+        <v/>
+      </c>
+      <c r="E29" s="56">
+        <f>Assumptions!C7</f>
+        <v/>
+      </c>
       <c r="F29" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Exit multiple</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="17" customHeight="1">
-      <c r="B30" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Current price  (mkt)</t>
-        </is>
-      </c>
-      <c r="C30" s="53">
-        <f>Assumptions!C7</f>
-        <v/>
-      </c>
-      <c r="D30" s="53">
-        <f>Assumptions!C7</f>
-        <v/>
-      </c>
-      <c r="E30" s="53">
-        <f>Assumptions!C7</f>
-        <v/>
-      </c>
-      <c r="F30" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  Market quote</t>
         </is>
@@ -5302,22 +5357,22 @@
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="B4" s="62" t="inlineStr">
+      <c r="B4" s="65" t="inlineStr">
         <is>
           <t xml:space="preserve">  ASSUMPTION</t>
         </is>
       </c>
-      <c r="C4" s="63" t="inlineStr">
+      <c r="C4" s="66" t="inlineStr">
         <is>
           <t>BEAR</t>
         </is>
       </c>
-      <c r="D4" s="64" t="inlineStr">
+      <c r="D4" s="67" t="inlineStr">
         <is>
           <t>BASE</t>
         </is>
       </c>
-      <c r="E4" s="65" t="inlineStr">
+      <c r="E4" s="68" t="inlineStr">
         <is>
           <t>BULL</t>
         </is>
@@ -5329,9 +5384,9 @@
           <t xml:space="preserve">  REVENUE GROWTH</t>
         </is>
       </c>
-      <c r="C5" s="72" t="n"/>
-      <c r="D5" s="72" t="n"/>
-      <c r="E5" s="73" t="n"/>
+      <c r="C5" s="75" t="n"/>
+      <c r="D5" s="75" t="n"/>
+      <c r="E5" s="76" t="n"/>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="B6" s="18" t="inlineStr">
@@ -5339,15 +5394,17 @@
           <t xml:space="preserve">  Y1-Y5 Revenue Growth (avg)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D6" s="34">
+      <c r="C6" s="23">
+        <f>MAX((Assumptions!C10+Assumptions!E10+Assumptions!C11+Assumptions!E11+Assumptions!C12)/5-0.03,Assumptions!C26)</f>
+        <v/>
+      </c>
+      <c r="D6" s="23">
         <f>(Assumptions!C10+Assumptions!E10+Assumptions!C11+Assumptions!E11+Assumptions!C12)/5</f>
         <v/>
       </c>
-      <c r="E6" s="21" t="n">
-        <v>0.1</v>
+      <c r="E6" s="23">
+        <f>MIN((Assumptions!C10+Assumptions!E10+Assumptions!C11+Assumptions!E11+Assumptions!C12)/5+0.04,0.80)</f>
+        <v/>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
@@ -5356,15 +5413,17 @@
           <t xml:space="preserve">  Y6-Y10 Revenue Growth (avg)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="D7" s="34">
+      <c r="C7" s="23">
+        <f>MAX((Assumptions!E12+Assumptions!C13+Assumptions!E13+Assumptions!C14+Assumptions!E14)/5-0.02,Assumptions!C26)</f>
+        <v/>
+      </c>
+      <c r="D7" s="23">
         <f>(Assumptions!E12+Assumptions!C13+Assumptions!E13+Assumptions!C14+Assumptions!E14)/5</f>
         <v/>
       </c>
-      <c r="E7" s="21" t="n">
-        <v>0.06</v>
+      <c r="E7" s="23">
+        <f>MIN((Assumptions!E12+Assumptions!C13+Assumptions!E13+Assumptions!C14+Assumptions!E14)/5+0.03,0.60)</f>
+        <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
@@ -5373,9 +5432,9 @@
           <t xml:space="preserve">  MARGIN &amp; DISCOUNT RATE</t>
         </is>
       </c>
-      <c r="C8" s="72" t="n"/>
-      <c r="D8" s="72" t="n"/>
-      <c r="E8" s="73" t="n"/>
+      <c r="C8" s="75" t="n"/>
+      <c r="D8" s="75" t="n"/>
+      <c r="E8" s="76" t="n"/>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="B9" s="18" t="inlineStr">
@@ -5383,15 +5442,17 @@
           <t xml:space="preserve">  EBITDA Margin %</t>
         </is>
       </c>
-      <c r="C9" s="21" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="D9" s="34">
+      <c r="C9" s="23">
+        <f>MAX(Assumptions!E16-0.05,0.03)</f>
+        <v/>
+      </c>
+      <c r="D9" s="23">
         <f>Assumptions!E16</f>
         <v/>
       </c>
-      <c r="E9" s="21" t="n">
-        <v>0.4</v>
+      <c r="E9" s="23">
+        <f>MIN(Assumptions!E16+0.08,0.85)</f>
+        <v/>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
@@ -5400,15 +5461,17 @@
           <t xml:space="preserve">  FCF Margin (% of Revenue)</t>
         </is>
       </c>
-      <c r="C10" s="21" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="D10" s="34">
-        <f>(Assumptions!E16-Assumptions!E17-Assumptions!C18+Assumptions!C19)*(1-Assumptions!E18)</f>
-        <v/>
-      </c>
-      <c r="E10" s="21" t="n">
-        <v>0.27</v>
+      <c r="C10" s="23">
+        <f>MAX(0,(C9-Assumptions!C17)*(1-Assumptions!E18)+Assumptions!C17-Assumptions!E17-Assumptions!C18+Assumptions!C19*Assumptions!E31)</f>
+        <v/>
+      </c>
+      <c r="D10" s="23">
+        <f>MAX(0,(D9-Assumptions!C17)*(1-Assumptions!E18)+Assumptions!C17-Assumptions!E17-Assumptions!C18+Assumptions!C19*Assumptions!E31)</f>
+        <v/>
+      </c>
+      <c r="E10" s="23">
+        <f>MAX(0,(E9-Assumptions!C17)*(1-Assumptions!E18)+Assumptions!C17-Assumptions!E17-Assumptions!C18+Assumptions!C19*Assumptions!E31)</f>
+        <v/>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
@@ -5420,8 +5483,8 @@
       <c r="C11" s="21" t="n">
         <v>0.11</v>
       </c>
-      <c r="D11" s="34">
-        <f>WACC!E16</f>
+      <c r="D11" s="23">
+        <f>WACC!E17</f>
         <v/>
       </c>
       <c r="E11" s="21" t="n">
@@ -5437,7 +5500,7 @@
       <c r="C12" s="21" t="n">
         <v>0.02</v>
       </c>
-      <c r="D12" s="34">
+      <c r="D12" s="23">
         <f>Assumptions!C26</f>
         <v/>
       </c>
@@ -5451,9 +5514,9 @@
           <t xml:space="preserve">  COMMON INPUTS  (linked from model)</t>
         </is>
       </c>
-      <c r="C13" s="72" t="n"/>
-      <c r="D13" s="72" t="n"/>
-      <c r="E13" s="73" t="n"/>
+      <c r="C13" s="75" t="n"/>
+      <c r="D13" s="75" t="n"/>
+      <c r="E13" s="76" t="n"/>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="B14" s="18" t="inlineStr">
@@ -5518,26 +5581,26 @@
           <t xml:space="preserve">  VALUATION OUTPUT</t>
         </is>
       </c>
-      <c r="C17" s="72" t="n"/>
-      <c r="D17" s="72" t="n"/>
-      <c r="E17" s="73" t="n"/>
+      <c r="C17" s="75" t="n"/>
+      <c r="D17" s="75" t="n"/>
+      <c r="E17" s="76" t="n"/>
     </row>
     <row r="18" ht="28" customHeight="1">
-      <c r="B18" s="42" t="inlineStr">
+      <c r="B18" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">  IMPLIED SHARE PRICE</t>
         </is>
       </c>
-      <c r="C18" s="66">
-        <f>IFERROR((SUMPRODUCT(C14*C10*(1+C6)^{1,2,3,4,5},1/(1+C11)^{1,2,3,4,5})+SUMPRODUCT(C14*C10*(1+C6)^5*(1+C7)^{1,2,3,4,5},1/(1+C11)^{6,7,8,9,10})+C14*C10*(1+C6)^5*(1+C7)^5*(1+C12)/MAX(C11-C12,0.0001)/(1+C11)^10-C15)/C16,"--")</f>
-        <v/>
-      </c>
-      <c r="D18" s="67">
-        <f>IFERROR((SUMPRODUCT(D14*D10*(1+D6)^{1,2,3,4,5},1/(1+D11)^{1,2,3,4,5})+SUMPRODUCT(D14*D10*(1+D6)^5*(1+D7)^{1,2,3,4,5},1/(1+D11)^{6,7,8,9,10})+D14*D10*(1+D6)^5*(1+D7)^5*(1+D12)/MAX(D11-D12,0.0001)/(1+D11)^10-D15)/D16,"--")</f>
-        <v/>
-      </c>
-      <c r="E18" s="68">
-        <f>IFERROR((SUMPRODUCT(E14*E10*(1+E6)^{1,2,3,4,5},1/(1+E11)^{1,2,3,4,5})+SUMPRODUCT(E14*E10*(1+E6)^5*(1+E7)^{1,2,3,4,5},1/(1+E11)^{6,7,8,9,10})+E14*E10*(1+E6)^5*(1+E7)^5*(1+E12)/MAX(E11-E12,0.0001)/(1+E11)^10-E15)/E16,"--")</f>
+      <c r="C18" s="69">
+        <f>IFERROR(MAX(0,SUMPRODUCT(C14*C10*(1+C6)^{1,2,3,4,5},1/(1+C11)^({1,2,3,4,5}-Assumptions!C31))+SUMPRODUCT(C14*C10*(1+C6)^5*(1+C7)^{1,2,3,4,5},1/(1+C11)^({6,7,8,9,10}-Assumptions!C31))+C14*C10*(1+C6)^5*(1+C7)^5*(1+C12)/MAX(C11-C12,0.01)/(1+C11)^(10-Assumptions!C31)-C15)/C16,"--")</f>
+        <v/>
+      </c>
+      <c r="D18" s="70">
+        <f>IFERROR(MAX(0,SUMPRODUCT(D14*D10*(1+D6)^{1,2,3,4,5},1/(1+D11)^({1,2,3,4,5}-Assumptions!C31))+SUMPRODUCT(D14*D10*(1+D6)^5*(1+D7)^{1,2,3,4,5},1/(1+D11)^({6,7,8,9,10}-Assumptions!C31))+D14*D10*(1+D6)^5*(1+D7)^5*(1+D12)/MAX(D11-D12,0.01)/(1+D11)^(10-Assumptions!C31)-D15)/D16,"--")</f>
+        <v/>
+      </c>
+      <c r="E18" s="71">
+        <f>IFERROR(MAX(0,SUMPRODUCT(E14*E10*(1+E6)^{1,2,3,4,5},1/(1+E11)^({1,2,3,4,5}-Assumptions!C31))+SUMPRODUCT(E14*E10*(1+E6)^5*(1+E7)^{1,2,3,4,5},1/(1+E11)^({6,7,8,9,10}-Assumptions!C31))+E14*E10*(1+E6)^5*(1+E7)^5*(1+E12)/MAX(E11-E12,0.01)/(1+E11)^(10-Assumptions!C31)-E15)/E16,"--")</f>
         <v/>
       </c>
     </row>
@@ -5547,34 +5610,34 @@
           <t xml:space="preserve">  Current Market Price ($)</t>
         </is>
       </c>
-      <c r="C19" s="53">
+      <c r="C19" s="56">
         <f>Assumptions!C7</f>
         <v/>
       </c>
-      <c r="D19" s="53">
+      <c r="D19" s="56">
         <f>Assumptions!C7</f>
         <v/>
       </c>
-      <c r="E19" s="53">
+      <c r="E19" s="56">
         <f>Assumptions!C7</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  Upside / (Downside) %</t>
         </is>
       </c>
-      <c r="C20" s="69">
+      <c r="C20" s="72">
         <f>IFERROR((C18-D19)/D19,"--")</f>
         <v/>
       </c>
-      <c r="D20" s="54">
+      <c r="D20" s="57">
         <f>IFERROR((D18-D19)/D19,"--")</f>
         <v/>
       </c>
-      <c r="E20" s="70">
+      <c r="E20" s="73">
         <f>IFERROR((E18-D19)/D19,"--")</f>
         <v/>
       </c>
@@ -5585,9 +5648,9 @@
           <t xml:space="preserve">  EXPECTED VALUE SUMMARY</t>
         </is>
       </c>
-      <c r="C22" s="72" t="n"/>
-      <c r="D22" s="72" t="n"/>
-      <c r="E22" s="73" t="n"/>
+      <c r="C22" s="75" t="n"/>
+      <c r="D22" s="75" t="n"/>
+      <c r="E22" s="76" t="n"/>
     </row>
     <row r="23" ht="17" customHeight="1">
       <c r="B23" s="18" t="inlineStr">
@@ -5595,12 +5658,12 @@
           <t xml:space="preserve">  Equal-Weighted Avg Price ($)</t>
         </is>
       </c>
-      <c r="C23" s="71">
+      <c r="C23" s="74">
         <f>IFERROR((C18+D18+E18)/3,"--")</f>
         <v/>
       </c>
-      <c r="D23" s="72" t="n"/>
-      <c r="E23" s="73" t="n"/>
+      <c r="D23" s="75" t="n"/>
+      <c r="E23" s="76" t="n"/>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="B24" s="18" t="inlineStr">
@@ -5608,12 +5671,12 @@
           <t xml:space="preserve">  Expected Upside / (Downside) %</t>
         </is>
       </c>
-      <c r="C24" s="24">
+      <c r="C24" s="25">
         <f>IFERROR((C23-D19)/D19,"--")</f>
         <v/>
       </c>
-      <c r="D24" s="72" t="n"/>
-      <c r="E24" s="73" t="n"/>
+      <c r="D24" s="75" t="n"/>
+      <c r="E24" s="76" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -5638,20 +5701,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:K19"/>
+  <dimension ref="B1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -5664,17 +5728,17 @@
     <row r="2" ht="13" customHeight="1">
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Find the column where implied price = current market price. That growth rate is what the market is pricing in.</t>
+          <t xml:space="preserve">  Find the column where implied price = current market price. That growth rate is what the market is pricing in.  Range: 2% - 60% to cover both mature and high-growth companies.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="B4" s="74" t="inlineStr">
+      <c r="B4" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">  Target / Market Price ($)</t>
         </is>
       </c>
-      <c r="C4" s="73" t="n"/>
+      <c r="C4" s="76" t="n"/>
       <c r="D4" s="10">
         <f>Assumptions!C7</f>
         <v/>
@@ -5691,9 +5755,9 @@
           <t xml:space="preserve">  FCF Margin (model-derived)</t>
         </is>
       </c>
-      <c r="C5" s="73" t="n"/>
-      <c r="D5" s="34">
-        <f>(Assumptions!E16-Assumptions!E17-Assumptions!C18+Assumptions!C19)*(1-Assumptions!E18)</f>
+      <c r="C5" s="76" t="n"/>
+      <c r="D5" s="23">
+        <f>MAX(0,(Assumptions!E16-Assumptions!C17)*(1-Assumptions!E18)+Assumptions!C17-Assumptions!E17-Assumptions!C18+Assumptions!C19*Assumptions!E31)</f>
         <v/>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -5708,8 +5772,8 @@
           <t xml:space="preserve">  Terminal Growth Rate</t>
         </is>
       </c>
-      <c r="C6" s="73" t="n"/>
-      <c r="D6" s="34">
+      <c r="C6" s="76" t="n"/>
+      <c r="D6" s="23">
         <f>'DCF Valuation'!C5</f>
         <v/>
       </c>
@@ -5720,358 +5784,424 @@
           <t xml:space="preserve">  TABLE: Implied Share Price by Uniform Revenue Growth Rate x WACC -- find where implied price = market price</t>
         </is>
       </c>
-      <c r="C8" s="72" t="n"/>
-      <c r="D8" s="72" t="n"/>
-      <c r="E8" s="72" t="n"/>
-      <c r="F8" s="72" t="n"/>
-      <c r="G8" s="72" t="n"/>
-      <c r="H8" s="72" t="n"/>
-      <c r="I8" s="72" t="n"/>
-      <c r="J8" s="73" t="n"/>
+      <c r="C8" s="75" t="n"/>
+      <c r="D8" s="75" t="n"/>
+      <c r="E8" s="75" t="n"/>
+      <c r="F8" s="75" t="n"/>
+      <c r="G8" s="75" t="n"/>
+      <c r="H8" s="75" t="n"/>
+      <c r="I8" s="75" t="n"/>
+      <c r="J8" s="75" t="n"/>
+      <c r="K8" s="75" t="n"/>
+      <c r="L8" s="76" t="n"/>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="B9" s="57" t="inlineStr">
+      <c r="B9" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">  WACC \ Growth</t>
         </is>
       </c>
-      <c r="C9" s="75" t="n">
+      <c r="C9" s="78" t="n">
         <v>0.02</v>
       </c>
-      <c r="D9" s="75" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E9" s="75" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="F9" s="75" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G9" s="75" t="n">
+      <c r="D9" s="78" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E9" s="78" t="n">
         <v>0.1</v>
       </c>
-      <c r="H9" s="75" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I9" s="75" t="n">
+      <c r="F9" s="78" t="n">
         <v>0.15</v>
       </c>
-      <c r="J9" s="75" t="n">
+      <c r="G9" s="78" t="n">
         <v>0.2</v>
       </c>
+      <c r="H9" s="78" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I9" s="78" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J9" s="78" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K9" s="78" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L9" s="78" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="B10" s="59">
+      <c r="B10" s="62">
         <f>'DCF Valuation'!C4+(-0.015)</f>
         <v/>
       </c>
-      <c r="C10" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+C9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B10)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+C9)^10*(1+D6)/MAX(B10-D6,0.0001)/(1+B10)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="D10" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+D9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B10)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+D9)^10*(1+D6)/MAX(B10-D6,0.0001)/(1+B10)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="E10" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+E9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B10)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+E9)^10*(1+D6)/MAX(B10-D6,0.0001)/(1+B10)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="F10" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+F9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B10)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+F9)^10*(1+D6)/MAX(B10-D6,0.0001)/(1+B10)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="G10" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+G9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B10)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+G9)^10*(1+D6)/MAX(B10-D6,0.0001)/(1+B10)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="H10" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+H9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B10)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+H9)^10*(1+D6)/MAX(B10-D6,0.0001)/(1+B10)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="I10" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+I9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B10)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+I9)^10*(1+D6)/MAX(B10-D6,0.0001)/(1+B10)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="J10" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+J9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B10)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+J9)^10*(1+D6)/MAX(B10-D6,0.0001)/(1+B10)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+      <c r="C10" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+C9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B10)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+C9)^10*(1+D6)/MAX(B10-D6,0.01)/(1+B10)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="D10" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+D9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B10)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+D9)^10*(1+D6)/MAX(B10-D6,0.01)/(1+B10)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="E10" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+E9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B10)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+E9)^10*(1+D6)/MAX(B10-D6,0.01)/(1+B10)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="F10" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+F9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B10)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+F9)^10*(1+D6)/MAX(B10-D6,0.01)/(1+B10)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="G10" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+G9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B10)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+G9)^10*(1+D6)/MAX(B10-D6,0.01)/(1+B10)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="H10" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+H9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B10)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+H9)^10*(1+D6)/MAX(B10-D6,0.01)/(1+B10)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="I10" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+I9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B10)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+I9)^10*(1+D6)/MAX(B10-D6,0.01)/(1+B10)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="J10" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+J9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B10)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+J9)^10*(1+D6)/MAX(B10-D6,0.01)/(1+B10)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="K10" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+K9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B10)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+K9)^10*(1+D6)/MAX(B10-D6,0.01)/(1+B10)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="L10" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+L9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B10)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+L9)^10*(1+D6)/MAX(B10-D6,0.01)/(1+B10)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="B11" s="59">
+      <c r="B11" s="62">
         <f>'DCF Valuation'!C4+(-0.01)</f>
         <v/>
       </c>
-      <c r="C11" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+C9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B11)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+C9)^10*(1+D6)/MAX(B11-D6,0.0001)/(1+B11)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="D11" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+D9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B11)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+D9)^10*(1+D6)/MAX(B11-D6,0.0001)/(1+B11)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="E11" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+E9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B11)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+E9)^10*(1+D6)/MAX(B11-D6,0.0001)/(1+B11)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="F11" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+F9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B11)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+F9)^10*(1+D6)/MAX(B11-D6,0.0001)/(1+B11)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="G11" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+G9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B11)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+G9)^10*(1+D6)/MAX(B11-D6,0.0001)/(1+B11)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="H11" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+H9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B11)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+H9)^10*(1+D6)/MAX(B11-D6,0.0001)/(1+B11)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="I11" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+I9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B11)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+I9)^10*(1+D6)/MAX(B11-D6,0.0001)/(1+B11)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="J11" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+J9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B11)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+J9)^10*(1+D6)/MAX(B11-D6,0.0001)/(1+B11)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+      <c r="C11" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+C9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B11)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+C9)^10*(1+D6)/MAX(B11-D6,0.01)/(1+B11)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="D11" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+D9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B11)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+D9)^10*(1+D6)/MAX(B11-D6,0.01)/(1+B11)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="E11" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+E9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B11)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+E9)^10*(1+D6)/MAX(B11-D6,0.01)/(1+B11)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="F11" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+F9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B11)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+F9)^10*(1+D6)/MAX(B11-D6,0.01)/(1+B11)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="G11" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+G9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B11)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+G9)^10*(1+D6)/MAX(B11-D6,0.01)/(1+B11)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="H11" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+H9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B11)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+H9)^10*(1+D6)/MAX(B11-D6,0.01)/(1+B11)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="I11" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+I9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B11)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+I9)^10*(1+D6)/MAX(B11-D6,0.01)/(1+B11)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="J11" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+J9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B11)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+J9)^10*(1+D6)/MAX(B11-D6,0.01)/(1+B11)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="K11" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+K9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B11)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+K9)^10*(1+D6)/MAX(B11-D6,0.01)/(1+B11)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="L11" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+L9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B11)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+L9)^10*(1+D6)/MAX(B11-D6,0.01)/(1+B11)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="B12" s="59">
+      <c r="B12" s="62">
         <f>'DCF Valuation'!C4+(-0.005)</f>
         <v/>
       </c>
-      <c r="C12" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+C9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B12)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+C9)^10*(1+D6)/MAX(B12-D6,0.0001)/(1+B12)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="D12" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+D9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B12)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+D9)^10*(1+D6)/MAX(B12-D6,0.0001)/(1+B12)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="E12" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+E9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B12)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+E9)^10*(1+D6)/MAX(B12-D6,0.0001)/(1+B12)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="F12" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+F9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B12)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+F9)^10*(1+D6)/MAX(B12-D6,0.0001)/(1+B12)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="G12" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+G9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B12)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+G9)^10*(1+D6)/MAX(B12-D6,0.0001)/(1+B12)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="H12" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+H9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B12)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+H9)^10*(1+D6)/MAX(B12-D6,0.0001)/(1+B12)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="I12" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+I9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B12)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+I9)^10*(1+D6)/MAX(B12-D6,0.0001)/(1+B12)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="J12" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+J9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B12)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+J9)^10*(1+D6)/MAX(B12-D6,0.0001)/(1+B12)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+      <c r="C12" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+C9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B12)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+C9)^10*(1+D6)/MAX(B12-D6,0.01)/(1+B12)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="D12" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+D9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B12)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+D9)^10*(1+D6)/MAX(B12-D6,0.01)/(1+B12)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="E12" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+E9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B12)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+E9)^10*(1+D6)/MAX(B12-D6,0.01)/(1+B12)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="F12" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+F9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B12)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+F9)^10*(1+D6)/MAX(B12-D6,0.01)/(1+B12)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="G12" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+G9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B12)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+G9)^10*(1+D6)/MAX(B12-D6,0.01)/(1+B12)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="H12" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+H9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B12)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+H9)^10*(1+D6)/MAX(B12-D6,0.01)/(1+B12)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="I12" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+I9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B12)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+I9)^10*(1+D6)/MAX(B12-D6,0.01)/(1+B12)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="J12" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+J9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B12)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+J9)^10*(1+D6)/MAX(B12-D6,0.01)/(1+B12)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="K12" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+K9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B12)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+K9)^10*(1+D6)/MAX(B12-D6,0.01)/(1+B12)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="L12" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+L9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B12)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+L9)^10*(1+D6)/MAX(B12-D6,0.01)/(1+B12)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="B13" s="59">
+      <c r="B13" s="62">
         <f>'DCF Valuation'!C4+(0.0)</f>
         <v/>
       </c>
-      <c r="C13" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+C9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B13)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+C9)^10*(1+D6)/MAX(B13-D6,0.0001)/(1+B13)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="D13" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+D9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B13)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+D9)^10*(1+D6)/MAX(B13-D6,0.0001)/(1+B13)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="E13" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+E9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B13)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+E9)^10*(1+D6)/MAX(B13-D6,0.0001)/(1+B13)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="F13" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+F9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B13)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+F9)^10*(1+D6)/MAX(B13-D6,0.0001)/(1+B13)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="G13" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+G9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B13)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+G9)^10*(1+D6)/MAX(B13-D6,0.0001)/(1+B13)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="H13" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+H9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B13)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+H9)^10*(1+D6)/MAX(B13-D6,0.0001)/(1+B13)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="I13" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+I9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B13)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+I9)^10*(1+D6)/MAX(B13-D6,0.0001)/(1+B13)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="J13" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+J9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B13)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+J9)^10*(1+D6)/MAX(B13-D6,0.0001)/(1+B13)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+      <c r="C13" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+C9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B13)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+C9)^10*(1+D6)/MAX(B13-D6,0.01)/(1+B13)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="D13" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+D9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B13)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+D9)^10*(1+D6)/MAX(B13-D6,0.01)/(1+B13)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="E13" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+E9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B13)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+E9)^10*(1+D6)/MAX(B13-D6,0.01)/(1+B13)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="F13" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+F9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B13)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+F9)^10*(1+D6)/MAX(B13-D6,0.01)/(1+B13)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="G13" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+G9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B13)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+G9)^10*(1+D6)/MAX(B13-D6,0.01)/(1+B13)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="H13" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+H9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B13)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+H9)^10*(1+D6)/MAX(B13-D6,0.01)/(1+B13)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="I13" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+I9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B13)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+I9)^10*(1+D6)/MAX(B13-D6,0.01)/(1+B13)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="J13" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+J9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B13)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+J9)^10*(1+D6)/MAX(B13-D6,0.01)/(1+B13)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="K13" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+K9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B13)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+K9)^10*(1+D6)/MAX(B13-D6,0.01)/(1+B13)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="L13" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+L9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B13)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+L9)^10*(1+D6)/MAX(B13-D6,0.01)/(1+B13)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
-      <c r="B14" s="59">
+      <c r="B14" s="62">
         <f>'DCF Valuation'!C4+(0.005)</f>
         <v/>
       </c>
-      <c r="C14" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+C9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B14)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+C9)^10*(1+D6)/MAX(B14-D6,0.0001)/(1+B14)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="D14" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+D9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B14)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+D9)^10*(1+D6)/MAX(B14-D6,0.0001)/(1+B14)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="E14" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+E9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B14)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+E9)^10*(1+D6)/MAX(B14-D6,0.0001)/(1+B14)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="F14" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+F9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B14)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+F9)^10*(1+D6)/MAX(B14-D6,0.0001)/(1+B14)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="G14" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+G9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B14)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+G9)^10*(1+D6)/MAX(B14-D6,0.0001)/(1+B14)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="H14" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+H9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B14)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+H9)^10*(1+D6)/MAX(B14-D6,0.0001)/(1+B14)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="I14" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+I9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B14)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+I9)^10*(1+D6)/MAX(B14-D6,0.0001)/(1+B14)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="J14" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+J9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B14)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+J9)^10*(1+D6)/MAX(B14-D6,0.0001)/(1+B14)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+      <c r="C14" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+C9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B14)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+C9)^10*(1+D6)/MAX(B14-D6,0.01)/(1+B14)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="D14" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+D9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B14)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+D9)^10*(1+D6)/MAX(B14-D6,0.01)/(1+B14)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="E14" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+E9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B14)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+E9)^10*(1+D6)/MAX(B14-D6,0.01)/(1+B14)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="F14" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+F9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B14)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+F9)^10*(1+D6)/MAX(B14-D6,0.01)/(1+B14)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="G14" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+G9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B14)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+G9)^10*(1+D6)/MAX(B14-D6,0.01)/(1+B14)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="H14" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+H9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B14)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+H9)^10*(1+D6)/MAX(B14-D6,0.01)/(1+B14)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="I14" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+I9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B14)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+I9)^10*(1+D6)/MAX(B14-D6,0.01)/(1+B14)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="J14" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+J9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B14)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+J9)^10*(1+D6)/MAX(B14-D6,0.01)/(1+B14)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="K14" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+K9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B14)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+K9)^10*(1+D6)/MAX(B14-D6,0.01)/(1+B14)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="L14" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+L9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B14)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+L9)^10*(1+D6)/MAX(B14-D6,0.01)/(1+B14)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="B15" s="59">
+      <c r="B15" s="62">
         <f>'DCF Valuation'!C4+(0.01)</f>
         <v/>
       </c>
-      <c r="C15" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+C9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B15)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+C9)^10*(1+D6)/MAX(B15-D6,0.0001)/(1+B15)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="D15" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+D9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B15)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+D9)^10*(1+D6)/MAX(B15-D6,0.0001)/(1+B15)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="E15" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+E9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B15)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+E9)^10*(1+D6)/MAX(B15-D6,0.0001)/(1+B15)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="F15" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+F9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B15)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+F9)^10*(1+D6)/MAX(B15-D6,0.0001)/(1+B15)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="G15" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+G9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B15)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+G9)^10*(1+D6)/MAX(B15-D6,0.0001)/(1+B15)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="H15" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+H9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B15)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+H9)^10*(1+D6)/MAX(B15-D6,0.0001)/(1+B15)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="I15" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+I9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B15)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+I9)^10*(1+D6)/MAX(B15-D6,0.0001)/(1+B15)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="J15" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+J9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B15)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+J9)^10*(1+D6)/MAX(B15-D6,0.0001)/(1+B15)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+      <c r="C15" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+C9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B15)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+C9)^10*(1+D6)/MAX(B15-D6,0.01)/(1+B15)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="D15" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+D9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B15)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+D9)^10*(1+D6)/MAX(B15-D6,0.01)/(1+B15)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="E15" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+E9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B15)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+E9)^10*(1+D6)/MAX(B15-D6,0.01)/(1+B15)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="F15" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+F9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B15)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+F9)^10*(1+D6)/MAX(B15-D6,0.01)/(1+B15)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="G15" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+G9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B15)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+G9)^10*(1+D6)/MAX(B15-D6,0.01)/(1+B15)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="H15" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+H9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B15)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+H9)^10*(1+D6)/MAX(B15-D6,0.01)/(1+B15)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="I15" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+I9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B15)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+I9)^10*(1+D6)/MAX(B15-D6,0.01)/(1+B15)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="J15" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+J9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B15)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+J9)^10*(1+D6)/MAX(B15-D6,0.01)/(1+B15)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="K15" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+K9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B15)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+K9)^10*(1+D6)/MAX(B15-D6,0.01)/(1+B15)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="L15" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+L9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B15)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+L9)^10*(1+D6)/MAX(B15-D6,0.01)/(1+B15)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
-      <c r="B16" s="59">
+      <c r="B16" s="62">
         <f>'DCF Valuation'!C4+(0.015)</f>
         <v/>
       </c>
-      <c r="C16" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+C9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B16)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+C9)^10*(1+D6)/MAX(B16-D6,0.0001)/(1+B16)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="D16" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+D9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B16)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+D9)^10*(1+D6)/MAX(B16-D6,0.0001)/(1+B16)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="E16" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+E9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B16)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+E9)^10*(1+D6)/MAX(B16-D6,0.0001)/(1+B16)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="F16" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+F9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B16)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+F9)^10*(1+D6)/MAX(B16-D6,0.0001)/(1+B16)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="G16" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+G9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B16)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+G9)^10*(1+D6)/MAX(B16-D6,0.0001)/(1+B16)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="H16" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+H9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B16)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+H9)^10*(1+D6)/MAX(B16-D6,0.0001)/(1+B16)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="I16" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+I9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B16)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+I9)^10*(1+D6)/MAX(B16-D6,0.0001)/(1+B16)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
-        <v/>
-      </c>
-      <c r="J16" s="53">
-        <f>IFERROR((SUMPRODUCT(Assumptions!C28*D5*(1+J9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B16)^{1,2,3,4,5,6,7,8,9,10})+Assumptions!C28*D5*(1+J9)^10*(1+D6)/MAX(B16-D6,0.0001)/(1+B16)^10-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+      <c r="C16" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+C9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B16)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+C9)^10*(1+D6)/MAX(B16-D6,0.01)/(1+B16)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="D16" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+D9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B16)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+D9)^10*(1+D6)/MAX(B16-D6,0.01)/(1+B16)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="E16" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+E9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B16)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+E9)^10*(1+D6)/MAX(B16-D6,0.01)/(1+B16)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="F16" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+F9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B16)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+F9)^10*(1+D6)/MAX(B16-D6,0.01)/(1+B16)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="G16" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+G9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B16)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+G9)^10*(1+D6)/MAX(B16-D6,0.01)/(1+B16)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="H16" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+H9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B16)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+H9)^10*(1+D6)/MAX(B16-D6,0.01)/(1+B16)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="I16" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+I9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B16)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+I9)^10*(1+D6)/MAX(B16-D6,0.01)/(1+B16)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="J16" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+J9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B16)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+J9)^10*(1+D6)/MAX(B16-D6,0.01)/(1+B16)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="K16" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+K9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B16)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+K9)^10*(1+D6)/MAX(B16-D6,0.01)/(1+B16)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
+        <v/>
+      </c>
+      <c r="L16" s="56">
+        <f>IFERROR(MAX(0,SUMPRODUCT(Assumptions!C28*D5*(1+L9)^{1,2,3,4,5,6,7,8,9,10},1/(1+B16)^({1,2,3,4,5,6,7,8,9,10}-Assumptions!C31))+Assumptions!C28*D5*(1+L9)^10*(1+D6)/MAX(B16-D6,0.01)/(1+B16)^(10-Assumptions!C31)-(Assumptions!C8-Assumptions!E8))/Assumptions!E7,"--")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="14" customHeight="1">
-      <c r="B18" s="76" t="inlineStr">
+      <c r="B18" s="79" t="inlineStr">
         <is>
           <t xml:space="preserve">  HOW TO READ: Find your WACC row (0.00% offset = model WACC). Scan right to find where implied price matches market price. That column = market-implied growth rate.</t>
         </is>
       </c>
-      <c r="C18" s="72" t="n"/>
-      <c r="D18" s="72" t="n"/>
-      <c r="E18" s="72" t="n"/>
-      <c r="F18" s="72" t="n"/>
-      <c r="G18" s="72" t="n"/>
-      <c r="H18" s="72" t="n"/>
-      <c r="I18" s="72" t="n"/>
-      <c r="J18" s="72" t="n"/>
-      <c r="K18" s="73" t="n"/>
+      <c r="C18" s="75" t="n"/>
+      <c r="D18" s="75" t="n"/>
+      <c r="E18" s="75" t="n"/>
+      <c r="F18" s="75" t="n"/>
+      <c r="G18" s="75" t="n"/>
+      <c r="H18" s="75" t="n"/>
+      <c r="I18" s="75" t="n"/>
+      <c r="J18" s="75" t="n"/>
+      <c r="K18" s="75" t="n"/>
+      <c r="L18" s="76" t="n"/>
     </row>
     <row r="19" ht="14" customHeight="1">
-      <c r="B19" s="76" t="inlineStr">
+      <c r="B19" s="79" t="inlineStr">
         <is>
           <t xml:space="preserve">  This uses a UNIFORM growth rate for all 10 years. For two-phase growth analysis, see the Scenarios sheet.</t>
         </is>
       </c>
-      <c r="C19" s="72" t="n"/>
-      <c r="D19" s="72" t="n"/>
-      <c r="E19" s="72" t="n"/>
-      <c r="F19" s="72" t="n"/>
-      <c r="G19" s="72" t="n"/>
-      <c r="H19" s="72" t="n"/>
-      <c r="I19" s="72" t="n"/>
-      <c r="J19" s="72" t="n"/>
-      <c r="K19" s="73" t="n"/>
+      <c r="C19" s="75" t="n"/>
+      <c r="D19" s="75" t="n"/>
+      <c r="E19" s="75" t="n"/>
+      <c r="F19" s="75" t="n"/>
+      <c r="G19" s="75" t="n"/>
+      <c r="H19" s="75" t="n"/>
+      <c r="I19" s="75" t="n"/>
+      <c r="J19" s="75" t="n"/>
+      <c r="K19" s="75" t="n"/>
+      <c r="L19" s="76" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="E5:K5"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B1:K1"/>
+    <mergeCell ref="E4:L4"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B18:K18"/>
-    <mergeCell ref="E4:K4"/>
-    <mergeCell ref="B8:J8"/>
-    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B19:L19"/>
+    <mergeCell ref="E5:L5"/>
     <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B19:K19"/>
+    <mergeCell ref="B18:L18"/>
+    <mergeCell ref="B1:L1"/>
+    <mergeCell ref="B8:L8"/>
   </mergeCells>
-  <conditionalFormatting sqref="C10:J16">
+  <conditionalFormatting sqref="C10:L16">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
